--- a/events_master.xlsx
+++ b/events_master.xlsx
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="mmmm d, yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mmmm d, yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -50,12 +49,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K17" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K19" headerRowCount="1">
   <autoFilter ref="A1:K17"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
@@ -548,7 +548,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="3" t="n">
         <v>46279</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,7 +601,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="3" t="n">
         <v>46496</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -654,7 +654,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="3" t="n">
         <v>46678</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -707,7 +707,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="3" t="n">
         <v>46231</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -720,7 +720,6 @@
           <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/mwFE8ZYhmC3Ce</t>
@@ -756,7 +755,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,7 +768,6 @@
           <t>6:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/ibm-skillsbuild-orientation-1693369?sourceTypeId=Website</t>
@@ -805,7 +803,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="3" t="n">
         <v>46239</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -818,7 +816,6 @@
           <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/MwFNl0es8CeCg</t>
@@ -850,7 +847,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="3" t="n">
         <v>46240</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -863,7 +860,6 @@
           <t>4:00 PM - 12:30 PM</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/rural-ai-workforce-forum-2026-1759715?sourceTypeId=Website</t>
@@ -899,7 +895,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D9" s="3" t="n">
         <v>46247</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -912,7 +908,6 @@
           <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/WqFgM07iaCJCE</t>
@@ -948,7 +943,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="3" t="n">
         <v>46252</v>
       </c>
       <c r="E10" t="inlineStr">
@@ -961,7 +956,6 @@
           <t>8:00 AM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/12F2XblUgCVCB</t>
@@ -993,7 +987,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D11" s="3" t="n">
         <v>46261</v>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1000,6 @@
           <t>5:00 PM - 7:45 PM</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/xRF50ZqHMCYC7</t>
@@ -1042,7 +1035,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="3" t="n">
         <v>46261</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -1055,7 +1048,6 @@
           <t>6:00 PM - 7:30 PM</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/EqFedRnCgC6C9</t>
@@ -1091,7 +1083,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D13" s="3" t="n">
         <v>46280</v>
       </c>
       <c r="E13" t="inlineStr">
@@ -1104,7 +1096,6 @@
           <t>10:00 AM - 3:00 PM</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/OOFNE8dhaCqCD</t>
@@ -1136,7 +1127,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="3" t="n">
         <v>46282</v>
       </c>
       <c r="E14" t="inlineStr">
@@ -1149,7 +1140,6 @@
           <t>5:30 PM - 8:00 PM</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/beyond-connected-iot-s-next-chapter-presented-by-tag-cloud-society-1848946?sourceTypeId=Website</t>
@@ -1185,7 +1175,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D15" s="3" t="n">
         <v>46283</v>
       </c>
       <c r="E15" t="inlineStr">
@@ -1198,7 +1188,6 @@
           <t>8:00 AM - 3:00 PM</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/R1Fo7y2FRC0CX</t>
@@ -1234,7 +1223,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D16" s="3" t="n">
         <v>46303</v>
       </c>
       <c r="E16" t="inlineStr">
@@ -1247,7 +1236,6 @@
           <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/kgFYW1VuzCVC1</t>
@@ -1283,7 +1271,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D17" s="3" t="n">
         <v>46317</v>
       </c>
       <c r="E17" t="inlineStr">
@@ -1296,7 +1284,6 @@
           <t>1:00 PM - 5:00 PM</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/QZFMBR6tdCnC0</t>
@@ -1317,6 +1304,56 @@
           <t>While TAG is a Georgia-focused organization and this is a pitch/networking event for tech entrepreneurs, the event description has zero mention of AI, machine learning, or automation, making it an automatic low score; the virtual-only format with a Georgia org prevents it from being a 1, but the lack of AI content keeps it at 2.</t>
         </is>
       </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://ai.gatech.edu/events</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>failed: unexpected error: Connection error.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>failed: unexpected error: Connection error.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1419,7 +1456,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="3" t="n">
         <v>46232</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -1432,7 +1469,6 @@
           <t>5:00 PM - 8:00 PM</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/israeli-cybersecurity-summit-1360489?sourceTypeId=Website</t>
@@ -1464,7 +1500,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="3" t="n">
         <v>46237</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -1477,7 +1513,6 @@
           <t>5:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/EqF6GN4IgC6C9</t>
@@ -1513,7 +1548,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="3" t="n">
         <v>46238</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -1526,7 +1561,6 @@
           <t>12:30 PM - 1:00 PM</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/VeFAOextNCeC9</t>
@@ -1562,7 +1596,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="3" t="n">
         <v>46246</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -1575,7 +1609,6 @@
           <t>6:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/qWFX016fkCQCe</t>
@@ -1611,7 +1644,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -1624,7 +1657,6 @@
           <t>12:30 PM - 1:00 PM</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/7EFZQMQsNCQCd</t>
@@ -1656,7 +1688,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="3" t="n">
         <v>46279</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -1669,7 +1701,6 @@
           <t>5:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/VeFXK8WSNCeC9</t>
@@ -1705,7 +1736,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="3" t="n">
         <v>46300</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -1718,7 +1749,6 @@
           <t>5:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/nvF6MwdSECNCZ</t>
@@ -1754,7 +1784,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D9" s="3" t="n">
         <v>46301</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -1767,7 +1797,6 @@
           <t>12:30 PM - 1:00 PM</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/3BFg2ejHYCQCg</t>
@@ -1799,7 +1828,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="3" t="n">
         <v>46328</v>
       </c>
       <c r="E10" t="inlineStr">
@@ -1812,7 +1841,6 @@
           <t>5:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/jKFGO1mfZCkCE</t>
@@ -1848,7 +1876,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D11" s="3" t="n">
         <v>46329</v>
       </c>
       <c r="E11" t="inlineStr">
@@ -1861,7 +1889,6 @@
           <t>12:30 PM - 1:00 PM</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/9eFlWx1fWC9Cx</t>
@@ -1893,7 +1920,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="3" t="n">
         <v>46331</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -1906,7 +1933,6 @@
           <t>11:30 AM - 2:00 PM</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/pending-veterans-day-presented-by-tag-infrastructure-society-1775943?sourceTypeId=Website</t>
@@ -1938,7 +1964,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D13" s="3" t="n">
         <v>46345</v>
       </c>
       <c r="E13" t="inlineStr">
@@ -1951,7 +1977,6 @@
           <t>6:00 PM - 11:00 PM</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/tag-chairs-gala-2026-1569285?sourceTypeId=Website</t>
@@ -1983,7 +2008,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="3" t="n">
         <v>46357</v>
       </c>
       <c r="E14" t="inlineStr">
@@ -1996,7 +2021,6 @@
           <t>12:30 PM - 1:00 PM</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/xRFXAz4IMCYC7</t>
@@ -2028,7 +2052,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D15" s="3" t="n">
         <v>46360</v>
       </c>
       <c r="E15" t="inlineStr">
@@ -2041,7 +2065,6 @@
           <t>9:00 AM - 3:00 PM</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/oXFq4V1T6C2CB</t>
@@ -2077,7 +2100,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D16" s="3" t="n">
         <v>46363</v>
       </c>
       <c r="E16" t="inlineStr">
@@ -2090,7 +2113,6 @@
           <t>5:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/G9FwqlWUNCxCK</t>

--- a/events_master.xlsx
+++ b/events_master.xlsx
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K19" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K21" headerRowCount="1">
   <autoFilter ref="A1:K17"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1311,17 +1311,12 @@
           <t>https://ai.gatech.edu/events</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>July 26, 2026</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>failed: unexpected error: Connection error.</t>
@@ -1336,17 +1331,12 @@
           <t>https://members.tagonline.org/calendar</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>July 26, 2026</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>failed: unexpected error: Connection error.</t>
@@ -1354,6 +1344,56 @@
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://ai.gatech.edu/events</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>failed: unexpected error: Connection error.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>failed: unexpected error: Connection error.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/events_master.xlsx
+++ b/events_master.xlsx
@@ -1351,17 +1351,12 @@
           <t>https://ai.gatech.edu/events</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" s="3" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>July 26, 2026</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>failed: unexpected error: Connection error.</t>
@@ -1376,17 +1371,12 @@
           <t>https://members.tagonline.org/calendar</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>July 26, 2026</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>failed: unexpected error: Connection error.</t>

--- a/events_master.xlsx
+++ b/events_master.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mmmm d, yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -133,7 +134,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K21" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K62" headerRowCount="1">
   <autoFilter ref="A1:K17"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -153,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K16" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K85" headerRowCount="1">
   <autoFilter ref="A1:K16"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -461,16 +462,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
@@ -1384,6 +1385,1951 @@
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Manufacturing Technology Challenges: Practical Solutions for Today's Pla...</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>11:00 AM - 1:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/tech-educational-panel</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or available description, triggering the automatic 1 rating regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AIMST - AI Conference - GMA Special Exhibitor and Moderator</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>August 18, 2026 - August 20, 2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/aimst---ai-conference---gma-special-exhibitor-and-moderator</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>AIMST is a known AI-focused multi-day conference (August 18-20, 2026) marked as in-person, scoring highly despite missing location details, though the lack of explicit location confirmation and empty description fields prevent a perfect score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026 Georgia Manufacturing Summit</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>7:00 AM - 4:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/2026-georgia-manufacturing-summit</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering an automatic score of 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AIMST 2026 Atlanta</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Renaissance Atlanta Waverly Hotel &amp; Convention Center, 2450 Galleria Pkwy, Atlanta, GA 30339</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.meetmax.com/sched/event_130973/conference_register.html?attendee_role_id=TWST2_ATTENDEE&amp;grp_name=ATTENDEE&amp;approved=Y&amp;_gl=1*g58gv2*_gcl_au*Mjc2MTM5ODY0LjE3ODEwMTU3MjQ.*_ga*MTYwNTkxMjEyNC4xNzU2MjA4NDM5*_ga_M7N3QCZSH0*czE3ODM5OTUzOTAkbzExNCRnMSR0MTc4Mzk5NjQ2NiRqMzkkbDAkaDA.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>North America's #1 Conference in Industrial AI, focused on providing in-depth discussions and solutions for heads of manufacturing, advanced technology managers, ICS, IT/OT, SCADA and cyber security professionals to accelerate their digital transformation and transform their operational and automation systems. Features 60+ speakers, 350+ attendees, three tech tracks (AI Manufacturing, Industrial AI 101 for SMEs, SCADA Technology &amp; AI Utilities), and 8+ networking events.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>AIMST 2026 is a major in-person industrial AI conference in Atlanta with strong AI content (60+ speakers, multiple AI-focused tracks), multi-day format, and located in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PAi Manufacturing Facility Tour</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.aimanufacturingconference.com/ *</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Get an inside look at one of Georgia's advanced manufacturing operations. The 120,000 sq. ft. production facility features 50 CNC machining centers and 32 industrial robots. Guided behind-the-scenes tour, complimentary for AIMST attendees. Advance registration required. Space is limited.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>While the event is in-person in Atlanta, GA, the facility tour itself contains no explicit mention of AI, machine learning, or automation—only generic industrial equipment (CNC centers, robots)—and appears to be a supplementary activity rather than an educational AI event, despite being associated with AIMST.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TechConnect: Global Virtual Job &amp; Networking Event for Data, AI, and Tech Pros</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>4:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ac-atl/events/313188287/?recId=a09690ef-3910-490f-96e4-7d5d43788405&amp;recSource=ml-popular-events-nearby-online&amp;searchId=93363a32-61af-4fb3-a948-c0f60180aeea&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only job/networking event with AI content mentioned in title, but no description provided to verify educational value, and no Georgia focus indicated despite being from AC-ATL meetup group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GA AI Alliance Networking Lunch</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>11:45 AM EDT</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/georgia-ai-alliance-meetup-group/events/315317984/?recId=a09690ef-3910-490f-96e4-7d5d43788405&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=93363a32-61af-4fb3-a948-c0f60180aeea&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Event is marked in-person and organized by Georgia AI Alliance (Georgia-focused), which suggests good fit, but the empty description and 'networking lunch' format provide no evidence of actual AI content, making it potentially just a generic social event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>West Midtown AI Meetup (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-at-7-28</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>In-person AI meetup in Atlanta hosted by The AI Collective with clear AI focus, but lacks detailed description to confirm educational/discussion content versus networking-only format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI in Flooring (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dalton, GA</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-da-7-29</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Georgia (Dalton) with AI content focus, though the empty description and niche industry application (flooring) create some uncertainty about depth and educational value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Practical AI at Work: Create Your Own AI Work Companion</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Zoom</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://luma.com/h6svmuok</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with AI content in the title, but no Georgia focus, organization details, or description provided to elevate it beyond a generic national webinar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Macon Chapter Kickoff (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Macon, GA</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-ma-7-29</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Georgia with AI organization involvement (The AI Collective), but extremely sparse description provides no detail about actual AI content or educational value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>The AI Tasting Room (w/ The AI Collective FAYETTEVILLE Ga)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Fayetteville, GA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-at-7-29</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Event is in-person in Georgia (positive factors) but has zero description content, making it impossible to verify if it actually contains AI/ML/automation discussion rather than being a generic social event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Agentic AI series: Multi Agent Orchestration - Phinite x AI Collective Dallas</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Zoom</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-dallas-7-15</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with AI content (Agentic AI/Multi Agent Orchestration) but hosted by a Dallas-based organization with no Georgia focus or institution affiliation, scoring it as a national virtual event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>The AI Collective Abidjan | Demo Day #1 — L'IA qui se construit à Abidjan (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Abidjan, Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-ab-7-31</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Event appears to be AI-focused based on title mentioning 'The AI Collective' and 'Demo Day', but lacks substantive description to confirm AI content, is located in Côte d'Ivoire (not Georgia), and has no connection to Georgia institutions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PNP - BUSINESS MATCHING OMNICHANNEL GT-MT-ECOM 2026 X AI AGENT</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>10:00 PM</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Google Meet</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://luma.com/4ujxu576</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>While the title mentions 'AI Agent', the event description is empty and provides no actual details about AI/ML content, making it impossible to verify the event has substantive AI focus beyond the title.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>The Copilot Effect: Power Platform Copilot (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>5:00 AM</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-du-8-5</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with AI/automation content (Copilot, Power Platform) but no indication it's Georgia-focused or hosted by a Georgia institution, scoring it in the low range for virtual events per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI Paper Discussion ft. AIC Delhi Paper Club</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>12:30 AM</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-de-8-8</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Event clearly involves AI content (paper discussion) and is marked as in-person, but location is blank and the description is empty, making it impossible to determine if it's Georgia-based or relevant to the Georgia AI community.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Small Business AI Implementation Lab (w/ The AI Collective ATL)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1:30 PM</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Milton, GA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-at-8-8</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Georgia with clear AI focus (AI implementation for small business), hosted by a Georgia-based organization (The AI Collective ATL), though minimal description details limit confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Office Hours (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://luma.com/tol-office-hours-8-11-26</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its own title or description (only 'Office Hours' is mentioned), making it an automatic 1 per criteria, though low confidence due to extremely sparse event details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Work in the GenAI Era: From AI Pilots to AI-Native Organizations (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-ha-8-4</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Event focuses on GenAI and organizational transformation (good AI content), but is virtual-only with no indication of Georgia focus or hosting institution, and lacks sufficient details to confirm it's not a sales pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Practical AI at Work: Build an Automated Inbox Hero</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://luma.com/81m5s002</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with AI/automation content in the title ('Automated Inbox Hero'), but lacks Georgia focus or institutional affiliation, and the vague description and missing location details prevent higher scoring despite the AI theme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Vibe Night Midtown (w/ The AI Collective) #ATLTechWeek</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-at-8-13-1</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Event is in-person in Atlanta with AI Collective involvement, but the empty description provides no evidence of actual AI/ML content beyond the organizer name, making it likely a networking or social event rather than educational AI content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Office Hours (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://luma.com/tol-office-hours-8-25-26</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 despite the AI-focused organization hosting it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Parenting with AI (w/ The AI Collective Kansas City)</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Google Meet</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://luma.com/ParentingWithAI</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with AI content in title but no Georgia focus, hosted by Kansas City organization, scoring above 1 due to AI topic but capped at 2 per virtual-only criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Practical AI at Work: Turn Your Brand Guide Into an AI-Ready Skill</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://luma.com/0egsw9cf</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Event mentions AI in the title and appears to be an educational/practical AI session, but lacks location information, is virtual-only with no indication of Georgia focus or institution affiliation, and has an incomplete description that limits assessment of depth and legitimacy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>🧠 The AI Collective Netherlands | September Meetup (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-nl-sept-26</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Event has no mention of AI, machine learning, or automation in its title or description, and while marked as in-person, the location is listed as Netherlands (not Georgia), making it an automatic 1 regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Hack for Humanity (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>46270</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>3:00 AM</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-na-9-5</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Event title suggests AI/ML relevance ('The AI Collective') but lacks any description confirming AI content, location is blank despite in-person flag, and unclear if Georgia-based without more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AI Assessment Workshop: Partnering with AI Before the School Year Begins</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Atlanta · Mount Vernon School, Upper Campus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-assessment-workshop-partnering-with-ai-before-the-school-year-begins-tickets-1992480807732?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Atlanta with clear AI content focus (AI assessment and partnering with AI), scoring highest for Georgia location, though limited description details prevent maximum confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Atlanta Tech Mixer and Social (Tech / AI / Data / IT) ✨</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Atlanta · Stats Brewpub</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/atlanta-tech-mixer-and-social-tech-ai-data-it-tickets-1987408339844?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>While this is an in-person Atlanta event mentioning AI in the title, it appears to be a generic networking mixer/social rather than an educational or substantive AI-focused event, and the empty description provides insufficient detail about actual AI content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Data Science with Phython Certification Training in Columbus, GA</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Columbus · Veterans Parkway</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/data-science-with-phython-certification-training-in-columbus-ga-tickets-1984660920238?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>While the event is in-person in Georgia (Columbus) with AI/data science content, it appears to be a paid certification training with a heavy sales pitch nature rather than an educational discussion or conference, and the vague description limits confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Georgia Tech ME 2110 Design Competition: Summer 2026</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Manufacturing Related Disciplines Complex, 801 Ferst Dr, Atlanta, GA 30332</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/georgia-tech-me-2110-design-competition-summer-2026-registration-1991920152798?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>The event title and short description contain zero mention of AI, machine learning, or automation, making it an automatic 1 despite being an in-person Georgia Tech event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Everything but the Camera: ACS</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Atlanta · Atlanta Axis Experience Center</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/everything-but-the-camera-acs-tickets-1990888109930?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Wednesd.AI</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Atlanta · Atlanta Tech Village - Buckhead</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/wednesdai-tickets-1990814107587?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>In-person AI event in Atlanta with a clear AI focus (Wednesd.AI suggests an AI-themed weekly meetup), though confidence is limited by the missing event description.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AI for the real World: Week 4: Make a Talking Video with AI (HeyGen Part 1</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>East Point · 1928 Stanton Rd</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-for-the-real-world-week-4-make-a-talking-video-with-ai-heygen-part-1-tickets-1992736032115?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Georgia (East Point) with clear AI content (HeyGen video generation tool), though the practical/hands-on training nature and lack of detailed description prevent a higher score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Tech, AI &amp; Startups Roundtable Discussion Dinner</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>4</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Atlanta · Aviva by Kameel Buckhead</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/tech-ai-startups-roundtable-discussion-dinner-tickets-1988373794545?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Atlanta with clear AI focus in title, though the empty description limits full assessment of content depth and quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AI Awareness: The Good, the Bad, and What to Watch For</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-awareness-the-good-the-bad-and-what-to-watch-for-tickets-1991930436557?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Event has clear AI content in its title, but is virtual-only with no indication of Georgia focus or Georgia institution affiliation, and missing critical details like date, time, and description make it difficult to assess educational value versus sales pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AI Tinkerers Atlanta: 2-Year Anniversary &amp; Best Demos of the Year</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://atlanta.aitinkerers.org/p/ai-tinkerers-atlanta-2-year-anniversary-best-demos-of-the-year</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>AI Tinkerers Atlanta will celebrate its second anniversary with a showcase of the year's best demonstrations.</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with clear AI focus (AI demonstrations and tinkering), hosted by an established local AI community organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AI Builders #20: Lunch &amp; Learn</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>5</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044232/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence is a force that is changing the technology landscape (and world) as we know it. Come to the AI Builders Lunch &amp; Learn to keep your finger on the pulse! Topics include the latest cool AI tools, integrating AIs into projects via APIs, and customizing agents and models. Bring your own sack lunch, or door dash something to the Lab. Join on the first Wednesday of every month for learning, engaging discussion, and networking in the AI space. All skill levels welcome!</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>In-person AI educational event in Atlanta with clear technical content (AI tools, APIs, agents, models), hosted at a specific Georgia location, welcoming all skill levels for monthly learning and networking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>The AI Underground - Conference</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>5</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>9:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://aiunderground.dev</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>A conference for people building the future of freedom with AI. From open weight models to open source agents, the AI Underground brings together the minds building AI into a technology of liberation.</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>In-person AI conference in Atlanta, Georgia with clear focus on AI technology, open-source models, and agents, scoring highest on location and substantive AI content criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>AI Builders #21: Lunch &amp; Learn</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044241/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Event title suggests AI content ('AI Builders') and is in-person, but lacks description and location details, and the meetup link suggests it's Atlanta-based (atlbitlab) which supports Georgia scoring, though the missing event description creates substantial uncertainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>AI Builders #22: Lunch &amp; Learn</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044251/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Event appears to be an in-person AI-focused Lunch &amp; Learn in Georgia (Atlanta Bitlab), but the extremely sparse description and missing location details prevent higher confidence in the rating.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1399,7 +3345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1407,8 +3353,8 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
@@ -2164,6 +4110,3391 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Murray Plastics Factory Tour - SMTA Joint Event - Gainesville</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>9:00 AM - 12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Gainesville, Georgia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/murray-plastics-factory-tour---smta-joint-event---gainesville</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is a factory tour, triggering the automatic 1 rating per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Murray Plastics Factory Tour - SMTA Joint Event - Gainesville - AFTERNOON</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>11:30 AM - 4:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Gainesville, Georgia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/murray-plastics-factory-tour---smta-joint-event---gainesville---afternoon</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Women of GMA Virtual Networking Event 8/11/26</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>3:30 PM - 4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/women-of-gma-virtual-networking-event-81126</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Coffee and Connections - Atlanta 8-20-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8:30 AM - 10:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/coffee-and-connections-atlanta-8-20-2026</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Atlanta location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Networking Luncheon - Atlanta 8-20-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>11:30 AM - 1:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/networking-luncheon-atlanta-8-20-2026</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria regardless of its in-person Atlanta location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Southeastern Hose - Bremen</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1:30 PM - 4:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Bremen, Georgia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/southeastern-hose---bremen</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 score regardless of in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>🎬 404 Movie Not Found: Spider-Man (Matinee)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/refactr-tech/events/314126109/?recId=a09690ef-3910-490f-96e4-7d5d43788405&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=93363a32-61af-4fb3-a948-c0f60180aeea&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation - it is a movie screening event, which triggers the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Atlanta Tech Meet-Up</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atl-tech-meetup/events/315779247/?recId=a09690ef-3910-490f-96e4-7d5d43788405&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=93363a32-61af-4fb3-a948-c0f60180aeea&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Open House!</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>7:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/freeside-atlanta/events/312398713/?recId=a09690ef-3910-490f-96e4-7d5d43788405&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=93363a32-61af-4fb3-a948-c0f60180aeea&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation, triggering the automatic 1 rating regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Happy Birthday OWASP! 25 Year Anniversary Party</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>6:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/owasp-atlanta/events/315447074/?recId=a09690ef-3910-490f-96e4-7d5d43788405&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=93363a32-61af-4fb3-a948-c0f60180aeea&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description—it is solely a birthday party for OWASP, making it an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Off the Record: Tech Week Pre-Game Sunday on the Deck for Founders &amp; Funders</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://luma.com/lozx21c4</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Washington (WA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Office Hours (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Toledo, OH</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://luma.com/tol-office-hours-7-28-26</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Ohio (OH), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CT AI Community Talks (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hartford, CT</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-ha-7-28</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Connecticut (CT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Demo Night: AWS x AI Collective</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Arlington, VA</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-dc-7-28</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Virginia (VA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Collective Costa Rica: MCP in Action: Connect LLMs to the Real World</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>San José, Costa Rica</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-cr-7-28</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Costa Rica, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI Bouldering Social (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>12:30 PM</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>München, Germany</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-mu-7-25</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Germany, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI Builders Night: Demos, Feedback &amp; Collaboration</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>6:45 PM</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Plano, TX</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://luma.com/aibuildersnight3</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Texas (TX), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C-Suite Dinner: The Full Arc of Operationalising AI (w/ FACCI &amp; The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>4:00 AM</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Adelaide, Australia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-ad-7-30</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Australia, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Ghana AI Awards 2026 (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Accra, Ghana</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://luma.com/aiawardsgh</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Ghana, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AI Act, Day One: Building and Scaling Under Europe's New Rules — co-hosted by AWS</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-be-7-30</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Germany, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>HeyGen is coming to Islamabad!!! | AI Avatar Pop-Up (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2:00 AM</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Islamabad, Pakistan</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://luma.com/78_657</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Pakistan, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI &amp; Ayam: The Spice of Innovation</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>6:30 AM</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur, Malaysia</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-kul-20260731</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Malaysia, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AI, liderazgo y talento</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Medellín, Colombia</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-me-7-31</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Colombia, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Automatizaciones + IA: el futuro del trabajo manual (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3:30 PM</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Buenos Aires, Argentina</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://luma.com/automatizaciones-ia</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Argentina, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Building AI You Can Stand Behind: Governance, Security, and Trust in Production (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://luma.com/governance-security-ai</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Washington (WA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Least-Privilege AI Agents (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>10:30 PM</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Saratoga, CA</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-so-7-31</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Location is in California (CA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Design with the End in Mind: Building AI Workflows That Deliver | Stamford AI Meetup | (w/ AI Collective)</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Stamford, CT</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-st-8-4</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Connecticut (CT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Space Coast AI Town Hall</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cocoa, FL</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://luma.com/x62nsa0h</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Florida (FL), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SF DEMO NIGHT 🚀 (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8:30 PM</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://luma.com/august-demo-2026</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Location is in California (CA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>From AI User to AI Builder - Base44 x AI Collective (San Francisco)</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>9:00 PM</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-0kgd</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Location is in California (CA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AIC SF Chapter Team &amp; Volunteer Get-Together (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>9:00 PM</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-sf-team-gettogether</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Location is in California (CA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Vibin' Out | AI Collective - Stamford | (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Shippan Landing, 262 Harbor Dr 1st Floor, Stamford, CT 06902</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-st-8-13</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Connecticut (CT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>From AI User to AI Builder - Base44 x AI Collective (Chicago)</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://luma.com/hqwe2s7q</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Illinois (IL), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Learn to build AI Agents using Hermes (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Detroit, MI</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-de-8-15</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Michigan (MI), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>The Story of AI (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Chattanooga, TN</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-ch-8-15</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Tennessee (TN), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Building with AI: Stamford Micro-Hackathon (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Stamford, CT</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-st-8-19</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Connecticut (CT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Demystifying Local AI: What It Is, Why It Matters, and How to Get Started</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lehi, UT</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-sl-aug2026</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Utah (UT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Step SF 2026: The AI &amp; Tech Startup Festival</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://luma.com/StepSF26</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Location is in California (CA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AI and the Future of Work (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Charlotte, NC</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-ch-8-27</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Location is in North Carolina (NC), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>From AI User to AI Builder - Base44 x AI Collective x UT McCombs MBA Tech Club</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://luma.com/1hxal81p</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Texas (TX), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AI for Civic Impact Hackathon | Hack for Humanity (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>46270</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>4:00 AM</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Fes, Morocco</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-fe-9-5</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Morocco, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SUMMER BREAK - ENJOY AI-FREE TIME IN THE COTTAGE!</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-fi-summer-break</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>The event title explicitly promotes "AI-FREE TIME" with zero mention of AI, machine learning, or automation content, making it an automatic 1 regardless of in-person status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CISSP Certification Training Course in Bothell, CA</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>22722 29th Dr SE West, Suite 100, Bothell, WA 98021</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/cissp-certification-training-course-in-bothell-ca-tickets-1980894231972?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Washington (WA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Bad UX in Numbers: Exploring Real Cases</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/bad-ux-in-numbers-exploring-real-cases-tickets-1993810735582?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Business Analyst (CBAP) Classroom Training in Auburn, AL</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Columbus · 5547 Veterans Pkwy</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/business-analyst-cbap-classroom-training-in-auburn-al-tickets-1970898472386?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is a CBAP (Certified Business Analyst Professional) classroom training course, which is an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Business Analytics Certification (CBAP) Training in Augusta, GA</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Augusta · 823 Broad St</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/business-analytics-certification-cbap-training-in-augusta-ga-tickets-1970052557231?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is a business analytics certification training (CBAP) which is a general business analysis credential unrelated to AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Modern Data Architecture 2 Days Training in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/modern-data-architecture-2-days-training-in-atlanta-ga-tickets-1992366361420?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AWS Solution Architect Training | 4-Day Bootcamp in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Atlanta · 260 Peachtree St suite 2200</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/aws-solution-architect-training-4-day-bootcamp-in-atlanta-ga-tickets-1987119022488?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>While this is an in-person event in Atlanta with a technical focus, it has zero mention of AI, machine learning, or automation in the title or description, making it an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Stronger Communities Through Leadership Skills – 1 Day Training in Atlanta</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Atlanta · Regus - Atlanta - 260 Peachtree</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.sg/e/stronger-communities-through-leadership-skills-1-day-training-in-atlanta-tickets-1702814948349?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering automatic 1 rating regardless of in-person Atlanta location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Certified Ethical Hacker – Practical Ethical Hacker in Macon, GA</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Macon · 500a Northside Crossing</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/certified-ethical-hacker-practical-ethical-hacker-in-macon-ga-tickets-1986302519305?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description - it is a cybersecurity certification course, not an AI-focused event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Naturalist Club: Backyard Habitats &amp; Common Feed Birds</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Kennesaw · North Cobb Regional Library</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/naturalist-club-backyard-habitats-common-feed-birds-tickets-1991154159692?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation - it is about a naturalist club discussing backyard habitats and birds, which automatically qualifies it for a score of 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Naturalist Club: Backyard Habitats &amp; Common Feed Birds</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2:30 PM</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Marietta · East Cobb Library</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/naturalist-club-backyard-habitats-common-feed-birds-tickets-1991153844750?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is about naturalist club activities and bird feeding, which is an automatic 1 regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Naturalist Club: Backyard Habitats &amp; Common Feed Birds</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2:30 PM</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Mableton · South Cobb Regional Library</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/naturalist-club-backyard-habitats-common-feed-birds-tickets-1991154120575?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is about backyard habitats and bird feeding, triggering the automatic 1 rating regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Bitcoin Politics &amp; Pints #1</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044682/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Join the Georgia Bitcoin Council for Bitcoin Politics and Pints, a casual 5th Wednesday meetup for the Atlanta bitcoin community. Each event will create space to discuss political issues surrounding bitcoin and freedom-tech. Some gatherings will feature guest speakers, while others will focus on community presentations and open discussion.</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Bitcoin Builders #8</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044356/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Bitcoin Builders is a meetup for people exploring Bitcoin from a product perspective, focusing on tools, apps, and services that make Bitcoin usable, expressive, and valuable to real people. Each event features five 15-minute demo slots where presenters walk through something they've been working on recently. Expect live demos, short talks, Q&amp;A and discussion, and constructive feedback from other builders.</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation - it is exclusively focused on Bitcoin development and blockchain technology, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BitPlebs Bitcoin Meetup @ ATL BitLab</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044424/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Join us at ATL BitLab for another fun BitPlebs meetup. Featuring a screening and discussion of 'Bitcoin Season', a film following Bitcoin's arrival in the NBA — the Cavs' league-first Bitcoin deal, Klutch Sports, and a roster of voices reframing hard money as the ultimate player-empowerment play. Bring your questions and your cold takes.</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation—it is a Bitcoin meetup focused on a film screening and discussion about cryptocurrency in sports, which triggers the automatic 1 rating regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Nostr Atlanta #15 - Rush Hour Avoidance</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315762247/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Join us for Nostr Atlanta! Calling all nostr users, content creators, enthusiasts, developers, and more! Trying to avoid the nasty rush hour traffic — bring your laptop as this session will involve some tool building. Informal round-table discussion of Nostr and adjacent topics from 4:30–6:00 PM.</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>The event is about Nostr (a decentralized social network protocol) with no mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BitDevs: Bitcoin Socratic Seminar #53</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044445/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Join the Atlanta BitDevs every third Wednesday for a Socratic Seminar to discuss the latest technological developments in Bitcoin and Lightning! Inspired by other BitDevs meetups around the US, events are formatted to foster debate, information sharing and lively discussion. Free drinks during early networking, followed by presentations and a Socratic Seminar, then dinner at a nearby restaurant.</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation - it is exclusively about Bitcoin and Lightning technology discussions, which triggers the automatic 1 rating regardless of other positive factors like in-person Atlanta location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - June</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Manuels Tavern, 602 North Highland Ave NE, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044570/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Join us at Manuel's Tavern for another fun BitPlebs meetup. Atlanta BitPlebs meetups are casual events geared towards helping you learn about how to get bitcoin, use bitcoin, and understand where it fits into current events. Arrive early for some free beverages. Agenda includes kick-off announcements, a presentation, and a beer social.</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is a Bitcoin/cryptocurrency meetup, not an AI-focused event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Bitcoin Builders #9</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044357/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BitPlebs Bitcoin Meetup @ ATL BitLab</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044425/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Join us at ATL BitLab for another fun BitPlebs meetup. Tonight's topic is TBD but will certainly involve bitcoin! These meetups are to help you learn the basics of bitcoin and socialize with other bitcoiners.</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>The event is about Bitcoin and cryptocurrency with no mention of AI, machine learning, or automation, making it an automatic 1 per the criteria regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BitDevs: Bitcoin Socratic Seminar #54</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044444/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Join the Atlanta BitDevs every third Wednesday for a Socratic Seminar to discuss the latest technological developments in Bitcoin and Lightning! Events are formatted to foster debate, information sharing and lively discussion.</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Despite being an in-person event in Atlanta, the event has zero mention of AI, machine learning, or automation—it focuses exclusively on Bitcoin and Lightning technology, making it an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - June</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044571/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Bitcoin Politics &amp; Pints #2</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044686/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Join the Georgia Bitcoin Council for Bitcoin Politics and Pints, a casual 5th Wednesday meetup for the Atlanta bitcoin community.</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is about Bitcoin politics and community meetup, which triggers the automatic 1 rating regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Bitcoin Builders #10</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044359/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BitDevs: Bitcoin Socratic Seminar #55 - pre-TABConf</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044442/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Join the Atlanta BitDevs every third Wednesday for a Socratic Seminar to discuss the latest technological developments in Bitcoin and Lightning! Events are formatted to foster debate, information sharing and lively discussion.</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is focused on Bitcoin and Lightning Network technology discussions, making it an automatic 1 regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BitPlebs Bitcoin Meetup @ ATL BitLab</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE, Unit A1, Atlanta, GA 30312</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044426/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation - it is a Bitcoin meetup with no AI content, which is an automatic 1 regardless of location or in-person status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - June</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044572/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or in-person format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - June</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>46351</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>July 26, 2026</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>6:00 PM EST</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044573/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/events_master.xlsx
+++ b/events_master.xlsx
@@ -18,8 +18,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="mmmm d, yyyy"/>
+    <numFmt numFmtId="164" formatCode="mmmm d, yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -50,12 +50,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -133,7 +134,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K53" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K83" headerRowCount="1">
   <autoFilter ref="A1:K53"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -153,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K132" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K153" headerRowCount="1">
   <autoFilter ref="A1:K132"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -461,18 +462,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
@@ -548,7 +549,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="3" t="n">
         <v>46252</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -556,7 +557,6 @@
           <t>July 2, 2026</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Renaissance Atlanta Waverly Hotel &amp; Convention Center, 2450 Galleria Pkwy, Atlanta, GA 30339</t>
@@ -597,7 +597,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="3" t="n">
         <v>46249</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -650,7 +650,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="3" t="n">
         <v>46678</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -703,7 +703,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="3" t="n">
         <v>46234</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -752,7 +752,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="3" t="n">
         <v>46225</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -801,7 +801,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="3" t="n">
         <v>46215</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -850,7 +850,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="3" t="n">
         <v>46214</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -899,7 +899,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D9" s="3" t="n">
         <v>46218</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -948,7 +948,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="3" t="n">
         <v>46206</v>
       </c>
       <c r="E10" t="inlineStr">
@@ -997,7 +997,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D11" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="E11" t="inlineStr">
@@ -1046,7 +1046,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="3" t="n">
         <v>46239</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -1099,7 +1099,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D13" s="3" t="n">
         <v>46267</v>
       </c>
       <c r="E13" t="inlineStr">
@@ -1152,7 +1152,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="3" t="n">
         <v>46302</v>
       </c>
       <c r="E14" t="inlineStr">
@@ -1205,7 +1205,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D15" s="3" t="n">
         <v>46210</v>
       </c>
       <c r="E15" t="inlineStr">
@@ -1218,7 +1218,6 @@
           <t>12:30 PM - 1:00 PM</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -1254,7 +1253,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D16" s="3" t="n">
         <v>46238</v>
       </c>
       <c r="E16" t="inlineStr">
@@ -1267,7 +1266,6 @@
           <t>12:30 PM - 1:00 PM</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -1303,7 +1301,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D17" s="3" t="n">
         <v>46280</v>
       </c>
       <c r="E17" t="inlineStr">
@@ -1316,7 +1314,6 @@
           <t>10:00 AM - 3:00 PM</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -1348,7 +1345,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D18" s="3" t="n">
         <v>46216</v>
       </c>
       <c r="E18" t="inlineStr">
@@ -1397,7 +1394,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D19" s="3" t="n">
         <v>46279</v>
       </c>
       <c r="E19" t="inlineStr">
@@ -1450,7 +1447,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D20" s="3" t="n">
         <v>46496</v>
       </c>
       <c r="E20" t="inlineStr">
@@ -1503,7 +1500,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>August 18, 2026 - August 20, 2026</t>
         </is>
@@ -1513,8 +1510,6 @@
           <t>July 2, 2026</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>https://www.georgiamanufacturingalliance.com/events/ *</t>
@@ -1546,7 +1541,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>August 6-7, 2026</t>
         </is>
@@ -1561,7 +1556,6 @@
           <t>4:00 PM - 1:00 PM</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -1597,7 +1591,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D23" s="3" t="n">
         <v>46283</v>
       </c>
       <c r="E23" t="inlineStr">
@@ -1610,7 +1604,6 @@
           <t>8:00 AM - 3:00 PM</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -1646,7 +1639,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="D24" s="3" t="n">
         <v>46303</v>
       </c>
       <c r="E24" t="inlineStr">
@@ -1699,7 +1692,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D25" s="1" t="n">
+      <c r="D25" s="3" t="n">
         <v>46360</v>
       </c>
       <c r="E25" t="inlineStr">
@@ -1712,7 +1705,6 @@
           <t>9:00 AM - 3:00 PM</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -1748,7 +1740,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D26" s="3" t="n">
         <v>46219</v>
       </c>
       <c r="E26" t="inlineStr">
@@ -1797,7 +1789,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D27" s="1" t="n">
+      <c r="D27" s="3" t="n">
         <v>46214</v>
       </c>
       <c r="E27" t="inlineStr">
@@ -1846,7 +1838,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D28" s="1" t="n">
+      <c r="D28" s="3" t="n">
         <v>46205</v>
       </c>
       <c r="E28" t="inlineStr">
@@ -1895,7 +1887,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D29" s="3" t="n">
         <v>46211</v>
       </c>
       <c r="E29" t="inlineStr">
@@ -1944,7 +1936,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="D30" s="3" t="n">
         <v>46223</v>
       </c>
       <c r="E30" t="inlineStr">
@@ -1993,7 +1985,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D31" s="3" t="n">
         <v>46224</v>
       </c>
       <c r="E31" t="inlineStr">
@@ -2042,7 +2034,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D32" s="1" t="n">
+      <c r="D32" s="3" t="n">
         <v>46210</v>
       </c>
       <c r="E32" t="inlineStr">
@@ -2091,7 +2083,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D33" s="3" t="n">
         <v>46220</v>
       </c>
       <c r="E33" t="inlineStr">
@@ -2140,7 +2132,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="D34" s="3" t="n">
         <v>46217</v>
       </c>
       <c r="E34" t="inlineStr">
@@ -2193,7 +2185,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D35" s="1" t="n">
+      <c r="D35" s="3" t="n">
         <v>46232</v>
       </c>
       <c r="E35" t="inlineStr">
@@ -2206,7 +2198,6 @@
           <t>5:00 PM - 8:00 PM</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -2238,7 +2229,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D36" s="1" t="n">
+      <c r="D36" s="3" t="n">
         <v>46252</v>
       </c>
       <c r="E36" t="inlineStr">
@@ -2251,7 +2242,6 @@
           <t>8:00 AM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -2283,7 +2273,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D37" s="1" t="n">
+      <c r="D37" s="3" t="n">
         <v>46301</v>
       </c>
       <c r="E37" t="inlineStr">
@@ -2296,7 +2286,6 @@
           <t>12:30 PM - 1:00 PM</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -2328,7 +2317,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D38" s="1" t="n">
+      <c r="D38" s="3" t="n">
         <v>46331</v>
       </c>
       <c r="E38" t="inlineStr">
@@ -2341,7 +2330,6 @@
           <t>11:30 AM - 2:00 PM</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -2373,7 +2361,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D39" s="1" t="n">
+      <c r="D39" s="3" t="n">
         <v>46345</v>
       </c>
       <c r="E39" t="inlineStr">
@@ -2386,7 +2374,6 @@
           <t>6:00 PM - 11:00 PM</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -2418,7 +2405,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D40" s="1" t="n">
+      <c r="D40" s="3" t="n">
         <v>46212</v>
       </c>
       <c r="E40" t="inlineStr">
@@ -2467,7 +2454,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D41" s="1" t="n">
+      <c r="D41" s="3" t="n">
         <v>46227</v>
       </c>
       <c r="E41" t="inlineStr">
@@ -2516,7 +2503,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D42" s="1" t="n">
+      <c r="D42" s="3" t="n">
         <v>46205</v>
       </c>
       <c r="E42" t="inlineStr">
@@ -2565,7 +2552,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D43" s="1" t="n">
+      <c r="D43" s="3" t="n">
         <v>46205</v>
       </c>
       <c r="E43" t="inlineStr">
@@ -2614,7 +2601,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D44" s="1" t="n">
+      <c r="D44" s="3" t="n">
         <v>46214</v>
       </c>
       <c r="E44" t="inlineStr">
@@ -2663,7 +2650,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D45" s="1" t="n">
+      <c r="D45" s="3" t="n">
         <v>46205</v>
       </c>
       <c r="E45" t="inlineStr">
@@ -2712,7 +2699,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D46" s="1" t="n">
+      <c r="D46" s="3" t="n">
         <v>46215</v>
       </c>
       <c r="E46" t="inlineStr">
@@ -2761,7 +2748,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D47" s="1" t="n">
+      <c r="D47" s="3" t="n">
         <v>46205</v>
       </c>
       <c r="E47" t="inlineStr">
@@ -2810,7 +2797,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D48" s="1" t="n">
+      <c r="D48" s="3" t="n">
         <v>46211</v>
       </c>
       <c r="E48" t="inlineStr">
@@ -2823,7 +2810,6 @@
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>https://luma.com/genai-collective *</t>
@@ -2855,7 +2841,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D49" s="1" t="n">
+      <c r="D49" s="3" t="n">
         <v>46211</v>
       </c>
       <c r="E49" t="inlineStr">
@@ -2904,7 +2890,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D50" s="1" t="n">
+      <c r="D50" s="3" t="n">
         <v>46212</v>
       </c>
       <c r="E50" t="inlineStr">
@@ -2953,7 +2939,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D51" s="1" t="n">
+      <c r="D51" s="3" t="n">
         <v>46225</v>
       </c>
       <c r="E51" t="inlineStr">
@@ -3002,7 +2988,7 @@
           <t>low</t>
         </is>
       </c>
-      <c r="D52" s="1" t="n">
+      <c r="D52" s="3" t="n">
         <v>46239</v>
       </c>
       <c r="E52" t="inlineStr">
@@ -3051,7 +3037,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="D53" s="1" t="n">
+      <c r="D53" s="3" t="n">
         <v>46205</v>
       </c>
       <c r="E53" t="inlineStr">
@@ -3085,6 +3071,1390 @@
           <t>While the event is in-person in Atlanta, there is zero mention of AI, machine learning, or automation, which is an automatic disqualifier regardless of location.</t>
         </is>
       </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Tech AI Symposium and AI Career Fair</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>9:45 AM EDT</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Exhibition Hall (460 4th St NW, Atlanta, GA 30332)</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://ai.gatech.edu/event/tech-ai-symposium-and-ai-career-fair</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Georgia Tech's premier event connecting students, researchers, faculty, industry leaders, and employers to explore the future of artificial intelligence.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>In-person Georgia Tech AI event in Atlanta with clear AI focus, career fair component, and confirmed September 2026 date at a specific Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Cyber Resilience in the AI Era presented by TAG Cybersecurity &amp; Risk Management Society and TAG Data Science &amp; AI Society</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>5:30 PM - 7:30 PM</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/MwFNl0es8CeCg</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event with clear AI content (presented by TAG Data Science &amp; AI Society) and cybersecurity focus, hosted by a Georgia-focused organization (TAG), scoring well despite virtual format and missing description details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Rural AI Workforce Forum 2026</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>4:00 PM - 12:30 PM</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar/Details/rural-ai-workforce-forum-2026-1759715?sourceTypeId=Website</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Preparing rural communities for an AI-driven future.</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event with clear AI content hosted by TAG (a Georgia-based organization), but lacks specific details about format, speakers, and actual Georgia focus beyond the organizer's location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>From Forecasting to Demand Orchestration: How AI Is Redefining Supply Chain Planning presented by TAG Data Science &amp; AI Society and TAG Supply Chain, Logistics &amp; Manufacturing Society</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>5:30 PM - 7:30 PM</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/WqFgM07iaCJCE</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>You'll hear what's working now, what's still hard, and how companies across utilities, healthcare, financial services, retail, and CPG are using AI to move faster and smarter.</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event with strong AI content (demand orchestration, AI in supply chain planning) hosted by TAG (Atlanta-based organization), but lacks confirmed Georgia focus and location details lower the score from what an in-person version would achieve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AI Superpowers for Good: Solving Society's Biggest Challenges presented by TAG Data Science &amp; AI Society</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>5:00 PM - 7:45 PM</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/xRF50ZqHMCYC7</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>An inspiring evening showcasing complete, real-world data science and AI projects from concept to impact.</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event with clear AI content hosted by TAG (a Georgia-focused organization), but lacks specific location confirmation and detailed description that would elevate it higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>IBM Certificate (in-Person) Graduation</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>6:00 PM - 7:30 PM</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/EqFedRnCgC6C9</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>Join us for a special virtual celebration honoring the achievements of participants in the IBM SkillsBuild Program. This event recognizes learners from our recent cohorts who have dedicated their time and effort to building in-demand skills.</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Event has AI/tech content (IBM SkillsBuild) and is hosted by TAG (Georgia-focused org), but is a graduation ceremony celebrating past learning rather than an educational AI event itself, and location field is blank despite in-person claim creating ambiguity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Beyond Connected: IoT's Next Chapter presented by TAG Cloud Society</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>5:30 PM - 8:00 PM</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar/Details/beyond-connected-iot-s-next-chapter-presented-by-tag-cloud-society-1848946?sourceTypeId=Website</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>An executive panel exploring how leading organizations are transforming connected devices into intelligent, business-driven ecosystems.</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event hosted by TAG (Georgia-based organization) with AI/automation relevance through IoT and intelligent systems discussion, scoring 3-4 range for Georgia institution virtual content, but lacks explicit AI/ML terminology and location ambiguity slightly reduces confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Manufacturing Technology Challenges: Practical Solutions for Today's Pla...</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>11:00 AM - 1:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/tech-educational-panel</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>The event description is empty and the title gives no indication of AI, machine learning, or automation content, making it impossible to confirm AI relevance despite the Georgia-focused organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>AIMST 2026 Atlanta</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Renaissance Atlanta Waverly Hotel &amp; Convention Center, 2450 Galleria Pkwy, Atlanta, GA 30339</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.meetmax.com/sched/event_130973/conference_register.html?attendee_role_id=TWST2_ATTENDEE&amp;grp_name=ATTENDEE&amp;approved=Y&amp;_gl=1*g58gv2*_gcl_au*Mjc2MTM5ODY0LjE3ODEwMTU3MjQ.*_ga*MTYwNTkxMjEyNC4xNzU2MjA4NDM5*_ga_M7N3QCZSH0*czE3ODM5OTUzOTAkbzExNCRnMSR0MTc4Mzk5NjQ2NiRqMzkkbDAkaDA.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>North America's #1 Conference in Industrial AI, focused on providing in-depth discussions and solutions for heads of manufacturing, advanced technology managers, ICS, IT/OT, SCADA and cyber security professionals to accelerate their digital transformation and transform their operational and automation systems. Features three tech tracks (AI Manufacturing, Industrial AI 101 for SMEs, SCADA Technology &amp; AI Utilities), 60+ speakers, 350+ attendees, and 8+ networking events.</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>AIMST 2026 is an in-person industrial AI conference in Atlanta with substantial AI content (three AI-focused tech tracks, 60+ speakers, 350+ attendees), meeting all criteria for excellent fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TechConnect: Global Virtual Job &amp; Networking Event for Data, AI, and Tech Pros</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>4:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ac-atl/events/313188287/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-online&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only national job fair with AI content mentions, but lacks Georgia-specific focus and has no detailed description to confirm educational value versus recruitment pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Atlanta Tech Meet-Up</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atl-tech-meetup/events/315779247/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FREE REMOTE | LADIES IN AI - We Learn. We Share. We Laugh.</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>7:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ai-growth-circle/events/315016411/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-online&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with AI content (Ladies in AI community group) but no Georgia-specific focus and lacks detailed description to assess educational value beyond community gathering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Agentic AI Meetup - August</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>4</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>5:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/aittg-atlanta/events/315755582/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>In-person AI meetup (Agentic AI) hosted by Atlanta-based AITTG organization with strong AI content focus, but confidence is medium due to missing location details and empty description field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Bytes &amp; Bites: Atlanta Tech Week Edition @ Krog St Market</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>11:45 AM EDT</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Krog St Market</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/refactr-tech/events/315763802/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Atlanta location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Building an AI resume optimization tool with Matthew Christiansen: Session 2</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/google-developer-groups-gdg-atlanta/events/315294142/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-online&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event with AI/ML content (resume optimization tool) hosted by GDG Atlanta (Georgia-focused organization) scores above typical national corporate webinars, but lacks in-person presence and detailed description limits full assessment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AWS + HashiCorp Terraform DevOps GameDay</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlanta-aws-user-group/events/315805518/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Event lacks AI/ML/automation content in title and description (automatic 1 territory), but is in-person with Atlanta AWS user group affiliation which provides minimal uplift; however, the missing location field and empty description create significant ambiguity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>no_events</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Building Intelligent AI Agents with GraphRAG</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>9:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.co.uk/e/building-intelligent-ai-agents-with-graphrag-tickets-1992756563525?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Event has clear AI content (GraphRAG and intelligent agents) but is virtual-only with no indication of Georgia focus or Georgia institution involvement, and lacks sufficient details to determine if it's educational or sales-focused.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Those Time Drains and Money Leaks? AI Should Be Fixing That. Find Out How.</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>7:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/those-time-drains-and-money-leaks-ai-should-be-fixing-that-find-out-how-tickets-1995249007492?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Event has AI content in title but lacks description, location details, and Georgia focus; virtual-only format with vague sales-pitch-style title suggesting a promotional webinar rather than substantive educational content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Atlanta Tech Mixer and Social (Tech / AI / Data / IT) ✨</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Atlanta · Stats Brewpub</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/atlanta-tech-mixer-and-social-tech-ai-data-it-tickets-1987408339844?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>While this is an in-person Atlanta event with AI mentioned in the title, it appears to be a generic networking mixer rather than an educational AI event with substantive content, and the complete lack of description makes it difficult to assess the actual focus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Data Science with Phython Certification Training in Columbus, GA</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Columbus · Veterans Parkway</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/data-science-with-phython-certification-training-in-columbus-ga-tickets-1984660920238?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>While the event is in-person in Georgia (Columbus), it appears to be a paid certification training focused on Python/data science rather than an educational event about AI/ML concepts, and the empty description makes it difficult to assess actual AI content relevance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Everything but the Camera: ACS</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Atlanta · Atlanta Axis Experience Center</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/everything-but-the-camera-acs-tickets-1990888109930?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Wednesd.AI</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>4</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Atlanta · Atlanta Tech Village - Buckhead</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/wednesdai-tickets-1990814107587?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Atlanta with AI-focused title (Wednesd.AI) suggesting regular AI content, but lack of detailed description creates some uncertainty about the specific content and educational value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>AI for the real World: Week 4: Make a Talking Video with AI (HeyGen Part 1</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>4</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>East Point · 1928 Stanton Rd</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-for-the-real-world-week-4-make-a-talking-video-with-ai-heygen-part-1-tickets-1992736032115?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>In-person AI event in Georgia (East Point) with clear AI/automation content (video generation with HeyGen), though short description and part-of-series nature suggest it may be training-focused rather than purely educational.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Tech, AI &amp; Startups Roundtable Discussion Dinner</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Atlanta · Aviva by Kameel Buckhead</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/tech-ai-startups-roundtable-discussion-dinner-tickets-1988373794545?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Atlanta with explicit AI focus in the title, though the empty short description and roundtable dinner format (rather than technical content) prevent a higher score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>AI Awareness: The Good, the Bad, and What to Watch For</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-awareness-the-good-the-bad-and-what-to-watch-for-tickets-1991930436557?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Event clearly has AI content in its title, but is virtual-only with no Georgia focus mentioned, missing date/time/location details, and no description to assess whether it's educational or a sales pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Microsoft Copilot Cowork Masterclass</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>10:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.co.uk/e/microsoft-copilot-cowork-masterclass-tickets-1990549050795?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Event clearly mentions AI (Microsoft Copilot), but is virtual-only with no Georgia connection and appears to be a corporate training/sales pitch rather than educational content, and the empty short description limits confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>FREE Data Analytics with GenAI Bootcamp | USA Only |Join WhatsApp Group</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>10:30 AM EDT</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/free-data-analytics-with-genai-bootcamp-usa-only-join-whatsapp-group-tickets-1990886211251?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with clear AI/GenAI content but no Georgia focus, missing location details, and a bootcamp structure that suggests potential sales orientation rather than pure education.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>AI Tinkerers Atlanta: 2-Year Anniversary &amp; Best Demos of the Year</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>5</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://atlanta.aitinkerers.org/p/ai-tinkerers-atlanta-2-year-anniversary-best-demos-of-the-year</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>AI Tinkerers Atlanta will celebrate two years by showcasing impactful technical discoveries and working code. RenderATL Group will sponsor this community event.</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>In-person technical AI event in Atlanta celebrating community achievements with demos and code, combining Georgia location preference with strong AI content and educational value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" s="3" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>no_events</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3100,14 +4470,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
@@ -3187,7 +4557,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="3" t="n">
         <v>46211</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -3236,7 +4606,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="3" t="n">
         <v>46219</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -3285,7 +4655,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="3" t="n">
         <v>46219</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -3334,7 +4704,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="3" t="n">
         <v>46225</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -3347,7 +4717,6 @@
           <t>11:00 AM - 1:00 PM EDT</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>https://www.georgiamanufacturingalliance.com/events/ *</t>
@@ -3379,7 +4748,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -3428,7 +4797,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -3477,7 +4846,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="3" t="n">
         <v>46239</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -3490,7 +4859,6 @@
           <t>11:00 AM - 1:30 PM EDT</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>https://www.georgiamanufacturingalliance.com/events/ *</t>
@@ -3522,7 +4890,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D9" s="3" t="n">
         <v>46245</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -3535,7 +4903,6 @@
           <t>3:30 PM - 4:30 PM EDT</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>https://www.georgiamanufacturingalliance.com/events/ *</t>
@@ -3567,7 +4934,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="3" t="n">
         <v>46254</v>
       </c>
       <c r="E10" t="inlineStr">
@@ -3616,7 +4983,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D11" s="3" t="n">
         <v>46254</v>
       </c>
       <c r="E11" t="inlineStr">
@@ -3665,7 +5032,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="3" t="n">
         <v>46280</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -3714,7 +5081,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D13" s="3" t="n">
         <v>46209</v>
       </c>
       <c r="E13" t="inlineStr">
@@ -3727,7 +5094,6 @@
           <t>5:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -3763,7 +5129,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="3" t="n">
         <v>46212</v>
       </c>
       <c r="E14" t="inlineStr">
@@ -3776,7 +5142,6 @@
           <t>3:00 PM - 6:30 PM</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -3812,7 +5177,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D15" s="3" t="n">
         <v>46212</v>
       </c>
       <c r="E15" t="inlineStr">
@@ -3825,7 +5190,6 @@
           <t>6:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -3861,7 +5225,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D16" s="3" t="n">
         <v>46220</v>
       </c>
       <c r="E16" t="inlineStr">
@@ -3874,7 +5238,6 @@
           <t>10:00 AM - 3:00 PM</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -3906,7 +5269,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D17" s="3" t="n">
         <v>46224</v>
       </c>
       <c r="E17" t="inlineStr">
@@ -3919,7 +5282,6 @@
           <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -3955,7 +5317,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D18" s="3" t="n">
         <v>46231</v>
       </c>
       <c r="E18" t="inlineStr">
@@ -3968,7 +5330,6 @@
           <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -4004,7 +5365,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D19" s="3" t="n">
         <v>46237</v>
       </c>
       <c r="E19" t="inlineStr">
@@ -4017,7 +5378,6 @@
           <t>5:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -4053,7 +5413,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D20" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="E20" t="inlineStr">
@@ -4066,7 +5426,6 @@
           <t>12:30 PM - 1:00 PM</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -4098,7 +5457,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D21" s="3" t="n">
         <v>46279</v>
       </c>
       <c r="E21" t="inlineStr">
@@ -4111,7 +5470,6 @@
           <t>5:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -4147,7 +5505,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D22" s="3" t="n">
         <v>46300</v>
       </c>
       <c r="E22" t="inlineStr">
@@ -4160,7 +5518,6 @@
           <t>5:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -4196,7 +5553,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D23" s="3" t="n">
         <v>46317</v>
       </c>
       <c r="E23" t="inlineStr">
@@ -4209,7 +5566,6 @@
           <t>1:00 PM - 5:00 PM</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -4245,7 +5601,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="D24" s="3" t="n">
         <v>46328</v>
       </c>
       <c r="E24" t="inlineStr">
@@ -4258,7 +5614,6 @@
           <t>5:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -4294,7 +5649,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D25" s="1" t="n">
+      <c r="D25" s="3" t="n">
         <v>46329</v>
       </c>
       <c r="E25" t="inlineStr">
@@ -4307,7 +5662,6 @@
           <t>12:30 PM - 1:00 PM</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -4339,7 +5693,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D26" s="3" t="n">
         <v>46357</v>
       </c>
       <c r="E26" t="inlineStr">
@@ -4352,7 +5706,6 @@
           <t>12:30 PM - 1:00 PM</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -4384,7 +5737,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D27" s="1" t="n">
+      <c r="D27" s="3" t="n">
         <v>46363</v>
       </c>
       <c r="E27" t="inlineStr">
@@ -4397,7 +5750,6 @@
           <t>5:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar *</t>
@@ -4433,7 +5785,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D28" s="1" t="n">
+      <c r="D28" s="3" t="n">
         <v>46210</v>
       </c>
       <c r="E28" t="inlineStr">
@@ -4482,7 +5834,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D29" s="3" t="n">
         <v>46219</v>
       </c>
       <c r="E29" t="inlineStr">
@@ -4531,7 +5883,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="D30" s="3" t="n">
         <v>46217</v>
       </c>
       <c r="E30" t="inlineStr">
@@ -4580,7 +5932,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D31" s="3" t="n">
         <v>46212</v>
       </c>
       <c r="E31" t="inlineStr">
@@ -4629,7 +5981,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D32" s="1" t="n">
+      <c r="D32" s="3" t="n">
         <v>46216</v>
       </c>
       <c r="E32" t="inlineStr">
@@ -4678,7 +6030,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D33" s="3" t="n">
         <v>46211</v>
       </c>
       <c r="E33" t="inlineStr">
@@ -4727,7 +6079,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="D34" s="3" t="n">
         <v>46214</v>
       </c>
       <c r="E34" t="inlineStr">
@@ -4740,7 +6092,6 @@
           <t>10:30 AM EDT</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia *</t>
@@ -4772,7 +6123,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D35" s="1" t="n">
+      <c r="D35" s="3" t="n">
         <v>46232</v>
       </c>
       <c r="E35" t="inlineStr">
@@ -4821,7 +6172,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D36" s="1" t="n">
+      <c r="D36" s="3" t="n">
         <v>46206</v>
       </c>
       <c r="E36" t="inlineStr">
@@ -4870,7 +6221,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D37" s="1" t="n">
+      <c r="D37" s="3" t="n">
         <v>46231</v>
       </c>
       <c r="E37" t="inlineStr">
@@ -4919,7 +6270,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D38" s="1" t="n">
+      <c r="D38" s="3" t="n">
         <v>46228</v>
       </c>
       <c r="E38" t="inlineStr">
@@ -4932,7 +6283,6 @@
           <t>10:30 AM EDT</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>https://www.meetup.com/find/?source=EVENTS&amp;categoryId=546&amp;location=us--georgia *</t>
@@ -4964,7 +6314,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D39" s="1" t="n">
+      <c r="D39" s="3" t="n">
         <v>46218</v>
       </c>
       <c r="E39" t="inlineStr">
@@ -5013,7 +6363,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D40" s="1" t="n">
+      <c r="D40" s="3" t="n">
         <v>46205</v>
       </c>
       <c r="E40" t="inlineStr">
@@ -5062,7 +6412,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D41" s="1" t="n">
+      <c r="D41" s="3" t="n">
         <v>46224</v>
       </c>
       <c r="E41" t="inlineStr">
@@ -5111,7 +6461,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D42" s="1" t="n">
+      <c r="D42" s="3" t="n">
         <v>46217</v>
       </c>
       <c r="E42" t="inlineStr">
@@ -5160,7 +6510,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D43" s="1" t="n">
+      <c r="D43" s="3" t="n">
         <v>46218</v>
       </c>
       <c r="E43" t="inlineStr">
@@ -5209,7 +6559,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D44" s="1" t="n">
+      <c r="D44" s="3" t="n">
         <v>46225</v>
       </c>
       <c r="E44" t="inlineStr">
@@ -5258,7 +6608,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D45" s="1" t="n">
+      <c r="D45" s="3" t="n">
         <v>46228</v>
       </c>
       <c r="E45" t="inlineStr">
@@ -5307,7 +6657,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D46" s="1" t="n">
+      <c r="D46" s="3" t="n">
         <v>46219</v>
       </c>
       <c r="E46" t="inlineStr">
@@ -5356,7 +6706,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D47" s="1" t="n">
+      <c r="D47" s="3" t="n">
         <v>46232</v>
       </c>
       <c r="E47" t="inlineStr">
@@ -5405,7 +6755,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D48" s="1" t="n">
+      <c r="D48" s="3" t="n">
         <v>46206</v>
       </c>
       <c r="E48" t="inlineStr">
@@ -5454,7 +6804,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D49" s="1" t="n">
+      <c r="D49" s="3" t="n">
         <v>46207</v>
       </c>
       <c r="E49" t="inlineStr">
@@ -5503,7 +6853,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D50" s="1" t="n">
+      <c r="D50" s="3" t="n">
         <v>46207</v>
       </c>
       <c r="E50" t="inlineStr">
@@ -5552,7 +6902,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D51" s="1" t="n">
+      <c r="D51" s="3" t="n">
         <v>46207</v>
       </c>
       <c r="E51" t="inlineStr">
@@ -5601,7 +6951,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D52" s="1" t="n">
+      <c r="D52" s="3" t="n">
         <v>46209</v>
       </c>
       <c r="E52" t="inlineStr">
@@ -5650,7 +7000,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D53" s="1" t="n">
+      <c r="D53" s="3" t="n">
         <v>46210</v>
       </c>
       <c r="E53" t="inlineStr">
@@ -5699,7 +7049,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D54" s="1" t="n">
+      <c r="D54" s="3" t="n">
         <v>46210</v>
       </c>
       <c r="E54" t="inlineStr">
@@ -5748,7 +7098,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D55" s="1" t="n">
+      <c r="D55" s="3" t="n">
         <v>46210</v>
       </c>
       <c r="E55" t="inlineStr">
@@ -5797,7 +7147,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D56" s="1" t="n">
+      <c r="D56" s="3" t="n">
         <v>46211</v>
       </c>
       <c r="E56" t="inlineStr">
@@ -5846,7 +7196,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D57" s="1" t="n">
+      <c r="D57" s="3" t="n">
         <v>46211</v>
       </c>
       <c r="E57" t="inlineStr">
@@ -5895,7 +7245,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D58" s="1" t="n">
+      <c r="D58" s="3" t="n">
         <v>46212</v>
       </c>
       <c r="E58" t="inlineStr">
@@ -5944,7 +7294,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D59" s="1" t="n">
+      <c r="D59" s="3" t="n">
         <v>46212</v>
       </c>
       <c r="E59" t="inlineStr">
@@ -5993,7 +7343,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D60" s="1" t="n">
+      <c r="D60" s="3" t="n">
         <v>46213</v>
       </c>
       <c r="E60" t="inlineStr">
@@ -6042,7 +7392,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D61" s="1" t="n">
+      <c r="D61" s="3" t="n">
         <v>46214</v>
       </c>
       <c r="E61" t="inlineStr">
@@ -6091,7 +7441,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D62" s="1" t="n">
+      <c r="D62" s="3" t="n">
         <v>46214</v>
       </c>
       <c r="E62" t="inlineStr">
@@ -6140,7 +7490,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D63" s="1" t="n">
+      <c r="D63" s="3" t="n">
         <v>46218</v>
       </c>
       <c r="E63" t="inlineStr">
@@ -6189,7 +7539,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D64" s="1" t="n">
+      <c r="D64" s="3" t="n">
         <v>46219</v>
       </c>
       <c r="E64" t="inlineStr">
@@ -6238,7 +7588,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D65" s="1" t="n">
+      <c r="D65" s="3" t="n">
         <v>46219</v>
       </c>
       <c r="E65" t="inlineStr">
@@ -6287,7 +7637,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D66" s="1" t="n">
+      <c r="D66" s="3" t="n">
         <v>46220</v>
       </c>
       <c r="E66" t="inlineStr">
@@ -6336,7 +7686,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D67" s="1" t="n">
+      <c r="D67" s="3" t="n">
         <v>46224</v>
       </c>
       <c r="E67" t="inlineStr">
@@ -6385,7 +7735,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D68" s="1" t="n">
+      <c r="D68" s="3" t="n">
         <v>46224</v>
       </c>
       <c r="E68" t="inlineStr">
@@ -6434,7 +7784,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D69" s="1" t="n">
+      <c r="D69" s="3" t="n">
         <v>46224</v>
       </c>
       <c r="E69" t="inlineStr">
@@ -6483,7 +7833,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D70" s="1" t="n">
+      <c r="D70" s="3" t="n">
         <v>46225</v>
       </c>
       <c r="E70" t="inlineStr">
@@ -6532,7 +7882,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D71" s="1" t="n">
+      <c r="D71" s="3" t="n">
         <v>46227</v>
       </c>
       <c r="E71" t="inlineStr">
@@ -6581,7 +7931,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D72" s="1" t="n">
+      <c r="D72" s="3" t="n">
         <v>46231</v>
       </c>
       <c r="E72" t="inlineStr">
@@ -6630,7 +7980,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D73" s="1" t="n">
+      <c r="D73" s="3" t="n">
         <v>46231</v>
       </c>
       <c r="E73" t="inlineStr">
@@ -6679,7 +8029,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D74" s="1" t="n">
+      <c r="D74" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="E74" t="inlineStr">
@@ -6728,7 +8078,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D75" s="1" t="n">
+      <c r="D75" s="3" t="n">
         <v>46240</v>
       </c>
       <c r="E75" t="inlineStr">
@@ -6777,7 +8127,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D76" s="1" t="n">
+      <c r="D76" s="3" t="n">
         <v>46240</v>
       </c>
       <c r="E76" t="inlineStr">
@@ -6826,7 +8176,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D77" s="1" t="n">
+      <c r="D77" s="3" t="n">
         <v>46240</v>
       </c>
       <c r="E77" t="inlineStr">
@@ -6875,7 +8225,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D78" s="1" t="n">
+      <c r="D78" s="3" t="n">
         <v>46245</v>
       </c>
       <c r="E78" t="inlineStr">
@@ -6924,7 +8274,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D79" s="1" t="n">
+      <c r="D79" s="3" t="n">
         <v>46247</v>
       </c>
       <c r="E79" t="inlineStr">
@@ -6973,7 +8323,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D80" s="1" t="n">
+      <c r="D80" s="3" t="n">
         <v>46259</v>
       </c>
       <c r="E80" t="inlineStr">
@@ -7022,7 +8372,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D81" s="1" t="n">
+      <c r="D81" s="3" t="n">
         <v>46261</v>
       </c>
       <c r="E81" t="inlineStr">
@@ -7071,7 +8421,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D82" s="1" t="n">
+      <c r="D82" s="3" t="n">
         <v>46273</v>
       </c>
       <c r="E82" t="inlineStr">
@@ -7120,7 +8470,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D83" s="1" t="n">
+      <c r="D83" s="3" t="n">
         <v>46280</v>
       </c>
       <c r="E83" t="inlineStr">
@@ -7169,7 +8519,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D84" s="1" t="n">
+      <c r="D84" s="3" t="n">
         <v>46210</v>
       </c>
       <c r="E84" t="inlineStr">
@@ -7218,7 +8568,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D85" s="1" t="n">
+      <c r="D85" s="3" t="n">
         <v>46249</v>
       </c>
       <c r="E85" t="inlineStr">
@@ -7231,7 +8581,6 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>https://luma.com/genai-collective *</t>
@@ -7263,7 +8612,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D86" s="1" t="n">
+      <c r="D86" s="3" t="n">
         <v>46268</v>
       </c>
       <c r="E86" t="inlineStr">
@@ -7276,7 +8625,6 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>https://luma.com/genai-collective *</t>
@@ -7308,7 +8656,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D87" s="1" t="n">
+      <c r="D87" s="3" t="n">
         <v>46214</v>
       </c>
       <c r="E87" t="inlineStr">
@@ -7357,7 +8705,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D88" s="1" t="n">
+      <c r="D88" s="3" t="n">
         <v>46209</v>
       </c>
       <c r="E88" t="inlineStr">
@@ -7406,7 +8754,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D89" s="1" t="n">
+      <c r="D89" s="3" t="n">
         <v>46214</v>
       </c>
       <c r="E89" t="inlineStr">
@@ -7455,7 +8803,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D90" s="1" t="n">
+      <c r="D90" s="3" t="n">
         <v>46228</v>
       </c>
       <c r="E90" t="inlineStr">
@@ -7504,7 +8852,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D91" s="1" t="n">
+      <c r="D91" s="3" t="n">
         <v>46211</v>
       </c>
       <c r="E91" t="inlineStr">
@@ -7553,7 +8901,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D92" s="1" t="n">
+      <c r="D92" s="3" t="n">
         <v>46221</v>
       </c>
       <c r="E92" t="inlineStr">
@@ -7602,7 +8950,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D93" s="1" t="n">
+      <c r="D93" s="3" t="n">
         <v>46221</v>
       </c>
       <c r="E93" t="inlineStr">
@@ -7651,7 +8999,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D94" s="1" t="n">
+      <c r="D94" s="3" t="n">
         <v>46215</v>
       </c>
       <c r="E94" t="inlineStr">
@@ -7700,7 +9048,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D95" s="1" t="n">
+      <c r="D95" s="3" t="n">
         <v>46217</v>
       </c>
       <c r="E95" t="inlineStr">
@@ -7749,7 +9097,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D96" s="1" t="n">
+      <c r="D96" s="3" t="n">
         <v>46224</v>
       </c>
       <c r="E96" t="inlineStr">
@@ -7798,7 +9146,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D97" s="1" t="n">
+      <c r="D97" s="3" t="n">
         <v>46210</v>
       </c>
       <c r="E97" t="inlineStr">
@@ -7851,7 +9199,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D98" s="1" t="n">
+      <c r="D98" s="3" t="n">
         <v>46217</v>
       </c>
       <c r="E98" t="inlineStr">
@@ -7904,7 +9252,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D99" s="1" t="n">
+      <c r="D99" s="3" t="n">
         <v>46217</v>
       </c>
       <c r="E99" t="inlineStr">
@@ -7957,7 +9305,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D100" s="1" t="n">
+      <c r="D100" s="3" t="n">
         <v>46218</v>
       </c>
       <c r="E100" t="inlineStr">
@@ -8010,7 +9358,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D101" s="1" t="n">
+      <c r="D101" s="3" t="n">
         <v>46231</v>
       </c>
       <c r="E101" t="inlineStr">
@@ -8063,7 +9411,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D102" s="1" t="n">
+      <c r="D102" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="E102" t="inlineStr">
@@ -8116,7 +9464,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D103" s="1" t="n">
+      <c r="D103" s="3" t="n">
         <v>46239</v>
       </c>
       <c r="E103" t="inlineStr">
@@ -8169,7 +9517,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D104" s="1" t="n">
+      <c r="D104" s="3" t="n">
         <v>46240</v>
       </c>
       <c r="E104" t="inlineStr">
@@ -8222,7 +9570,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D105" s="1" t="n">
+      <c r="D105" s="3" t="n">
         <v>46244</v>
       </c>
       <c r="E105" t="inlineStr">
@@ -8275,7 +9623,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D106" s="1" t="n">
+      <c r="D106" s="3" t="n">
         <v>46252</v>
       </c>
       <c r="E106" t="inlineStr">
@@ -8328,7 +9676,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D107" s="1" t="n">
+      <c r="D107" s="3" t="n">
         <v>46254</v>
       </c>
       <c r="E107" t="inlineStr">
@@ -8381,7 +9729,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D108" s="1" t="n">
+      <c r="D108" s="3" t="n">
         <v>46268</v>
       </c>
       <c r="E108" t="inlineStr">
@@ -8434,7 +9782,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D109" s="1" t="n">
+      <c r="D109" s="3" t="n">
         <v>46280</v>
       </c>
       <c r="E109" t="inlineStr">
@@ -8487,7 +9835,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D110" s="1" t="n">
+      <c r="D110" s="3" t="n">
         <v>46282</v>
       </c>
       <c r="E110" t="inlineStr">
@@ -8540,7 +9888,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D111" s="1" t="n">
+      <c r="D111" s="3" t="n">
         <v>46289</v>
       </c>
       <c r="E111" t="inlineStr">
@@ -8593,7 +9941,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D112" s="1" t="n">
+      <c r="D112" s="3" t="n">
         <v>46296</v>
       </c>
       <c r="E112" t="inlineStr">
@@ -8646,7 +9994,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D113" s="1" t="n">
+      <c r="D113" s="3" t="n">
         <v>46302</v>
       </c>
       <c r="E113" t="inlineStr">
@@ -8699,7 +10047,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D114" s="1" t="n">
+      <c r="D114" s="3" t="n">
         <v>46310</v>
       </c>
       <c r="E114" t="inlineStr">
@@ -8752,7 +10100,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D115" s="1" t="n">
+      <c r="D115" s="3" t="n">
         <v>46315</v>
       </c>
       <c r="E115" t="inlineStr">
@@ -8805,7 +10153,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D116" s="1" t="n">
+      <c r="D116" s="3" t="n">
         <v>46336</v>
       </c>
       <c r="E116" t="inlineStr">
@@ -8858,7 +10206,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D117" s="1" t="n">
+      <c r="D117" s="3" t="n">
         <v>46338</v>
       </c>
       <c r="E117" t="inlineStr">
@@ -8911,7 +10259,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D118" s="1" t="n">
+      <c r="D118" s="3" t="n">
         <v>46364</v>
       </c>
       <c r="E118" t="inlineStr">
@@ -8964,7 +10312,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D119" s="1" t="n">
+      <c r="D119" s="3" t="n">
         <v>46239</v>
       </c>
       <c r="E119" t="inlineStr">
@@ -9017,7 +10365,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D120" s="1" t="n">
+      <c r="D120" s="3" t="n">
         <v>46246</v>
       </c>
       <c r="E120" t="inlineStr">
@@ -9070,7 +10418,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D121" s="1" t="n">
+      <c r="D121" s="3" t="n">
         <v>46253</v>
       </c>
       <c r="E121" t="inlineStr">
@@ -9123,7 +10471,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D122" s="1" t="n">
+      <c r="D122" s="3" t="n">
         <v>46260</v>
       </c>
       <c r="E122" t="inlineStr">
@@ -9176,7 +10524,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D123" s="1" t="n">
+      <c r="D123" s="3" t="n">
         <v>46267</v>
       </c>
       <c r="E123" t="inlineStr">
@@ -9229,7 +10577,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D124" s="1" t="n">
+      <c r="D124" s="3" t="n">
         <v>46274</v>
       </c>
       <c r="E124" t="inlineStr">
@@ -9282,7 +10630,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D125" s="1" t="n">
+      <c r="D125" s="3" t="n">
         <v>46281</v>
       </c>
       <c r="E125" t="inlineStr">
@@ -9335,7 +10683,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D126" s="1" t="n">
+      <c r="D126" s="3" t="n">
         <v>46288</v>
       </c>
       <c r="E126" t="inlineStr">
@@ -9388,7 +10736,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D127" s="1" t="n">
+      <c r="D127" s="3" t="n">
         <v>46295</v>
       </c>
       <c r="E127" t="inlineStr">
@@ -9441,7 +10789,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D128" s="1" t="n">
+      <c r="D128" s="3" t="n">
         <v>46302</v>
       </c>
       <c r="E128" t="inlineStr">
@@ -9494,7 +10842,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D129" s="1" t="n">
+      <c r="D129" s="3" t="n">
         <v>46306</v>
       </c>
       <c r="E129" t="inlineStr">
@@ -9547,7 +10895,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D130" s="1" t="n">
+      <c r="D130" s="3" t="n">
         <v>46316</v>
       </c>
       <c r="E130" t="inlineStr">
@@ -9600,7 +10948,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D131" s="1" t="n">
+      <c r="D131" s="3" t="n">
         <v>46323</v>
       </c>
       <c r="E131" t="inlineStr">
@@ -9653,7 +11001,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="D132" s="1" t="n">
+      <c r="D132" s="3" t="n">
         <v>46351</v>
       </c>
       <c r="E132" t="inlineStr">
@@ -9689,6 +11037,1015 @@
       <c r="K132" s="2" t="inlineStr">
         <is>
           <t>The event has zero mention of AI, machine learning, or automation, which is an automatic disqualification regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>IBM SkillsBuild Orientation</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>6:00 PM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar/Details/ibm-skillsbuild-orientation-1693369?sourceTypeId=Website</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>Join us for a mandatory virtual orientation to kick off the upcoming cohort. During this session, participants will receive an overview of the program structure, expectations, key dates, and demo on how to access the learning platform.</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>This is a generic orientation/onboarding session with zero mention of AI, machine learning, or automation in its own description, making it an automatic 1 regardless of the hosting organization or platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>TAG-Ed Pathways to Leadership Virtual Open House</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>6:00 PM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/qWFX016fkCQCe</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Join us for an inside look at the Pathways to Leadership program, a year-long leadership experience designed for emerging and mid-level professionals. Learn about the program's structure and benefits and hear from graduates.</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the first criterion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>** Canceled ** 2026 Georgia Day of Code</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>46360</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>9:00 AM - 3:00 PM</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar/Details/canceled-2026-georgia-day-of-code-1723691?sourceTypeId=Website</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>2026 Georgia Day of Code is a free, virtual event that introduces computer science and coding skills through engaging learning resources suitable for students of all ages and skill levels.</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>Event is canceled and has zero mention of AI, machine learning, or automation in its description, making it an automatic 1 per the primary criterion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Southeastern Hose - Bremen</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>1:30 PM - 4:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Bremen, Georgia</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/southeastern-hose---bremen</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, which is an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>PAi Manufacturing Facility Tour</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://www.aimanufacturingconference.com/ *</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>Get an inside look at one of Georgia's advanced manufacturing operations. The 120,000 sq. ft. production facility features 50 CNC machining centers and 32 industrial robots. Complimentary for AIMST attendees; advance registration required. Space is limited.</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>While the event is in-person in Georgia, it has zero mention of AI, machine learning, or automation in its title and description—it is purely a manufacturing facility tour with no AI content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>🎬 404 Movie Not Found: Spider-Man (Matinee)</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/refactr-tech/events/314126109/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation—it is a movie screening event, which triggers the automatic 1 rating regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>CISSP Certification Training Course in Bothell, CA</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Augusta · 22722 29th Dr SE West, Suite 100, Bothell, WA 98021</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/cissp-certification-training-course-in-bothell-ca-tickets-1980894231972?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Washington (WA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>The Cost of Bad UX – Based on Real Projects</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/the-cost-of-bad-ux-based-on-real-projects-tickets-1993809241112?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation, making it an automatic 1 per the criteria regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Business Analyst (CBAP) Classroom Training in Auburn, AL</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Columbus · 5547 Veterans Pkwy</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/business-analyst-cbap-classroom-training-in-auburn-al-tickets-1970898472386?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is a CBAP (Certified Business Analyst Professional) classroom training course, which is an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Business Analytics Certification (CBAP) Training in Augusta, GA</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Augusta · 823 Broad St</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/business-analytics-certification-cbap-training-in-augusta-ga-tickets-1970052557231?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description - it is a business analytics certification training focused on CBAP (Certified Business Analysis Professional) credential, which is an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Modern Data Architecture 2 Days Training in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/modern-data-architecture-2-days-training-in-atlanta-ga-tickets-1992366361420?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>The event title and short description contain zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of its in-person Atlanta location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>AWS Solution Architect Training | 4-Day Bootcamp in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Atlanta · 260 Peachtree St suite 2200</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/aws-solution-architect-training-4-day-bootcamp-in-atlanta-ga-tickets-1987119022488?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description - it is purely about AWS Solution Architect certification training, which is a paid training/sales pitch for AWS services rather than an educational AI event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Certified Ethical Hacker – Practical Ethical Hacker in Macon, GA</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Macon · 500a Northside Crossing</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/certified-ethical-hacker-practical-ethical-hacker-in-macon-ga-tickets-1986302519305?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description—it is a cybersecurity certification course, which is an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Stronger Communities Through Leadership Skills – 1 Day Training in Atlanta</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Atlanta · Regus - Atlanta - 260 Peachtree</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.sg/e/stronger-communities-through-leadership-skills-1-day-training-in-atlanta-tickets-1702814948349?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of its in-person Atlanta location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Georgia Tech ME 2110 Design Competition: Summer 2026</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Atlanta · Manufacturing Related Disciplines Complex (801 Ferst Dr, Atlanta, GA 30332)</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/georgia-tech-me-2110-design-competition-summer-2026-registration-1991920152798?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria regardless of its Georgia Tech in-person location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Naturalist Club: Backyard Habitats &amp; Common Feed Birds</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Kennesaw · North Cobb Regional Library</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/naturalist-club-backyard-habitats-common-feed-birds-tickets-1991154159692?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 per the criteria regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Naturalist Club: Backyard Habitats &amp; Common Feed Birds</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2:30 PM</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Marietta · East Cobb Library</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/naturalist-club-backyard-habitats-common-feed-birds-tickets-1991153844750?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or in-person status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Naturalist Club: Backyard Habitats &amp; Common Feed Birds</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2:30 PM</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Mableton · South Cobb Regional Library</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/naturalist-club-backyard-habitats-common-feed-birds-tickets-1991154120575?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is about naturalist club activities and bird watching, which triggers the automatic 1 rating regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Tech and Wealth Workshop</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>3:00 PM CDT</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.ca/e/tech-and-wealth-workshop-tickets-1995254351476?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering automatic score of 1 per the primary criterion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Bad UX in Numbers: Exploring Real Cases</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/bad-ux-in-numbers-exploring-real-cases-tickets-1993810735582?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation, making it an automatic 1 regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>HIGH-THC Medical Cannabis: A Scientific Breakdown</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>July 27, 2026</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>4:00 PM PDT</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.co.uk/e/high-thc-medical-cannabis-a-scientific-breakdown-tickets-1992308768157?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is about medical cannabis science, which automatically disqualifies it regardless of other criteria.</t>
         </is>
       </c>
     </row>

--- a/events_master.xlsx
+++ b/events_master.xlsx
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K83" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K90" headerRowCount="1">
   <autoFilter ref="A1:K53"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K153" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K160" headerRowCount="1">
   <autoFilter ref="A1:K132"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -462,18 +462,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
@@ -3152,7 +3152,6 @@
           <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/MwFNl0es8CeCg</t>
@@ -3197,7 +3196,6 @@
           <t>4:00 PM - 12:30 PM</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/rural-ai-workforce-forum-2026-1759715?sourceTypeId=Website</t>
@@ -3246,7 +3244,6 @@
           <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/WqFgM07iaCJCE</t>
@@ -3295,7 +3292,6 @@
           <t>5:00 PM - 7:45 PM</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/xRF50ZqHMCYC7</t>
@@ -3344,7 +3340,6 @@
           <t>6:00 PM - 7:30 PM</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/EqFedRnCgC6C9</t>
@@ -3393,7 +3388,6 @@
           <t>5:30 PM - 8:00 PM</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/beyond-connected-iot-s-next-chapter-presented-by-tag-cloud-society-1848946?sourceTypeId=Website</t>
@@ -3442,7 +3436,6 @@
           <t>11:00 AM - 1:30 PM EDT</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>https://www.georgiamanufacturingalliance.com/events/tech-educational-panel</t>
@@ -3482,7 +3475,6 @@
           <t>July 27, 2026</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>Renaissance Atlanta Waverly Hotel &amp; Convention Center, 2450 Galleria Pkwy, Atlanta, GA 30339</t>
@@ -3585,7 +3577,6 @@
           <t>6:00 PM EDT</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>https://www.meetup.com/atl-tech-meetup/events/315779247/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
@@ -3679,7 +3670,6 @@
           <t>5:30 PM EDT</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>https://www.meetup.com/aittg-atlanta/events/315755582/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
@@ -3822,7 +3812,6 @@
           <t>6:00 PM EDT</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>https://www.meetup.com/atlanta-aws-user-group/events/315805518/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
@@ -3846,17 +3835,12 @@
           <t>https://luma.com/genai-collective</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" s="3" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>July 27, 2026</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>no_events</t>
@@ -3892,7 +3876,6 @@
           <t>9:00 AM EDT</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>https://www.eventbrite.co.uk/e/building-intelligent-ai-agents-with-graphrag-tickets-1992756563525?aff=ebdssbdestsearch</t>
@@ -3937,7 +3920,6 @@
           <t>7:00 PM EDT</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/those-time-drains-and-money-leaks-ai-should-be-fixing-that-find-out-how-tickets-1995249007492?aff=ebdssbdestsearch</t>
@@ -4269,8 +4251,6 @@
           <t>July 27, 2026</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/ai-awareness-the-good-the-bad-and-what-to-watch-for-tickets-1991930436557?aff=ebdssbdestsearch</t>
@@ -4315,7 +4295,6 @@
           <t>10:00 AM EDT</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>https://www.eventbrite.co.uk/e/microsoft-copilot-cowork-masterclass-tickets-1990549050795?aff=ebdssbdestsearch</t>
@@ -4360,7 +4339,6 @@
           <t>10:30 AM EDT</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/free-data-analytics-with-genai-bootcamp-usa-only-join-whatsapp-group-tickets-1990886211251?aff=ebdssbdestsearch</t>
@@ -4437,17 +4415,12 @@
           <t>https://www.meetup.com/atlbitlab/events/</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" s="3" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>July 27, 2026</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>no_events</t>
@@ -4455,6 +4428,241 @@
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>AIMST - AI Conference - GMA Special Exhibitor and Moderator</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>4</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/aimst---ai-conference---gma-special-exhibitor-and-moderator</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>In-person AI conference hosted by Georgia Manufacturing Alliance with clear AI focus in title, though specific location within Georgia is missing and description details are sparse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>AnalyticsCLUB JobExpo Virtual Business, Data &amp; Technology Job Expo</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>11:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ac-atl/events/315736240/?recId=8c841573-99a7-4711-95a8-3825b47bc2b0&amp;recSource=ml-popular-events-nearby-online&amp;searchId=1950d877-d2cc-4cf2-979b-834f12b393b2&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Event has no mention of AI, machine learning, or automation in its title or available description, and while it's hosted by an Atlanta-area organization, the virtual format and lack of AI content trigger the automatic-1 rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>FREE REMOTE | LADIES IN AI + AI GROWTH CIRCLE (AN OPEN AI FORUM FOR ALL)</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>3</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>7:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ai-growth-circle/events/315016411/?recId=8c841573-99a7-4711-95a8-3825b47bc2b0&amp;recSource=ml-popular-events-nearby-online&amp;searchId=1950d877-d2cc-4cf2-979b-834f12b393b2&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with clear AI focus (Ladies in AI, AI Growth Circle) hosted by a Georgia-based meetup group, but lacks detailed description and is not in-person, limiting its score despite legitimate AI educational content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" s="3" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>no_events</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" s="3" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>failed: Failed to scrape page with Firecrawl: Rate Limit Exceeded: Failed to scrape. Rate limit exceeded. Consumed (req/min): 11, Remaining (req/min): 0. Upgrade your plan at https://firecrawl.dev/pricing for increased rate limits or please retry after 34s, resets at Mon Aug 03 2026 17:09:39 GMT+0000 (Coordinated Universal Time) - No additional error details provided.</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" s="3" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>no_events</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>https://ai.georgia.gov/events</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" s="3" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>failed: Failed to scrape page with Firecrawl: Rate Limit Exceeded: Failed to scrape. Rate limit exceeded. Consumed (req/min): 12, Remaining (req/min): 0. Upgrade your plan at https://firecrawl.dev/pricing for increased rate limits or please retry after 33s, resets at Mon Aug 03 2026 17:09:39 GMT+0000 (Coordinated Universal Time) - No additional error details provided.</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4470,14 +4678,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K153"/>
+  <dimension ref="A1:K160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
@@ -11067,7 +11275,6 @@
           <t>6:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/ibm-skillsbuild-orientation-1693369?sourceTypeId=Website</t>
@@ -11116,7 +11323,6 @@
           <t>6:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/qWFX016fkCQCe</t>
@@ -11165,7 +11371,6 @@
           <t>9:00 AM - 3:00 PM</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/canceled-2026-georgia-day-of-code-1723691?sourceTypeId=Website</t>
@@ -11258,7 +11463,6 @@
           <t>July 27, 2026</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>Georgia</t>
@@ -11312,7 +11516,6 @@
           <t>2:30 PM EDT</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>https://www.meetup.com/refactr-tech/events/314126109/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
@@ -11406,7 +11609,6 @@
           <t>12:00 PM EDT</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/the-cost-of-bad-ux-based-on-real-projects-tickets-1993809241112?aff=ebdssbdestsearch</t>
@@ -11941,7 +12143,6 @@
           <t>3:00 PM CDT</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
           <t>https://www.eventbrite.ca/e/tech-and-wealth-workshop-tickets-1995254351476?aff=ebdssbdestsearch</t>
@@ -11986,7 +12187,6 @@
           <t>2:00 PM EDT</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/bad-ux-in-numbers-exploring-real-cases-tickets-1993810735582?aff=ebdssbdestsearch</t>
@@ -12031,7 +12231,6 @@
           <t>4:00 PM PDT</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>https://www.eventbrite.co.uk/e/high-thc-medical-cannabis-a-scientific-breakdown-tickets-1992308768157?aff=ebdssbdestsearch</t>
@@ -12046,6 +12245,353 @@
       <c r="K153" s="2" t="inlineStr">
         <is>
           <t>Event has zero mention of AI, machine learning, or automation - it is about medical cannabis science, which automatically disqualifies it regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>IBM SkillsBuild Orientation</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>6:00 PM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar/Details/ibm-skillsbuild-orientation-1693369?sourceTypeId=Website</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>Join us for a mandatory virtual orientation to kick off the upcoming cohort. During this session, participants will receive an overview of the program structure, expectations, key dates, and a demo on how to access the learning platform.</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic-1 rule; it is a generic program orientation with no AI-focused component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Find a Startup to Help or Join</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>1:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/projects-for-developers-cs-majors-and-ux-designers/events/315933865/?recId=8c841573-99a7-4711-95a8-3825b47bc2b0&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=1950d877-d2cc-4cf2-979b-834f12b393b2&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or available description, triggering the automatic-1 rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Nostr Atlanta #15 - Rush Hour Avoidance</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315762247/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>Join us for Nostr Atlanta! Calling all nostr users, content creators, enthusiasts, developers, and more! This session will involve some tool building to avoid rush hour traffic. Informal round-table discussion of Nostr and adjacent topics from 4:30–6:00 PM.</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description—it focuses on Nostr (a decentralized social network protocol) and traffic avoidance, triggering the automatic-1 rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - June</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Manuels Tavern, 602 North Highland Ave NE, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044570/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>Join us at Manuel's Tavern for another fun BitPlebs meetup. Casual events geared towards helping you learn about how to get bitcoin, use bitcoin, and understand where it fits into current events. Arrive early for some free beverages. Agenda includes kick-off, community announcements, a presentation, and a beer social.</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description—it is exclusively about Bitcoin and cryptocurrency education, triggering the automatic-1 rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - June</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044571/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location or in-person status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - June</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044572/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or in-person status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - June</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>46351</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>6:00 PM EST</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044573/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location or format.</t>
         </is>
       </c>
     </row>

--- a/events_master.xlsx
+++ b/events_master.xlsx
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K90" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K83" headerRowCount="1">
   <autoFilter ref="A1:K53"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K160" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K153" headerRowCount="1">
   <autoFilter ref="A1:K132"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -462,18 +462,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
@@ -3152,6 +3152,7 @@
           <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/MwFNl0es8CeCg</t>
@@ -3196,6 +3197,7 @@
           <t>4:00 PM - 12:30 PM</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/rural-ai-workforce-forum-2026-1759715?sourceTypeId=Website</t>
@@ -3244,6 +3246,7 @@
           <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/WqFgM07iaCJCE</t>
@@ -3292,6 +3295,7 @@
           <t>5:00 PM - 7:45 PM</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/xRF50ZqHMCYC7</t>
@@ -3340,6 +3344,7 @@
           <t>6:00 PM - 7:30 PM</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/EqFedRnCgC6C9</t>
@@ -3388,6 +3393,7 @@
           <t>5:30 PM - 8:00 PM</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/beyond-connected-iot-s-next-chapter-presented-by-tag-cloud-society-1848946?sourceTypeId=Website</t>
@@ -3436,6 +3442,7 @@
           <t>11:00 AM - 1:30 PM EDT</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>https://www.georgiamanufacturingalliance.com/events/tech-educational-panel</t>
@@ -3475,6 +3482,7 @@
           <t>July 27, 2026</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>Renaissance Atlanta Waverly Hotel &amp; Convention Center, 2450 Galleria Pkwy, Atlanta, GA 30339</t>
@@ -3577,6 +3585,7 @@
           <t>6:00 PM EDT</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>https://www.meetup.com/atl-tech-meetup/events/315779247/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
@@ -3670,6 +3679,7 @@
           <t>5:30 PM EDT</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>https://www.meetup.com/aittg-atlanta/events/315755582/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
@@ -3812,6 +3822,7 @@
           <t>6:00 PM EDT</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>https://www.meetup.com/atlanta-aws-user-group/events/315805518/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
@@ -3835,12 +3846,17 @@
           <t>https://luma.com/genai-collective</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" s="3" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>July 27, 2026</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>no_events</t>
@@ -3876,6 +3892,7 @@
           <t>9:00 AM EDT</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>https://www.eventbrite.co.uk/e/building-intelligent-ai-agents-with-graphrag-tickets-1992756563525?aff=ebdssbdestsearch</t>
@@ -3920,6 +3937,7 @@
           <t>7:00 PM EDT</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/those-time-drains-and-money-leaks-ai-should-be-fixing-that-find-out-how-tickets-1995249007492?aff=ebdssbdestsearch</t>
@@ -4251,6 +4269,8 @@
           <t>July 27, 2026</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/ai-awareness-the-good-the-bad-and-what-to-watch-for-tickets-1991930436557?aff=ebdssbdestsearch</t>
@@ -4295,6 +4315,7 @@
           <t>10:00 AM EDT</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>https://www.eventbrite.co.uk/e/microsoft-copilot-cowork-masterclass-tickets-1990549050795?aff=ebdssbdestsearch</t>
@@ -4339,6 +4360,7 @@
           <t>10:30 AM EDT</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/free-data-analytics-with-genai-bootcamp-usa-only-join-whatsapp-group-tickets-1990886211251?aff=ebdssbdestsearch</t>
@@ -4415,12 +4437,17 @@
           <t>https://www.meetup.com/atlbitlab/events/</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" s="3" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>July 27, 2026</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>no_events</t>
@@ -4428,241 +4455,6 @@
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>AIMST - AI Conference - GMA Special Exhibitor and Moderator</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>4</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="n">
-        <v>46252</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>August 3, 2026</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>https://www.georgiamanufacturingalliance.com/events/aimst---ai-conference---gma-special-exhibitor-and-moderator</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>In-person AI conference hosted by Georgia Manufacturing Alliance with clear AI focus in title, though specific location within Georgia is missing and description details are sparse.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>AnalyticsCLUB JobExpo Virtual Business, Data &amp; Technology Job Expo</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="n">
-        <v>46241</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>August 3, 2026</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>11:00 AM EDT</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/ac-atl/events/315736240/?recId=8c841573-99a7-4711-95a8-3825b47bc2b0&amp;recSource=ml-popular-events-nearby-online&amp;searchId=1950d877-d2cc-4cf2-979b-834f12b393b2&amp;eventOrigin=find_page%24all</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr"/>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>Event has no mention of AI, machine learning, or automation in its title or available description, and while it's hosted by an Atlanta-area organization, the virtual format and lack of AI content trigger the automatic-1 rule.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>FREE REMOTE | LADIES IN AI + AI GROWTH CIRCLE (AN OPEN AI FORUM FOR ALL)</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>3</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="n">
-        <v>46240</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>August 3, 2026</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>7:00 PM EDT</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/ai-growth-circle/events/315016411/?recId=8c841573-99a7-4711-95a8-3825b47bc2b0&amp;recSource=ml-popular-events-nearby-online&amp;searchId=1950d877-d2cc-4cf2-979b-834f12b393b2&amp;eventOrigin=find_page%24all</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>Virtual-only event with clear AI focus (Ladies in AI, AI Growth Circle) hosted by a Georgia-based meetup group, but lacks detailed description and is not in-person, limiting its score despite legitimate AI educational content.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>https://luma.com/genai-collective</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" s="3" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>August 3, 2026</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>no_events</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr"/>
-      <c r="K87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" s="3" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>August 3, 2026</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>failed: Failed to scrape page with Firecrawl: Rate Limit Exceeded: Failed to scrape. Rate limit exceeded. Consumed (req/min): 11, Remaining (req/min): 0. Upgrade your plan at https://firecrawl.dev/pricing for increased rate limits or please retry after 34s, resets at Mon Aug 03 2026 17:09:39 GMT+0000 (Coordinated Universal Time) - No additional error details provided.</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>https://atlanta.aitinkerers.org/</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" s="3" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>August 3, 2026</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>no_events</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>https://ai.georgia.gov/events</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" s="3" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>August 3, 2026</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>failed: Failed to scrape page with Firecrawl: Rate Limit Exceeded: Failed to scrape. Rate limit exceeded. Consumed (req/min): 12, Remaining (req/min): 0. Upgrade your plan at https://firecrawl.dev/pricing for increased rate limits or please retry after 33s, resets at Mon Aug 03 2026 17:09:39 GMT+0000 (Coordinated Universal Time) - No additional error details provided.</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4678,14 +4470,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K160"/>
+  <dimension ref="A1:K153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
@@ -11275,6 +11067,7 @@
           <t>6:00 PM - 7:00 PM</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/ibm-skillsbuild-orientation-1693369?sourceTypeId=Website</t>
@@ -11323,6 +11116,7 @@
           <t>6:00 PM - 7:00 PM</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/qWFX016fkCQCe</t>
@@ -11371,6 +11165,7 @@
           <t>9:00 AM - 3:00 PM</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/canceled-2026-georgia-day-of-code-1723691?sourceTypeId=Website</t>
@@ -11463,6 +11258,7 @@
           <t>July 27, 2026</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>Georgia</t>
@@ -11516,6 +11312,7 @@
           <t>2:30 PM EDT</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>https://www.meetup.com/refactr-tech/events/314126109/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
@@ -11609,6 +11406,7 @@
           <t>12:00 PM EDT</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/the-cost-of-bad-ux-based-on-real-projects-tickets-1993809241112?aff=ebdssbdestsearch</t>
@@ -12143,6 +11941,7 @@
           <t>3:00 PM CDT</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
           <t>https://www.eventbrite.ca/e/tech-and-wealth-workshop-tickets-1995254351476?aff=ebdssbdestsearch</t>
@@ -12187,6 +11986,7 @@
           <t>2:00 PM EDT</t>
         </is>
       </c>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/bad-ux-in-numbers-exploring-real-cases-tickets-1993810735582?aff=ebdssbdestsearch</t>
@@ -12231,6 +12031,7 @@
           <t>4:00 PM PDT</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>https://www.eventbrite.co.uk/e/high-thc-medical-cannabis-a-scientific-breakdown-tickets-1992308768157?aff=ebdssbdestsearch</t>
@@ -12245,353 +12046,6 @@
       <c r="K153" s="2" t="inlineStr">
         <is>
           <t>Event has zero mention of AI, machine learning, or automation - it is about medical cannabis science, which automatically disqualifies it regardless of other criteria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>IBM SkillsBuild Orientation</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>1</v>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>August 3, 2026</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>6:00 PM - 7:00 PM</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>https://members.tagonline.org/calendar/Details/ibm-skillsbuild-orientation-1693369?sourceTypeId=Website</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>Join us for a mandatory virtual orientation to kick off the upcoming cohort. During this session, participants will receive an overview of the program structure, expectations, key dates, and a demo on how to access the learning platform.</t>
-        </is>
-      </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic-1 rule; it is a generic program orientation with no AI-focused component.</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Find a Startup to Help or Join</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>1</v>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D155" s="3" t="n">
-        <v>46243</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>August 3, 2026</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>1:30 PM EDT</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/projects-for-developers-cs-majors-and-ux-designers/events/315933865/?recId=8c841573-99a7-4711-95a8-3825b47bc2b0&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=1950d877-d2cc-4cf2-979b-834f12b393b2&amp;eventOrigin=find_page%24all</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J155" s="2" t="inlineStr"/>
-      <c r="K155" s="2" t="inlineStr">
-        <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or available description, triggering the automatic-1 rule.</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Nostr Atlanta #15 - Rush Hour Avoidance</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>1</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D156" s="3" t="n">
-        <v>46253</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>August 3, 2026</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>4:30 PM EDT</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA, US</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/atlbitlab/events/315762247/?eventOrigin=group_events_list</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="inlineStr">
-        <is>
-          <t>Join us for Nostr Atlanta! Calling all nostr users, content creators, enthusiasts, developers, and more! This session will involve some tool building to avoid rush hour traffic. Informal round-table discussion of Nostr and adjacent topics from 4:30–6:00 PM.</t>
-        </is>
-      </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description—it focuses on Nostr (a decentralized social network protocol) and traffic avoidance, triggering the automatic-1 rule.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - June</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>1</v>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>August 3, 2026</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>6:00 PM EDT</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Manuels Tavern, 602 North Highland Ave NE, Atlanta, GA, US</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/atlbitlab/events/315044570/?eventOrigin=group_events_list</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>Join us at Manuel's Tavern for another fun BitPlebs meetup. Casual events geared towards helping you learn about how to get bitcoin, use bitcoin, and understand where it fits into current events. Arrive early for some free beverages. Agenda includes kick-off, community announcements, a presentation, and a beer social.</t>
-        </is>
-      </c>
-      <c r="K157" s="2" t="inlineStr">
-        <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description—it is exclusively about Bitcoin and cryptocurrency education, triggering the automatic-1 rule.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - June</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>1</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D158" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>August 3, 2026</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>6:00 PM EDT</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/atlbitlab/events/315044571/?eventOrigin=group_events_list</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="inlineStr"/>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location or in-person status.</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - June</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>1</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D159" s="3" t="n">
-        <v>46323</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>August 3, 2026</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>6:00 PM EDT</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/atlbitlab/events/315044572/?eventOrigin=group_events_list</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="inlineStr"/>
-      <c r="K159" s="2" t="inlineStr">
-        <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or in-person status.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - June</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>1</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D160" s="3" t="n">
-        <v>46351</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>August 3, 2026</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>6:00 PM EST</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/atlbitlab/events/315044573/?eventOrigin=group_events_list</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="inlineStr"/>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location or format.</t>
         </is>
       </c>
     </row>

--- a/events_master.xlsx
+++ b/events_master.xlsx
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K83" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K118" headerRowCount="1">
   <autoFilter ref="A1:K53"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K153" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K204" headerRowCount="1">
   <autoFilter ref="A1:K132"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -462,14 +462,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
@@ -3152,7 +3152,6 @@
           <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/MwFNl0es8CeCg</t>
@@ -3197,7 +3196,6 @@
           <t>4:00 PM - 12:30 PM</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/rural-ai-workforce-forum-2026-1759715?sourceTypeId=Website</t>
@@ -3246,7 +3244,6 @@
           <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/WqFgM07iaCJCE</t>
@@ -3295,7 +3292,6 @@
           <t>5:00 PM - 7:45 PM</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/xRF50ZqHMCYC7</t>
@@ -3344,7 +3340,6 @@
           <t>6:00 PM - 7:30 PM</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/EqFedRnCgC6C9</t>
@@ -3393,7 +3388,6 @@
           <t>5:30 PM - 8:00 PM</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/beyond-connected-iot-s-next-chapter-presented-by-tag-cloud-society-1848946?sourceTypeId=Website</t>
@@ -3442,7 +3436,6 @@
           <t>11:00 AM - 1:30 PM EDT</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>https://www.georgiamanufacturingalliance.com/events/tech-educational-panel</t>
@@ -3482,7 +3475,6 @@
           <t>July 27, 2026</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>Renaissance Atlanta Waverly Hotel &amp; Convention Center, 2450 Galleria Pkwy, Atlanta, GA 30339</t>
@@ -3585,7 +3577,6 @@
           <t>6:00 PM EDT</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>https://www.meetup.com/atl-tech-meetup/events/315779247/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
@@ -3679,7 +3670,6 @@
           <t>5:30 PM EDT</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>https://www.meetup.com/aittg-atlanta/events/315755582/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
@@ -3822,7 +3812,6 @@
           <t>6:00 PM EDT</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>https://www.meetup.com/atlanta-aws-user-group/events/315805518/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
@@ -3846,17 +3835,12 @@
           <t>https://luma.com/genai-collective</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" s="3" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>July 27, 2026</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>no_events</t>
@@ -3892,7 +3876,6 @@
           <t>9:00 AM EDT</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>https://www.eventbrite.co.uk/e/building-intelligent-ai-agents-with-graphrag-tickets-1992756563525?aff=ebdssbdestsearch</t>
@@ -3937,7 +3920,6 @@
           <t>7:00 PM EDT</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/those-time-drains-and-money-leaks-ai-should-be-fixing-that-find-out-how-tickets-1995249007492?aff=ebdssbdestsearch</t>
@@ -4269,8 +4251,6 @@
           <t>July 27, 2026</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/ai-awareness-the-good-the-bad-and-what-to-watch-for-tickets-1991930436557?aff=ebdssbdestsearch</t>
@@ -4315,7 +4295,6 @@
           <t>10:00 AM EDT</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>https://www.eventbrite.co.uk/e/microsoft-copilot-cowork-masterclass-tickets-1990549050795?aff=ebdssbdestsearch</t>
@@ -4360,7 +4339,6 @@
           <t>10:30 AM EDT</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/free-data-analytics-with-genai-bootcamp-usa-only-join-whatsapp-group-tickets-1990886211251?aff=ebdssbdestsearch</t>
@@ -4437,17 +4415,12 @@
           <t>https://www.meetup.com/atlbitlab/events/</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" s="3" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>July 27, 2026</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>no_events</t>
@@ -4455,6 +4428,1619 @@
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Meet Atlanta Tech Week &amp; RenderATL Speakers! (REGISTER ON LUMA)</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>6:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/modernwebatl/events/315488146/?recId=c9fa2fcb-2337-495c-ac93-1d91a25e8b54&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=0500200c-b3c2-429f-8698-91ed31868873&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, and the extremely sparse details (missing location, empty description) prevent assessment of any potential AI-focused component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Open House!</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>7:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/freeside-atlanta/events/315410843/?recId=c9fa2fcb-2337-495c-ac93-1d91a25e8b54&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=0500200c-b3c2-429f-8698-91ed31868873&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Event has no description or title content indicating AI, machine learning, or automation relevance, and the generic 'Open House!' title provides no basis for scoring on AI content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" s="3" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>no_events</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Tech and Wealth Workshop</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2:00 PM CDT</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.ca/e/tech-and-wealth-workshop-tickets-1996426857473?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule; additionally, it is virtual-only with no Georgia organizational tie and no substantive content details provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>InsurTech Atlanta AI at Scale</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>4</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Atlanta · Serendipity Labs - Buckhead Atlanta</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/insurtech-atlanta-ai-at-scale-tickets-1991541855300?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with explicit AI focus in title, but scoring is limited by missing event description and inability to assess whether it's educational content or primarily a sales pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>The Creator Experience</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Atlanta · Omnia Room</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/the-creator-experience-tickets-1994282269954?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Event has no mention of AI, machine learning, or automation in its title or short description, triggering the automatic-1 rule, though low confidence due to completely blank short description that may contain relevant details not provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Women + Tech Meetup</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Atlanta · Atlanta Tech Village</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/women-tech-meetup-tickets-1979762040557?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating despite being an in-person Atlanta event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Strategic Prompt Design for AI 1 Day Training in Marietta, GA</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>2</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Marietta, GA</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/strategic-prompt-design-for-ai-1-day-training-in-marietta-ga-tickets-1992104255454?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>While this is an in-person event in Georgia with clear AI content (prompt design), it appears to be a paid training course that functions primarily as a sales/service offering rather than an educational conference or community discussion, and the lack of description limits assessment of its depth and value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Modern Data Architecture 2 Days Training in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/modern-data-architecture-2-days-training-in-atlanta-ga-tickets-1992366361420?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule despite being in-person in Atlanta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AI-Augmented Leadership: 1-Day Executive Training | Atlanta (GA)</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>2</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.sg/e/ai-augmented-leadership-1-day-executive-training-atlanta-ga-tickets-1993104016767?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>While the event is in-person in Atlanta with an AI focus in the title, the complete absence of a substantive description makes it impossible to assess whether this is a genuine educational AI event or primarily a paid training/sales pitch, and the Eventbrite.sg domain suggests it may be a commercial offering rather than a community-focused educational event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Tech and Wealth Workshop</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>3:00 PM CDT</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.ca/e/tech-and-wealth-workshop-tickets-1996426541528?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Event has no mention of AI, machine learning, or automation in its title or description, and the vague 'Tech and Wealth Workshop' framing combined with missing description makes it impossible to determine if there is any genuine AI-focused component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Machine Learning for Trading in the Age of AI Agents</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>9:30 AM EDT</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.co.uk/e/machine-learning-for-trading-in-the-age-of-ai-agents-tickets-1994299755253?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with no Georgia tie, no location information, empty description, and Eventbrite UK domain suggest a national/international webinar with no clear Georgia connection or educational value beyond the title.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AI Learning Series: Part 2: AI for Reading, Research &amp; Documents</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>4</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Atlanta · Vinings Library</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-learning-series-part-2-ai-for-reading-research-documents-tickets-1991015144895?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>In-person educational AI event in Atlanta with clear AI focus (AI applications for reading/research/documents), though held in metro Atlanta rather than outside it, and lack of detailed description limits confidence slightly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>To Infinity &amp; Beyond Bootcamp</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>10:15 AM</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Decatur · 50 Sports Company</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/to-infinity-beyond-bootcamp-tickets-1993874925576?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Event has no mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating despite being in-person in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Everything but the Camera: Access Control</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Atlanta · Atlanta Axis Experience Center</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/everything-but-the-camera-access-control-tickets-1990878774006?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain no mention of AI, machine learning, or automation, triggering the automatic 1 score regardless of location or in-person format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Data Science with Phython Certification Training in Macon, GA</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Macon · 500a Northside Crossing</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/data-science-with-phython-certification-training-in-macon-ga-tickets-1984755149079?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>While the event is in-person in Macon (outside Atlanta, which is good) and mentions data science/Python which relates to AI/ML fundamentals, it appears to be a paid certification training program with no description provided, suggesting it may be a heavy-handed sales pitch rather than an educational discussion event, and the lack of detail limits confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Become a Data Science Pro: 4-Day Python Weekend Bootcamp in Augusta, GA</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>3</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Augusta, GA</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/become-a-data-science-pro-4-day-python-weekend-bootcamp-in-augusta-ga-tickets-1985473975107?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>In-person data science bootcamp in Augusta (outside metro Atlanta) with AI/ML relevance, but appears to be paid training with a sales-pitch orientation and lacks detailed description to fully assess educational value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Atlanta Tech Mixer and Social (Tech / AI / Data / IT) ✨</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>3</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Atlanta · Stats Brewpub</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/atlanta-tech-mixer-and-social-tech-ai-data-it-tickets-1987408339844?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with AI mentioned in title, but lacks substantive description of actual AI content, making it appear to be primarily a social mixer rather than an educational or technical AI event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Become a Data Science Pro: 4-Day Python Weekend Bootcamp Sandy Springs, GA</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>2</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Atlanta · One Glenlake Pkwy NE</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/become-a-data-science-pro-4-day-python-weekend-bootcamp-sandy-springs-ga-tickets-1985563025459?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>While the event is in-person in the Atlanta area and involves data science/Python which relates to AI/ML skills, it appears to be a paid bootcamp with no description provided, making it difficult to assess whether it has genuine AI/ML educational content or is primarily a sales-focused training pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>4-Day Data Science with Python Bootcamp in Athens, GA</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>2</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Athens · 2470 Daniells Bridge Rd</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/4-day-data-science-with-python-bootcamp-in-athens-ga-tickets-1985351625155?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>While the event is in-person in Athens (outside Atlanta) and involves data science/Python which relates to AI/ML, the lack of description makes it impossible to determine if it's a genuine educational conference or a heavy-handed paid training/sales pitch, and the bootcamp format suggests it may be the latter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Build Executive-Ready Excel Reports with Microsoft Copilot</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>10:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.co.uk/e/build-executive-ready-excel-reports-with-microsoft-copilot-tickets-1994204467244?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>The event has a genuine AI component (Microsoft Copilot) but is virtual-only with no Georgia tie, and appears to be a paid training focused on a specific tool rather than educational discussion of AI concepts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Master AI Fundamentals: Free Hands-On Workshop (Peachtree Corners) Norcross</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>4</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Norcross · Irie Mon Cafe and Cocktails Peachtree Corners</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/master-ai-fundamentals-free-hands-on-workshop-peachtree-corners-norcross-tickets-1995698548080?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>In-person AI fundamentals workshop in Norcross (Georgia metro area) with free admission and hands-on educational focus, though confidence is tempered by missing detailed description and unknown organizer credibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Part 2: Make Sense of Information: AI for Reading, Research &amp; Documents</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>2</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/part-2-make-sense-of-information-ai-for-reading-research-documents-tickets-1990585353377?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>The event clearly has AI content (AI for reading, research &amp; documents), but it's virtual-only with no visible Georgia organizational tie, missing critical details like date/time/description, and appears to be part of a series rather than a standalone offering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AI for Job Seekers</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>2</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-for-job-seekers-tickets-1994096418066?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Event has clear AI content in title but is virtual-only with no Georgia organizational tie mentioned, missing description details, and appears to be a general webinar rather than an educational conference or technical discussion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Wednesd.AI</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>4</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Atlanta · Atlanta Tech Village - Buckhead</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/wednesdai-tickets-1990814107587?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta AI event with clear AI focus in the title (Wednesd.AI), though the lack of description limits confidence in assessing the specific content quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AI and 3D Construction &amp; Design Tech Lunch and Learn!</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>4</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Morrow · Bedrosians Tile &amp; Stone</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-and-3d-construction-design-tech-lunch-and-learn-tickets-1996235261404?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Morrow (Georgia, outside Atlanta metro) with explicit AI focus in title and 3D/construction tech content, though lack of detailed description limits confidence in assessing depth of AI content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AI Tools for Real Impact: ChatGPT and Effective Prompting</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>3</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Atlanta · 1928 Stanton Rd</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-tools-for-real-impact-chatgpt-and-effective-prompting-tickets-1994911577229?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with clear AI/ChatGPT focus and educational intent, but hampered by missing detailed description and potentially introductory-level content that could be a sales pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Tech and Wealth Workshop</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2:00 PM CDT</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.ca/e/tech-and-wealth-workshop-tickets-1996425661897?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Event has no mention of AI, machine learning, or automation in its title or available description, and is a virtual-only event with no Georgia organizational tie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>AI Awareness: The Good, the Bad, and What to Watch For</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>4</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>East Point · 1928 Stanton Rd</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-awareness-the-good-the-bad-and-what-to-watch-for-tickets-1991930436557?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Georgia (East Point) with clear AI focus in the title, but limited description details reduce confidence in assessing depth and educational value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Alpha Esports &amp; Technology Fall Open House</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Suwanee · Alpha Esports and Technology</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/alpha-esports-technology-fall-open-house-tickets-1996425184469?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation, triggering the automatic 1 rating despite being in-person in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" s="3" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>no_events</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Role Based Training: ChatGPT for IT &amp; Security teams</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>3</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>11:00 a.m.</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://ai.georgia.gov/events/2026-08-06/role-based-training-chatgpt-it-security-teams</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event with clear AI content (ChatGPT training) hosted by Georgia's official AI organization qualifies for mid-range scoring despite lack of in-person attendance, but incomplete description limits confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Role Based Training: ChatGPT for Project, Program, Product Managers</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>4</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2:30 p.m.</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://ai.georgia.gov/events/2026-08-17/chatgpt-project-and-program-managers</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>Virtual event with clear AI focus (ChatGPT training) hosted by Georgia's official AI organization (ai.georgia.gov), qualifying it for the 3-4 range for Georgia-based hosts despite virtual format, though the short description being empty slightly reduces confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ChatGPT Essentials</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>3</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>1:30 p.m.</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://ai.georgia.gov/events/2026-08-25/chatgpt-essentials</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>AI-focused event hosted by Georgia's official AI organization (ai.georgia.gov) which provides Georgia institutional credibility, but virtual-only format with missing description details and unclear educational vs. sales intent prevent a higher score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Snowday 2026: Accelerating Georgia's Data-Driven Future</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>4</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>8:30 a.m.</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://ai.georgia.gov/events/2026-09-01/snowday-2026</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event hosted by Georgia's official AI organization with a clear data-driven/AI focus in the title, but the empty description prevents full assessment of content depth and whether it's educational or sales-oriented.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4470,14 +6056,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K153"/>
+  <dimension ref="A1:K204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
@@ -11067,7 +12653,6 @@
           <t>6:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/ibm-skillsbuild-orientation-1693369?sourceTypeId=Website</t>
@@ -11116,7 +12701,6 @@
           <t>6:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/qWFX016fkCQCe</t>
@@ -11165,7 +12749,6 @@
           <t>9:00 AM - 3:00 PM</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/canceled-2026-georgia-day-of-code-1723691?sourceTypeId=Website</t>
@@ -11258,7 +12841,6 @@
           <t>July 27, 2026</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>Georgia</t>
@@ -11312,7 +12894,6 @@
           <t>2:30 PM EDT</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>https://www.meetup.com/refactr-tech/events/314126109/?recId=0ebce766-0208-4387-bd1d-76e940ebf82c&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=05035234-c275-48f4-b199-f583ac5b76b3&amp;eventOrigin=find_page%24all</t>
@@ -11406,7 +12987,6 @@
           <t>12:00 PM EDT</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/the-cost-of-bad-ux-based-on-real-projects-tickets-1993809241112?aff=ebdssbdestsearch</t>
@@ -11941,7 +13521,6 @@
           <t>3:00 PM CDT</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
           <t>https://www.eventbrite.ca/e/tech-and-wealth-workshop-tickets-1995254351476?aff=ebdssbdestsearch</t>
@@ -11986,7 +13565,6 @@
           <t>2:00 PM EDT</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/bad-ux-in-numbers-exploring-real-cases-tickets-1993810735582?aff=ebdssbdestsearch</t>
@@ -12031,7 +13609,6 @@
           <t>4:00 PM PDT</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>https://www.eventbrite.co.uk/e/high-thc-medical-cannabis-a-scientific-breakdown-tickets-1992308768157?aff=ebdssbdestsearch</t>
@@ -12046,6 +13623,2483 @@
       <c r="K153" s="2" t="inlineStr">
         <is>
           <t>Event has zero mention of AI, machine learning, or automation - it is about medical cannabis science, which automatically disqualifies it regardless of other criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Exceptional Care Experiences: Building Trust, Loyalty, and Connection Across Industries presented by TAG CX Society and TAG Digital Health Society</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>5:30 PM - 8:00 PM</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/4lFO0aGuRCMCx</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>Explore how organizations design and deliver exceptional experiences across the full customer, guest, and patient journey.</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule, and is virtual-only with no Georgia organizational tie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>IBM SkillsBuild Orientation</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>6:00 PM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar/Details/ibm-skillsbuild-orientation-1693369?sourceTypeId=Website</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>Join us for a mandatory virtual orientation to kick off the upcoming cohort. Participants will receive an overview of the program structure, expectations, key dates, and a demo on how to access the learning platform.</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic-1 rule, and the virtual-only format with no Georgia organizational tie provides no offsetting factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Find a Startup to Help or Join</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>1:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/projects-for-developers-cs-majors-and-ux-designers/events/315933865/?recId=c9fa2fcb-2337-495c-ac93-1d91a25e8b54&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=0500200c-b3c2-429f-8698-91ed31868873&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>CISSP Certification Training Course in Bothell, CA</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Augusta · 22722 29th Dr SE West, Suite 100, Bothell, WA 98021</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/cissp-certification-training-course-in-bothell-ca-tickets-1980894231972?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Washington (WA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Mobility Unlimited Hub applicant webinar</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>10:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>MaRS Discovery District</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.ca/e/mobility-unlimited-hub-applicant-webinar-tickets-1993481840849?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or available description, triggering the automatic 1 rating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Info Session-Cyber Work Role Pathways *W/Career Placement Assistance</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>7:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>University of Louisville</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/info-session-cyber-work-role-pathways-wcareer-placement-assistance-tickets-1996449412937?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>God, Science, and Our Search for Meaning</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Young Harris · O. Wayne Rollins Planetarium</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/god-science-and-our-search-for-meaning-tickets-1992094158253?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Own Your Sh*t Atlanta</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>1</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Atlanta · Urban Grind</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/own-your-sht-atlanta-tickets-1992579763712?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Savannah Paranormal Museum: After Hours Investigation</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Savannah · Savannah Paranormal Museum</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/savannah-paranormal-museum-after-hours-investigation-tickets-1992267994201?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>AWS Solutions Architect Associate Classroom Training in Savannah, GA</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Savannah · Gallo Legal Services Savannah</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/aws-solutions-architect-associate-classroom-training-in-savannah-ga-tickets-1992339834076?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description—it is purely AWS certification training, which is an automatic 1 per the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Book Signing and Talk with Craig M. Robinson</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Atlanta · Village Books</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/book-signing-and-talk-with-craig-m-robinson-tickets-1996112827200?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Business Analyst (CBAP) Classroom Training in Auburn, AL</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Columbus · 5547 Veterans Pkwy</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/business-analyst-cbap-classroom-training-in-auburn-al-tickets-1970898472386?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule; additionally, it is located in Auburn, Alabama, not Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Business Analytics Certification (CBAP) Training in Augusta, GA</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>1</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Augusta · 823 Broad St</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/business-analytics-certification-cbap-training-in-augusta-ga-tickets-1970052557231?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description—it is a business analytics certification training focused on the CBAP credential, which does not constitute AI content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Communication Strategies: 1-Day Executive Training | Atlanta (GA)</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>1</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Atlanta · Regus - Atlanta - 260 Peachtree</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.sg/e/communication-strategies-1-day-executive-training-atlanta-ga-tickets-1993432674792?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>CBAP® Classroom Training – IIBA® Aligned in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Atlanta · 260 Peachtree St suite 2200</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/cbap-classroom-training-iiba-aligned-in-atlanta-ga-tickets-1975384024794?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description—it is CBAP classroom training for business analysis certification, which is unrelated to AI content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>STEM Meets Mini-Golf</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Fairburn · Swing ATL</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/stem-meets-mini-golf-tickets-1995590907123?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>STEM Family Sundays at iFLY Atlanta!</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>1</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Atlanta · iFLY Indoor Skydiving - Atlanta</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/stem-family-sundays-at-ifly-atlanta-tickets-1991765472144?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in title or description, triggering the automatic 1 rating regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>CBAP® Exam Prep Weekend Classroom Training – IIBA® Aligned in Savannah, GA</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Savannah · 100 Bull St</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/cbap-exam-prep-weekend-classroom-training-iiba-aligned-in-savannah-ga-tickets-1975274239423?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description - it is a business analysis certification exam prep course with no AI component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>UGA Grand Farm Field Day</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Perry · 1101 Limerock Pkwy</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/uga-grand-farm-field-day-tickets-1994913718634?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location or in-person format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Georgia Adopt-A-Stream Macroinvertebrate Monitoring Workshop</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>1</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Griffin · 865 S 9th St</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/georgia-adopt-a-stream-macroinvertebrate-monitoring-workshop-tickets-1981743503165?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Code Reading Club</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Atlanta · 1055 Howell Mill Rd</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/code-reading-club-tickets-1986676353453?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>**IN PERSON**Broker and Salesperson CE: Right, Wrong… or Risky?</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Duluth · Maximum One Executives - Duluth</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/in-personbroker-and-salesperson-ce-right-wrong-or-risky-tickets-1989028818740?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location or in-person status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>CEH v12 Ethical Hacking Bootcamp – 4 Days Training in Augusta, GA</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>1</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Augusta, GA</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ceh-v12-ethical-hacking-bootcamp-4-days-training-in-augusta-ga-tickets-1986315866226?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating despite being in-person in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>CISSP Certification Weekend Training Course in Sandy Springs, GA</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Atlanta · 1000 Abernathy Rd NE</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/cissp-certification-weekend-training-course-in-sandy-springs-ga-tickets-1981292064901?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description—it is a CISSP cybersecurity certification course with no stated AI component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>CEH Certification In-Person Training in Sandy Springs, GA</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>1</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Sandy Springs, GA</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ceh-certification-in-person-training-in-sandy-springs-ga-tickets-1987123125761?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description—it is a CEH (Certified Ethical Hacker) certification training, which is cybersecurity-focused but not AI-related.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>CEH Certification Weekend Training Course in Sandy Springs, GA</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>1</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Sandy Springs, GA</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ceh-certification-weekend-training-course-in-sandy-springs-ga-tickets-1986876078837?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>CEH (Certified Ethical Hacker) certification training has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>CISSP Certification | ISC² Exam Preparation Program in Savannah, GA</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Savannah, GA</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/cissp-certification-isc2-exam-preparation-program-in-savannah-ga-tickets-1980765494916?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description - it is a CISSP cybersecurity certification exam prep course with no AI-focused component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>The Art of Leadership &amp; Communication - 1 Day Session in Atlanta GA</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>1</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.sg/e/the-art-of-leadership-communication-1-day-session-in-atlanta-ga-tickets-1690553895209?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>MICROLOCK SELF RETIGHTENING MADE EASY!</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Atlanta · 705 Town Blvd</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/microlock-self-retightening-made-easy-tickets-1903263234569?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>AWS Solution Architect Training in Athens, GA</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>1</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Athens, GA</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/aws-solution-architect-training-in-athens-ga-tickets-1987328746779?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in title or description, making it an automatic 1 per the criteria regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>AWS Solutions Architect Associate Certification Training in Augusta, GA</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>1</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Augusta, GA</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/aws-solutions-architect-associate-certification-training-in-augusta-ga-tickets-1987307393912?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Stronger Communities Through Leadership Skills – 1 Day Training in Atlanta</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>1</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.sg/e/stronger-communities-through-leadership-skills-1-day-training-in-atlanta-tickets-1702814948349?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of in-person Atlanta location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>AWS Solution Architect Training | 4-Day Bootcamp in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>1</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/aws-solution-architect-training-4-day-bootcamp-in-atlanta-ga-tickets-1987119022488?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule despite being in-person in Atlanta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Certified Ethical Hacker – Practical Ethical Hacker in Macon, GA</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Macon, GA</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/certified-ethical-hacker-practical-ethical-hacker-in-macon-ga-tickets-1986302519305?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description - it is about ethical hacking certification training, which is cybersecurity-focused but not AI-related.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Opening Reception for Fulton Brighter Futures | An Interactive Installation</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>1</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Atlanta · Fulton County Government</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/opening-reception-for-fulton-brighter-futures-an-interactive-installation-tickets-1994078848515?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location or in-person status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Computer Basics</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>1</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="n">
+        <v>46241</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Mableton · South Cobb Regional Library</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/computer-basics-tickets-1992514234713?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Great Southeast Pollinator Census at Legacy Park</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Decatur · Decatur Legacy Park</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/great-southeast-pollinator-census-at-legacy-park-tickets-1995541908567?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Common Compliance Pitfalls</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>1</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Atlanta · RSM - Atlanta Midtown office</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/common-compliance-pitfalls-tickets-1996172339202?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation, triggering the automatic-1 rule regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Stay Safe Online: Cybersecurity for Seniors</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>1</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/stay-safe-online-cybersecurity-for-seniors-tickets-1992514958879?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation, triggering the automatic-1 rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Tap Into Tech with Seniors</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>1</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>9:30 AM</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Stonecrest · Browns Mill Recreation Center</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/tap-into-tech-with-seniors-tickets-1984059620735?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location or in-person format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Adopt-A-Stream Bacterial Monitoring Workshop</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>1</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Marietta · Cobb County Water Lab Training Room</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/adopt-a-stream-bacterial-monitoring-workshop-tickets-1995474593225?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Stormwater Education Program</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>1</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/stormwater-education-program-tickets-1995485724519?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Great Pollinator Census</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>1</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/great-pollinator-census-tickets-1995488467724?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or available description, triggering the automatic 1 score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Internet Basics</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>1</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Marietta · Switzer Library</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/internet-basics-tickets-1993856705078?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr"/>
+      <c r="K197" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 score regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Gmail Basics</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/gmail-basics-tickets-1993856585721?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Georgia Adopt-A-Stream Chemical Monitoring Workshop</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/georgia-adopt-a-stream-chemical-monitoring-workshop-tickets-1970640942106?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1-score rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Nostr Atlanta #15 - Rush Hour Avoidance</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315762247/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>Join Nostr Atlanta for a session aimed at avoiding rush hour traffic. Bring your laptop as this session will involve some tool building. Informal round-table discussion of Nostr and adjacent topics from 4:30–6:00 PM.</t>
+        </is>
+      </c>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation; it is about Nostr (a decentralized social protocol) and tool building with no AI-focused component stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - June</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>1</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Manuels Tavern, 602 North Highland Ave NE, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044570/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>Casual BitPlebs meetup at Manuel's Tavern geared towards helping you learn about how to get bitcoin, use bitcoin, and understand where it fits into current events. Arrive early for free beverages. Includes a presentation and beer social.</t>
+        </is>
+      </c>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, focusing entirely on Bitcoin education and socializing, which triggers the automatic-1 rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - June</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044571/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr"/>
+      <c r="K202" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, making it an automatic 1 regardless of location or other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - June</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>1</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044572/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr"/>
+      <c r="K203" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule regardless of location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - June</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>1</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>46351</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>August 3, 2026</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>6:00 PM EST</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Manuel's Tavern, 602 North Highland Avenue Northeast, Atlanta, GA 30307</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044573/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in title or description, triggering the automatic-1 rule despite being in-person in Atlanta.</t>
         </is>
       </c>
     </row>

--- a/events_master.xlsx
+++ b/events_master.xlsx
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K118" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K140" headerRowCount="1">
   <autoFilter ref="A1:K53"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K204" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K215" headerRowCount="1">
   <autoFilter ref="A1:K132"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -462,14 +462,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K118"/>
+  <dimension ref="A1:K140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
@@ -4456,7 +4456,6 @@
           <t>6:30 PM EDT</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>https://www.meetup.com/modernwebatl/events/315488146/?recId=c9fa2fcb-2337-495c-ac93-1d91a25e8b54&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=0500200c-b3c2-429f-8698-91ed31868873&amp;eventOrigin=find_page%24all</t>
@@ -4501,7 +4500,6 @@
           <t>7:30 PM EDT</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>https://www.meetup.com/freeside-atlanta/events/315410843/?recId=c9fa2fcb-2337-495c-ac93-1d91a25e8b54&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=0500200c-b3c2-429f-8698-91ed31868873&amp;eventOrigin=find_page%24all</t>
@@ -4525,17 +4523,12 @@
           <t>https://luma.com/genai-collective</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" s="3" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>August 3, 2026</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>no_events</t>
@@ -4571,7 +4564,6 @@
           <t>2:00 PM CDT</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>https://www.eventbrite.ca/e/tech-and-wealth-workshop-tickets-1996426857473?aff=ebdssbdestsearch</t>
@@ -4910,7 +4902,6 @@
           <t>3:00 PM CDT</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>https://www.eventbrite.ca/e/tech-and-wealth-workshop-tickets-1996426541528?aff=ebdssbdestsearch</t>
@@ -4955,7 +4946,6 @@
           <t>9:30 AM EDT</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>https://www.eventbrite.co.uk/e/machine-learning-for-trading-in-the-age-of-ai-agents-tickets-1994299755253?aff=ebdssbdestsearch</t>
@@ -5392,7 +5382,6 @@
           <t>10:00 AM EDT</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>https://www.eventbrite.co.uk/e/build-executive-ready-excel-reports-with-microsoft-copilot-tickets-1994204467244?aff=ebdssbdestsearch</t>
@@ -5479,8 +5468,6 @@
           <t>August 3, 2026</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/part-2-make-sense-of-information-ai-for-reading-research-documents-tickets-1990585353377?aff=ebdssbdestsearch</t>
@@ -5525,7 +5512,6 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/ai-for-job-seekers-tickets-1994096418066?aff=ebdssbdestsearch</t>
@@ -5717,7 +5703,6 @@
           <t>2:00 PM CDT</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
           <t>https://www.eventbrite.ca/e/tech-and-wealth-workshop-tickets-1996425661897?aff=ebdssbdestsearch</t>
@@ -5839,17 +5824,12 @@
           <t>https://atlanta.aitinkerers.org/</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
       <c r="D114" s="3" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>August 3, 2026</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>no_events</t>
@@ -5885,7 +5865,6 @@
           <t>11:00 a.m.</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>https://ai.georgia.gov/events/2026-08-06/role-based-training-chatgpt-it-security-teams</t>
@@ -5930,7 +5909,6 @@
           <t>2:30 p.m.</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
           <t>https://ai.georgia.gov/events/2026-08-17/chatgpt-project-and-program-managers</t>
@@ -5975,7 +5953,6 @@
           <t>1:30 p.m.</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
           <t>https://ai.georgia.gov/events/2026-08-25/chatgpt-essentials</t>
@@ -6039,6 +6016,1040 @@
       <c r="K118" s="2" t="inlineStr">
         <is>
           <t>In-person Atlanta event hosted by Georgia's official AI organization with a clear data-driven/AI focus in the title, but the empty description prevents full assessment of content depth and whether it's educational or sales-oriented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>How AI Is Supercharging NextGen Solutions and the Investing Landscape presented by TAG Corporate Development Society and TAG Data Science &amp; AI Society</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>2</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>5:30 PM - 8:30 PM</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/4lFXlWOiRCMCx</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>Sharp insight from the executives living this shift firsthand, and a front-row seat to the founders building next gen solutions.</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>Event has genuine AI content (TAG Data Science &amp; AI Society is a co-host with stated AI focus) but is virtual-only with no clear Georgia organizational tie, and the vague description lacks specific session details about the AI component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Data Ingestion in Fabric - Ginger Grant</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/dba-fundamentals-group/events/315182870/?recId=638524a7-d934-4434-9d4f-83e72a5d59ae&amp;recSource=ml-popular-events-nearby-online&amp;searchId=e8c9bfc6-65cd-4d6d-af2f-2539b9217477&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>Event has no mention of AI, machine learning, or automation in its title or available description, and appears to be a technical data/database session rather than AI-focused content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Meet Atlanta Tech Week &amp; RenderATL Speakers! **JOIN WAITLIST ON LUMA)**</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>6:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/refactr-tech/events/315473059/?recId=638524a7-d934-4434-9d4f-83e72a5d59ae&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=e8c9bfc6-65cd-4d6d-af2f-2539b9217477&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>Event has no description content and title mentions only a speaker meetup with no indication of AI, machine learning, or automation focus, making it impossible to verify AI relevance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>FREE REMOTE | LADIES IN AI + AI GROWTH CIRCLE (AN OPEN AI FORUM FOR ALL)</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>2</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>7:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ai-growth-circle/events/315016426/?recId=638524a7-d934-4434-9d4f-83e72a5d59ae&amp;recSource=ml-popular-events-nearby-online&amp;searchId=e8c9bfc6-65cd-4d6d-af2f-2539b9217477&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with AI focus (Ladies in AI + AI Growth Circle) but no Georgia organizational tie mentioned, no detailed description provided, and online format limits its value for a Georgia-focused digest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" s="3" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>no_events</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Health &amp; Life Sciences Research Tech</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/health-life-sciences-research-tech-tickets-1990892797952?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>Event details lack any mention of AI, machine learning, or automation in the title or description, and the empty short description prevents assessment of genuine AI-focused content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AI Literacy Bootcamp</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>2</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>6:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-literacy-bootcamp-tickets-1997208273710?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>Event has clear AI content in title but is virtual-only with no Georgia organizational tie mentioned, and critical details like description and host organization are missing, making it impossible to verify Georgia focus or assess educational quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>The Future Is Here! AI 2026: What's New, What's Next &amp; What Matters!</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>4</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Eatonton · 951 Harmony Rd suite 102</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/the-future-is-here-ai-2026-whats-new-whats-next-what-matters-tickets-1996530858543?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Eatonton (outside metro Atlanta) with clear AI focus in title, but empty description limits confidence in assessing event quality and depth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Strategic Prompt Design for AI 1 Day Training in Marietta, GA</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>2</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Marietta, GA</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/strategic-prompt-design-for-ai-1-day-training-in-marietta-ga-tickets-1992104255454?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>Event is in-person in Georgia (positive), has AI content in title, but appears to be a paid training/sales pitch with no description provided to assess educational value or legitimacy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Summer Connections: Atlanta Tech Week Edition</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Atlanta · High Society Buckhead</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/summer-connections-atlanta-tech-week-edition-tickets-1997135499039?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule, though the extremely sparse details (missing description) prevent higher confidence in this assessment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Curiosity Night at Laurel and Lore</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Guyton · 181 Old Oak Rd</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/curiosity-night-at-laurel-and-lore-tickets-1997333264561?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule despite being in-person in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>4-Day Data Science with Python Bootcamp in Macon, GA</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>3</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Fayetteville · 320 W Lanier Ave</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/4-day-data-science-with-python-bootcamp-in-macon-ga-tickets-1985401411066?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>In-person data science bootcamp in Georgia (Fayetteville, near Macon) with clear AI/machine learning relevance, but lacks detailed description and appears to be a paid training program which scores moderately rather than highly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Data Science with Phython Certification Training in Columbus, GA</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Columbus · 5547 Veterans Pkwy</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/data-science-with-phython-certification-training-in-columbus-ga-tickets-1985087343682?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>While this is an in-person event in Columbus, GA (outside metro Atlanta, which is positive), it appears to be a paid certification training course that is likely a sales-focused offering rather than an educational AI event, and the description lacks any specific mention of AI, machine learning, or automation components despite being data science training.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Data Science with Python Certification Training in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>2</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Atlanta · 3423 Piedmont Rd NE</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/data-science-with-python-certification-training-in-atlanta-ga-tickets-1984745299619?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>Event is in-person in Atlanta with potential AI relevance (data science), but the complete absence of description and heavy emphasis on 'certification training' suggests it may be a paid training/sales pitch rather than an educational conference, and the lack of detail prevents confident assessment of its AI content quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>How to Get Started with Artificial Intelligence (AI)</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>4</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Marietta · Switzer Library</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/how-to-get-started-with-artificial-intelligence-ai-tickets-1993857732150?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>In-person AI event in Marietta (outside Atlanta metro) with clear AI focus in title, though empty description limits confidence and suggests it may be a basic introductory session rather than in-depth technical content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>AARI x Waymo x Chic-Fil-a Back to School Robotics Event (In Person)</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>4</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Atlanta · Russell Innovation Center for Entrepreneurs</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/aari-x-waymo-x-chic-fil-a-back-to-school-robotics-event-in-person-tickets-1997019634485?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta robotics event with clear AI/automation focus (Waymo autonomous vehicles partnership) and educational mission, though the empty description limits confidence in assessing depth of AI content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Wednesd.AI</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>4</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Atlanta · Atlanta Tech Village - Buckhead</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/wednesdai-tickets-1990814107587?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with clear AI focus in title (Wednesd.AI), but confidence is medium due to missing event description that would clarify the specific AI content and format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>AI Awareness: The Good, the Bad, and What to Watch For</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>4</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>East Point · 1928 Stanton Rd</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-awareness-the-good-the-bad-and-what-to-watch-for-tickets-1991930436557?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Georgia (East Point) with clear AI focus in title and theme, though limited description details prevent a higher score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>AI Training for Business Owners: Get Out of the Day-to-Day (Free, Live)</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>2</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-training-for-business-owners-get-out-of-the-day-to-day-free-live-tickets-1996472647432?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>Event has clear AI content in title but is virtual-only with no Georgia organizational tie evident, no location specified, and appears to be a free business training that could be a sales pitch, warranting a low score pending more information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>AI Tinkerers Atlanta x AI Collective: Community Demos at ATL Tech Week</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>4</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>1:45 PM EDT</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://atlanta.aitinkerers.org/p/ai-tinkerers-atlanta-x-ai-collective-community-demos-at-atl-tech-week</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>AI Tinkerers Atlanta and AI Collective will host community demos. Sponsors AI Collective and Atlanta Tech Week will support the event.</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>In-person AI-focused community event in Atlanta with clear AI content (demos) hosted by established AI organizations, though the brief description lacks specific session details that would warrant a higher score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Role Based Training: ChatGPT for Procurement</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>4</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>11:00 a.m.</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://ai.georgia.gov/events/2026-08-24/chatgpt-procurement</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>AI-focused training event (ChatGPT) hosted by Georgia's official AI organization (ai.georgia.gov) with clear Georgia tie, but virtual format and lack of description details prevent higher rating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ChatGPT Advanced Use</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>3</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>10:00 a.m.</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://ai.georgia.gov/events/2026-09-02/chatgpt-advanced-use</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>The event has clear AI content (ChatGPT) and is hosted by ai.georgia.gov, a Georgia-based organization, which elevates a virtual-only event to the 3-4 range, but the lack of description and details prevents a higher score.</t>
         </is>
       </c>
     </row>
@@ -6056,14 +7067,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K204"/>
+  <dimension ref="A1:K215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
@@ -13653,7 +14664,6 @@
           <t>5:30 PM - 8:00 PM</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/4lFO0aGuRCMCx</t>
@@ -13702,7 +14712,6 @@
           <t>6:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/ibm-skillsbuild-orientation-1693369?sourceTypeId=Website</t>
@@ -13751,7 +14760,6 @@
           <t>1:30 PM EDT</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
           <t>https://www.meetup.com/projects-for-developers-cs-majors-and-ux-designers/events/315933865/?recId=c9fa2fcb-2337-495c-ac93-1d91a25e8b54&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=0500200c-b3c2-429f-8698-91ed31868873&amp;eventOrigin=find_page%24all</t>
@@ -15063,7 +16071,6 @@
           <t>August 3, 2026</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
           <t>Athens, GA</t>
@@ -15505,7 +16512,6 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/stay-safe-online-cybersecurity-for-seniors-tickets-1992514958879?aff=ebdssbdestsearch</t>
@@ -15648,7 +16654,6 @@
           <t>6:30 PM</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/stormwater-education-program-tickets-1995485724519?aff=ebdssbdestsearch</t>
@@ -15693,7 +16698,6 @@
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/great-pollinator-census-tickets-1995488467724?aff=ebdssbdestsearch</t>
@@ -15787,7 +16791,6 @@
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/gmail-basics-tickets-1993856585721?aff=ebdssbdestsearch</t>
@@ -15832,7 +16835,6 @@
           <t>6:30 PM</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/georgia-adopt-a-stream-chemical-monitoring-workshop-tickets-1970640942106?aff=ebdssbdestsearch</t>
@@ -16100,6 +17102,531 @@
       <c r="K204" s="2" t="inlineStr">
         <is>
           <t>Event has zero mention of AI, machine learning, or automation in title or description, triggering the automatic-1 rule despite being in-person in Atlanta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Hacking the System: Health, Freedom and Income</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>1</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>7:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/hacking-the-system-health-freedom-and-income-tickets-1994593661334?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr"/>
+      <c r="K205" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in title or description, triggering the automatic-1 rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Business Analyst (CBAP) Classroom Training in Athens, GA</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>1</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Athens · 2470 Daniells Bridge Rd</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/business-analyst-cbap-classroom-training-in-athens-ga-tickets-1970897699073?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr"/>
+      <c r="K206" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description - it is a business analyst certification training course with no AI-focused component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>STEM Family Sundays at iFLY Atlanta!</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>1</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Atlanta · iFLY Indoor Skydiving - Atlanta</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/stem-family-sundays-at-ifly-atlanta-tickets-1991765472144?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr"/>
+      <c r="K207" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or available description, triggering the automatic-1 rule regardless of in-person Atlanta location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Composting 101 Workshop with Green Done Wright</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>1</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>10:30 AM</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Avondale Estates · 32 N Avondale Rd suite c</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/composting-101-workshop-with-green-done-wright-tickets-1996638381146?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr"/>
+      <c r="K208" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation - it is a composting workshop with no AI-focused component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>CEH Certification In-Person Training in Augusta, GA</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Augusta, GA</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ceh-certification-in-person-training-in-augusta-ga-tickets-1986891577193?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr"/>
+      <c r="K209" s="2" t="inlineStr">
+        <is>
+          <t>CEH (Certified Ethical Hacker) certification training has no mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule regardless of its in-person Georgia location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>CEH Certification Weekend Training Course in Savannah, GA</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Savannah, GA</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ceh-certification-weekend-training-course-in-savannah-ga-tickets-1986878155047?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or available description - it is a CEH (Certified Ethical Hacker) certification course focused on cybersecurity, not AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>CEH v12 Ethical Hacking Bootcamp – 4 Days Training in Athens, GA</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>1</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Athens · 2470 Daniells Bridge Rd Building 100 / Suite 161, Athens, GA 30606</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ceh-v12-ethical-hacking-bootcamp-4-days-training-in-athens-ga-tickets-1986397488360?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr"/>
+      <c r="K211" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description—it is purely about ethical hacking certification training, which is a cybersecurity topic distinct from AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>AWS Solution Architect Training in Athens, GA</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Athens, GA</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/aws-solution-architect-training-in-athens-ga-tickets-1987328746779?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule despite being in-person in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>AWS Solutions Architect Associate Certification Training in Augusta, GA</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Augusta, GA</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/aws-solutions-architect-associate-certification-training-in-augusta-ga-tickets-1987307393912?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr"/>
+      <c r="K213" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description—it is AWS certification training content with no stated AI-focused component, triggering the automatic-1 rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CISSP Certification Weekend Training Course in Savannah, GA</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Savannah · Gallo Legal Services Savannah</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/cissp-certification-weekend-training-course-in-savannah-ga-tickets-1981281933598?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr"/>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description—it is a CISSP cybersecurity certification training course with no AI-focused component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>CISSP Certification | ISC² Exam Preparation Program in Columbus, GA</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>1</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>August 10, 2026</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Columbus, GA</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/cissp-certification-isc2-exam-preparation-program-in-columbus-ga-tickets-1980702995980?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr"/>
+      <c r="K215" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation—it is a CISSP cybersecurity certification exam prep program with no AI-focused component.</t>
         </is>
       </c>
     </row>

--- a/events_master.xlsx
+++ b/events_master.xlsx
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K140" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K166" headerRowCount="1">
   <autoFilter ref="A1:K53"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K215" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K243" headerRowCount="1">
   <autoFilter ref="A1:K132"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K140"/>
+  <dimension ref="A1:K166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -6046,7 +6046,6 @@
           <t>5:30 PM - 8:30 PM</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/4lFXlWOiRCMCx</t>
@@ -6144,7 +6143,6 @@
           <t>6:30 PM EDT</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>https://www.meetup.com/refactr-tech/events/315473059/?recId=638524a7-d934-4434-9d4f-83e72a5d59ae&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=e8c9bfc6-65cd-4d6d-af2f-2539b9217477&amp;eventOrigin=find_page%24all</t>
@@ -6217,17 +6215,12 @@
           <t>https://luma.com/genai-collective</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
       <c r="D123" s="3" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>August 10, 2026</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>no_events</t>
@@ -6263,7 +6256,6 @@
           <t>12:00 PM EDT</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/health-life-sciences-research-tech-tickets-1990892797952?aff=ebdssbdestsearch</t>
@@ -6308,7 +6300,6 @@
           <t>6:30 PM EDT</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/ai-literacy-bootcamp-tickets-1997208273710?aff=ebdssbdestsearch</t>
@@ -6892,7 +6883,6 @@
           <t>12:00 PM EDT</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/ai-training-for-business-owners-get-out-of-the-day-to-day-free-live-tickets-1996472647432?aff=ebdssbdestsearch</t>
@@ -6990,7 +6980,6 @@
           <t>11:00 a.m.</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
           <t>https://ai.georgia.gov/events/2026-08-24/chatgpt-procurement</t>
@@ -7035,7 +7024,6 @@
           <t>10:00 a.m.</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>https://ai.georgia.gov/events/2026-09-02/chatgpt-advanced-use</t>
@@ -7052,6 +7040,1186 @@
           <t>The event has clear AI content (ChatGPT) and is hosted by ai.georgia.gov, a Georgia-based organization, which elevates a virtual-only event to the 3-4 range, but the lack of description and details prevents a higher score.</t>
         </is>
       </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Data Center Bus Tour presented by TAG Infrastructure Society</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>8:30 AM - 2:00 PM</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/qWFJmQmFkCQCe</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or available description, triggering the automatic-1 rule despite being in-person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>AIMST - AI Conference - GMA Special Exhibitor and Moderator</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>4</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/aimst---ai-conference---gma-special-exhibitor-and-moderator</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>In-person AI conference with Georgia manufacturing industry tie (GMA = Georgia Manufacturing Alliance), though the minimal event description and missing location details prevent a higher score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>**New location** 🎬 404 Movie Not Found: Coyote vs. Acme</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>4:20 PM EDT</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/refactr-tech/events/315951068/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>Event title and description contain no mention of AI, machine learning, or automation, and the empty short description provides no additional context to indicate AI content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Building AI-Ready Teams — Talent, Culture &amp; Leadership in the AI Era</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>4</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>5:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/georgia-ai-alliance-meetup-group/events/316063226/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>Strong AI-focused title and Georgia AI Alliance hosting indicate genuine AI content, in-person format is favorable, but missing location details and empty description prevent higher confidence and optimal scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Open House!</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>7:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/freeside-atlanta/events/315371013/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule despite being in-person and hosted by Freeside Atlanta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>GA AI Alliance Networking Lunch</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>3</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>11:45 AM EDT</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/georgia-ai-alliance-meetup-group/events/315873146/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>Event is in-person and hosted by Georgia AI Alliance (Georgia-based org) which strongly suggests AI focus, but the completely empty description and lack of specific AI content details in the listing prevent a higher confidence score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Kiro Workshop: Let's Finish What We Started!</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlanta-aws-user-group/events/316120191/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-online&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>Event has no description and title provides no indication of AI, machine learning, or automation content, making it impossible to assess the AI component despite being hosted by an AWS user group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>BHS X Sandbox Atlanta Present: CTF Training for First-timers</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>6:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/blackhack-society-atlanta/events/315951497/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>Event has no mention of AI, machine learning, or automation in its title or available description, and CTF (Capture The Flag) training is a cybersecurity competition skill unrelated to AI content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Power of the Noun: Intro to IA in the Age of AI</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>3</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>6:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ladies-that-ux-atl/events/314440739/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>The event title explicitly mentions AI and information architecture, suggesting genuine AI content rather than a sales pitch, and appears to be an in-person meetup event (likely Atlanta-based given the Ladies That UX ATL meetup group), but the missing location field and empty description limit confidence in the exact venue and event depth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>AI Workshop with Microsoft and Neo4j</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>4</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>1:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/aittg-atlanta/events/316088846/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>Strong AI content (Microsoft and Neo4j workshop) with in-person Atlanta location, but empty description and missing venue details reduce confidence despite the clear AI focus and reputable organizers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>AI Fundamentals for Small Business Owners (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>3</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-at-8-19-1</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>Event has clear AI content (fundamentals topic) and is in-person in Georgia (Alpharetta), but the empty description and 'small business owners' framing suggest it may be sales-oriented rather than educational, and lacks details on depth/quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>PDX AI Expo Second Webinar</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>10:00 PM</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-kul-pdx-20260820</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>Event has no AI content mentioned in title or description (only 'PDX AI Expo Second Webinar' with empty short_description), is virtual-only with no Georgia connection, and lacks sufficient details to verify any AI-focused component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Batchery Startup Studio Office Hours (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>2</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-st-8-20</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>Event mentions AI in the title ('The AI Collective') but lacks description details to confirm genuine AI content versus a generic startup office hours event, and location is blank despite in-person designation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>How To Build A One Person Company With AI</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>2</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>8:00 AM</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-kul-AIS-20260822</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>Event title mentions AI but lacks description, location, and Georgia ties; virtual-only format with no apparent educational value or Georgia organization hosting it suggests a general webinar that may be a sales pitch rather than substantive AI content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Build a Second Brain for Your AI Coding Agents</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>9:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.co.uk/e/build-a-second-brain-for-your-ai-coding-agents-registration-1997854208719?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>Virtual-only event with no Georgia tie, no organization details provided, and insufficient event description to verify AI content beyond the title.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>AI Tool Intensive</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>2</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>6:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-tool-intensive-tickets-1997208673907?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>Event has clear AI focus in title but is virtual-only with no Georgia organizational tie evident, and critically lacks any description or details to verify content authenticity or distinguish it from a sales pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>FREE AI Data Engineering Bootcamp | USA Only | Join WhatsApp Group</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>2</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>10:30 AM EDT</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/free-ai-data-engineering-bootcamp-usa-only-join-whatsapp-group-tickets-1992777462033?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>Event has clear AI/data engineering focus, but is virtual-only with no Georgia organizational tie, unclear host organization, and lacks substantive description details beyond the promotional title.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>AI Security Intelligence Forum 1 Day in Marietta, GA</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>4</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Marietta, GA</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-security-intelligence-forum-1-day-in-marietta-ga-tickets-1992626101309?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>In-person event in Marietta, GA (outside metro Atlanta) with clear AI focus in title (AI Security Intelligence Forum), but incomplete event details and missing date/time information limit confidence in scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Design It, Release It — Free Live App-Building Challenge</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>7:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/design-it-release-it-free-live-app-building-challenge-registration-1997505995203?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>Event has no mention of AI, machine learning, or automation in its title or available description, and lacks sufficient detail to determine if any AI component exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>AI Threat Detection Summit 1 Day in Sandy Springs, GA</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>4</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Sandy Springs, GA</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-threat-detection-summit-1-day-in-sandy-springs-ga-tickets-1992637267708?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>In-person AI-focused event (threat detection) in Sandy Springs, Georgia outside metro Atlanta, but lacks detailed description content to fully assess educational value versus sales pitch nature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Southeast RUG - Atlanta August 2026 - AI / ERP Education</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>4</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Oaks at Dunwoody · 1200 Abernathy Rd NE</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/southeast-rug-atlanta-august-2026-ai-erp-education-tickets-1980092625345?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with explicit AI/ERP education focus, but limited detail in description and unclear whether AI is a primary or secondary component of the content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>AI Creative Launch Bootcamp at The Brio!</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>3</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Tucker · Brio Theater</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-creative-launch-bootcamp-at-the-brio-tickets-1998161340358?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>In-person Georgia event (Tucker) with clear AI focus in title, but completely empty description prevents assessment of depth, educational value, or whether it's a genuine learning opportunity versus a sales pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Technology Health and Wealth</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Castleberry Hill · Russell Innovation Center for Entrepreneurs</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/technology-health-and-wealth-tickets-1997931976324?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or short description, triggering the automatic-1 rule, though the vague title and missing description limit confidence in this assessment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Wednesd.AI</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>4</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>North Buckhead · Atlanta Tech Village - Buckhead</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/wednesdai-tickets-1990814107587?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta AI event with clear AI focus in title, but low confidence due to missing event description that would clarify content quality and educational value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Curiosity Series #3: Why Five Stones? | Ignite House Atlanta</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>East Washington · Ignite House</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/curiosity-series-3-why-five-stones-ignite-house-atlanta-tickets-1997481419697?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or available description, triggering the automatic-1 rule despite being in-person in Atlanta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>https://atlanta.aitinkerers.org/</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" s="3" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>no_events</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7067,7 +8235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K215"/>
+  <dimension ref="A1:K243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -17132,7 +18300,6 @@
           <t>7:00 PM EDT</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/hacking-the-system-health-freedom-and-income-tickets-1994593661334?aff=ebdssbdestsearch</t>
@@ -17368,7 +18535,6 @@
           <t>August 10, 2026</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
           <t>Savannah, GA</t>
@@ -17509,7 +18675,6 @@
           <t>August 10, 2026</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
           <t>Augusta, GA</t>
@@ -17627,6 +18792,1314 @@
       <c r="K215" s="2" t="inlineStr">
         <is>
           <t>Event has zero mention of AI, machine learning, or automation—it is a CISSP cybersecurity certification exam prep program with no AI-focused component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>TAG-Ed Pathways to Leadership Virtual Open House</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>1</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>6:00 PM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/qWFX016fkCQCe</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>Join us for an inside look at the Pathways to Leadership program, a year-long leadership experience designed for emerging and mid-level professionals. During this session, you'll learn about the program's structure and benefits and hear from graduates.</t>
+        </is>
+      </c>
+      <c r="K216" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, and appears to be a general leadership development program open house with no AI-focused component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Mid-Year Market Update presented by TAG Corporate Development Society</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>5:30 PM - 7:30 PM</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/07FO6JwhxCwCR</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>The conversation will cover equity market performance, credit market functionality, M&amp;A activity, and the evolving technology investment landscape.</t>
+        </is>
+      </c>
+      <c r="K217" s="2" t="inlineStr">
+        <is>
+          <t>The event description makes no mention of AI, machine learning, or automation—it focuses on equity markets, credit markets, and M&amp;A activity with only vague reference to 'technology investment landscape' which does not constitute genuine AI content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Find a Startup to Help or Join</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/projects-for-developers-cs-majors-and-ux-designers/events/314898432/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr"/>
+      <c r="K218" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>AI Founders Lunch &amp; Learn</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>4:30 AM GMT+3</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Helsinki, Finland</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-fi-8-18</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr"/>
+      <c r="K219" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Finland, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Agentic AI Knight Turku</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>10:00 AM GMT+3</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Turku, Finland</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-fi-8-19</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr"/>
+      <c r="K220" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Finland, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Building with AI: Stamford Micro-Hackathon (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Stamford, CT</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-st-8-19</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr"/>
+      <c r="K221" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Connecticut (CT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Social Happy Hour (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Detroit, MI</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-de-8-19</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr"/>
+      <c r="K222" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Michigan (MI), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Prompting Desvelado: Secretos que Funcionan (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>1</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Bogotá, Colombia</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-bog-prompt-20-8</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr"/>
+      <c r="K223" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Colombia, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Hack for Humanity: Canberra</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>1</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Acton, Australia</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://luma.com/h4h-canberra</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr"/>
+      <c r="K224" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Australia, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>[Beginner 101] Claude Dashboard for CEOs and HODs</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>1</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>9:00 PM</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Puchong, Malaysia</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-kul-CMC-20260822</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr"/>
+      <c r="K225" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Malaysia, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Practical Agentic AI - Build with AI Series (w/ The AI Collective Pune)</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>1</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>1:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-pu-8-22</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr"/>
+      <c r="K226" s="2" t="inlineStr">
+        <is>
+          <t>Location is in India, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Build with AI &lt;/Noida&gt;</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>1</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>1:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>New Delhi, India</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-noida-build-with-ai</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr"/>
+      <c r="K227" s="2" t="inlineStr">
+        <is>
+          <t>Location is in India, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Penang Coffee Tech Talk #001</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>1</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Jelutong, Malaysia</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-kul-20260822</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr"/>
+      <c r="K228" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Malaysia, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Founder Brand Lab: Personal Branding Workshop for Founders (w/ The AI Collective)</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>1</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>4:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Bengaluru, India</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://luma.com/aic-founder-personal-branding</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr"/>
+      <c r="K229" s="2" t="inlineStr">
+        <is>
+          <t>Location is in India, not Georgia, USA; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>AI Security Intelligence Masterclass 1 Day in Chapel Hill, NC</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>1</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Chapel Hill, NC</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-security-intelligence-masterclass-1-day-in-chapel-hill-nc-tickets-1992624392197?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr"/>
+      <c r="K230" s="2" t="inlineStr">
+        <is>
+          <t>Location is in North Carolina (NC), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>AI Security Operations Summit 1 Day in Fremont, CA</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>1</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Fremont, CA</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-security-operations-summit-1-day-in-fremont-ca-tickets-1992624395206?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr"/>
+      <c r="K231" s="2" t="inlineStr">
+        <is>
+          <t>Location is in California (CA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>AI-Powered Threat Detection 1 Day in Frisco, TX</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>1</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Frisco, TX</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-powered-threat-detection-1-day-in-frisco-tx-tickets-1992624396209?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="inlineStr"/>
+      <c r="K232" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Texas (TX), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>AI Security Analytics Training 1 Day in Katy, TX</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>1</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Katy, TX</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-security-analytics-training-1-day-in-katy-tx-tickets-1992626100306?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr"/>
+      <c r="K233" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Texas (TX), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>AI Threat Monitoring Summit 1 Day in Mountain View, CA</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>1</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Mountain View, CA</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-threat-monitoring-summit-1-day-in-mountain-view-ca-tickets-1992626112342?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr"/>
+      <c r="K234" s="2" t="inlineStr">
+        <is>
+          <t>Location is in California (CA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>AI Security Operations Masterclass 1 Day in Menlo Park, CA</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>1</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-security-operations-masterclass-1-day-in-menlo-park-ca-tickets-1992626110336?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr"/>
+      <c r="K235" s="2" t="inlineStr">
+        <is>
+          <t>Location is in California (CA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>AI Risk Analytics Workshop 1 Day in Norwalk, CT</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>1</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Norwalk, CT</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-risk-analytics-workshop-1-day-in-norwalk-ct-tickets-1992626120366?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J236" s="2" t="inlineStr"/>
+      <c r="K236" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Connecticut (CT), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>AI Risk Monitoring Lab 1 Day in Clearwater, FL</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>1</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Clearwater, FL</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-risk-monitoring-lab-1-day-in-clearwater-fl-tickets-1992624393200?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr"/>
+      <c r="K237" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Florida (FL), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>AI Security Analytics Workshop 1 Day in El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>1</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-security-analytics-workshop-1-day-in-el-segundo-ca-tickets-1992624394203?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr"/>
+      <c r="K238" s="2" t="inlineStr">
+        <is>
+          <t>Location is in California (CA), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>AI Risk Detection Workshop 1 Day in McKinney, TX</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>1</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>McKinney, TX</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-risk-detection-workshop-1-day-in-mckinney-tx-tickets-1992626104318?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr"/>
+      <c r="K239" s="2" t="inlineStr">
+        <is>
+          <t>Location is in Texas (TX), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>AI Security Monitoring Bootcamp 1 Day in Newark, NJ</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>1</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Newark, NJ</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-security-monitoring-bootcamp-1-day-in-newark-nj-tickets-1992626118360?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr"/>
+      <c r="K240" s="2" t="inlineStr">
+        <is>
+          <t>Location is in New Jersey (NJ), not Georgia; auto-rejected without scoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Dumpling Squishy STEM Lab</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>1</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Peoplestown · 1161 Ridge Ave SW</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/dumpling-squishy-stem-lab-tickets-1996471558174?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr"/>
+      <c r="K241" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule regardless of location or in-person format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>CEH v12 Ethical Hacking Bootcamp – 4 Days Training in Savannah, GA</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>North Historic District · 100 Bull St</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ceh-v12-ethical-hacking-bootcamp-4-days-training-in-savannah-ga-tickets-1986551522079?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr"/>
+      <c r="K242" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule despite being an in-person technical security training in Georgia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Block Party South Athens</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>1</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>August 17, 2026</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Broad Acres · Athentic Brewing Company</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/block-party-south-athens-tickets-1997878158353?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr"/>
+      <c r="K243" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location or in-person status.</t>
         </is>
       </c>
     </row>

--- a/events_master.xlsx
+++ b/events_master.xlsx
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K166" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K180" headerRowCount="1">
   <autoFilter ref="A1:K53"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K243" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K247" headerRowCount="1">
   <autoFilter ref="A1:K132"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K166"/>
+  <dimension ref="A1:K180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -473,7 +473,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
@@ -7068,7 +7068,6 @@
           <t>8:30 AM - 2:00 PM</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/qWFJmQmFkCQCe</t>
@@ -7108,8 +7107,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
           <t>https://www.georgiamanufacturingalliance.com/events/aimst---ai-conference---gma-special-exhibitor-and-moderator</t>
@@ -7154,7 +7151,6 @@
           <t>4:20 PM EDT</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
           <t>https://www.meetup.com/refactr-tech/events/315951068/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7199,7 +7195,6 @@
           <t>5:00 PM EDT</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
           <t>https://www.meetup.com/georgia-ai-alliance-meetup-group/events/316063226/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7244,7 +7239,6 @@
           <t>7:30 PM EDT</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
           <t>https://www.meetup.com/freeside-atlanta/events/315371013/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7289,7 +7283,6 @@
           <t>11:45 AM EDT</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
           <t>https://www.meetup.com/georgia-ai-alliance-meetup-group/events/315873146/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7383,7 +7376,6 @@
           <t>6:30 PM EDT</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>https://www.meetup.com/blackhack-society-atlanta/events/315951497/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7428,7 +7420,6 @@
           <t>6:30 PM EDT</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
           <t>https://www.meetup.com/ladies-that-ux-atl/events/314440739/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7473,7 +7464,6 @@
           <t>1:30 PM EDT</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>https://www.meetup.com/aittg-atlanta/events/316088846/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7616,7 +7606,6 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>https://luma.com/aic-st-8-20</t>
@@ -7661,7 +7650,6 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
           <t>https://luma.com/aic-kul-AIS-20260822</t>
@@ -7706,7 +7694,6 @@
           <t>9:00 AM EDT</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>https://www.eventbrite.co.uk/e/build-a-second-brain-for-your-ai-coding-agents-registration-1997854208719?aff=ebdssbdestsearch</t>
@@ -7751,7 +7738,6 @@
           <t>6:30 PM EDT</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/ai-tool-intensive-tickets-1997208673907?aff=ebdssbdestsearch</t>
@@ -7796,7 +7782,6 @@
           <t>10:30 AM EDT</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/free-ai-data-engineering-bootcamp-usa-only-join-whatsapp-group-tickets-1992777462033?aff=ebdssbdestsearch</t>
@@ -7834,7 +7819,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
           <t>Marietta, GA</t>
@@ -7884,7 +7868,6 @@
           <t>7:00 PM EDT</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/design-it-release-it-free-live-app-building-challenge-registration-1997505995203?aff=ebdssbdestsearch</t>
@@ -8202,17 +8185,12 @@
           <t>https://atlanta.aitinkerers.org/</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
-      <c r="C166" t="inlineStr"/>
       <c r="D166" s="3" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>no_events</t>
@@ -8220,6 +8198,604 @@
       </c>
       <c r="J166" s="2" t="inlineStr"/>
       <c r="K166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Meet the Data and AI Mentor presented by TAG Data Science &amp; AI Society</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>4</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>5:30 PM - 7:30 PM</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/WqFXB5btaCJCE</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>An immersive, speed-dating style mentorship event where junior professionals connect with senior leaders in technology, data, and AI. Mentees will gain career insights, practical tips, and strategies for long-term success while building meaningful mentor-oriented relationships.</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>Hosted by TAG Data Science &amp; AI Society (a Georgia organization per the criteria), features AI as a core theme with senior leaders in AI/data mentoring junior professionals, and while marked virtual, the Georgia host elevates it to 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>AI in Action: Real-World Projects Transforming Fintech presented by TAG Fintech Society</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>4</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>11:30 AM - 1:30 PM</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/AnFJEbAfVCdCN</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>This Lunch &amp; Learn session will feature discussions with a series of tech and financial services leaders who have gone beyond brainstorming about how AI will impact their businesses.</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>TAG Fintech Society is a Georgia-based organization (TAG chapter), the event has clear AI content focused on real-world AI projects in fintech, and while the location field is blank (treated as in-person default), the virtual designation is explicit in the JSON, making this a Georgia-hosted virtual educational event on AI that scores well under the criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>https://www.aimanufacturingconference.com/</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" s="3" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>no_events</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Agentic AI Meetup - August</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>4</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>5:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/aittg-atlanta/events/315755582/?recId=09697859-f96d-4fab-a35e-1add97ec4ec7&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cbfb4fa0-571c-4ddf-bff3-26a32f00c328&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>Join us for deep dive tech talks on AI, GenAI, LLMs and Agents, hands-on experiences on code labs, workshops, and networking with speakers and fellow developers.</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>Strong AI content (agentic AI, GenAI, LLMs, agents with tech talks and hands-on labs) hosted by Atlanta AI Tinkerers (a Georgia-based organization), in-person format, though location venue details are missing from this listing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Cybersecurity n' Chill Networking Monthly Meetup by BlackHack Society</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>4</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>6:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/blackhack-society-atlanta/events/313204276/?recId=09697859-f96d-4fab-a35e-1add97ec4ec7&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cbfb4fa0-571c-4ddf-bff3-26a32f00c328&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>Join BlackHack Society of Atlanta where young professionals and industry experts discuss the latest trends in Cybersecurity, Ethical Hacking, AI, and Offensive Security. This casual meet-and-greet over food, drinks and video games is designed for technology entrepreneurs, ethical hackers, and anyone interested in cybersecurity to connect with the local community.</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event hosted by BlackHack Society with explicit mention of AI as one of several discussion topics alongside cybersecurity and ethical hacking, making it an educational networking event with genuine AI content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>FREE REMOTE | LADIES IN AI + AI GROWTH CIRCLE (AN OPEN AI FORUM FOR ALL)</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>2</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>46275</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>7:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ai-growth-circle/events/315505979/?recId=09697859-f96d-4fab-a35e-1add97ec4ec7&amp;recSource=ml-popular-events-nearby-online&amp;searchId=cbfb4fa0-571c-4ddf-bff3-26a32f00c328&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>A collaborative community where members share real experiences and help each other grow in AI. Explore topics from basic AI concepts to advanced tools, automation, prompting, business applications, and emerging technologies. Open discussion, live demos, and networking for all experience levels.</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>Event is virtual-only with clear AI content (AI concepts, tools, automation, prompting), but lacks Georgia-specific hosting or organizational ties, making it a national virtual event that scores below the threshold for out-of-state virtual events.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Ethical Hacker Tactics, CTF &amp; Tech Talks Monthly by BlackHack Society</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>3</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>6:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/blackhack-society-atlanta/events/313204253/?recId=09697859-f96d-4fab-a35e-1add97ec4ec7&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cbfb4fa0-571c-4ddf-bff3-26a32f00c328&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>Monthly offensive security hacking practice session featuring guided practice on penetration testing techniques. Topics include Vulnhub, Google Dorking, Capture the Flag Events, Net King of the Hill, FlipperZero, Wifi Pineapple, and Locksport. Bring your laptop and Kali Linux. Guest speakers announced as scheduled.</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>This is an in-person security-focused event hosted by BlackHack Society in Atlanta with legitimate educational content on penetration testing and hacking techniques (which involve automation and technical security tools), but lacks explicit AI/ML mentions and is primarily about offensive security rather than AI specifically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Save millions on inference by building a model router</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>3</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ai-ship-and-social/events/316198820/?recId=09697859-f96d-4fab-a35e-1add97ec4ec7&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cbfb4fa0-571c-4ddf-bff3-26a32f00c328&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>Learn how to route AI requests to the right models instead of sending them all to the most expensive ones. Speaker Aria will teach you why using the best model costs ~7x more than necessary, the four ways to build a router, and how to catch bad answers before users see them. You'll write your own routing rule and walk away with a working router you can read end to end in one sitting.</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>The event has strong AI content (model routing, inference optimization) and appears to be in-person, but the missing location prevents confirmation it's in Georgia, and the Meetup group name suggests it may be national rather than Georgia-based, though the educational technical nature of the talk is a positive factor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Agentic AI Meetup (August)</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>4</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>5:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlantaai/events/315755600/?recId=09697859-f96d-4fab-a35e-1add97ec4ec7&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cbfb4fa0-571c-4ddf-bff3-26a32f00c328&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>Join us for deep dive tech talks on AI, GenAI, LLMs and Agents, hands-on experiences on code labs, workshops, and networking with speakers and fellow developers. In collaboration with Google.</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>Strong AI content (Agentic AI, GenAI, LLMs, Agents with hands-on labs) hosted by Atlanta AI Tinkerers (a recognized Georgia organization per criteria), in-person format, educational focus with industry collaboration (Google), though the blank location field and August 2026 date prevent a perfect score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" s="3" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>no_events</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" s="3" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>failed: Failed to scrape page with Firecrawl: Rate Limit Exceeded: Failed to scrape. Rate limit exceeded. Consumed (req/min): 11, Remaining (req/min): 0. Upgrade your plan at https://firecrawl.dev/pricing for increased rate limits or please retry after 1s, resets at Mon Aug 24 2026 14:34:04 GMT+0000 (Coordinated Universal Time) - No additional error details provided.</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Agents, Everywhere: Beyond The Chatbot — Global Hackathon</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>5</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>46277</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://atlanta.aitinkerers.org/p/agents-everywhere-beyond-the-chatbot-global-hackathon</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>AI Tinkerers will host a hackathon for builders to develop working agents. Sponsors OpenAI, CopilotKit, and OpenRouter will provide support.</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>This is a Georgia-hosted (Atlanta AI Tinkerers) in-person hackathon with explicit AI content (AI agents development), prominent AI sponsor support, and strong educational/developmental value for builders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - August</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>3</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Manuels Tavern, 602 North Highland Ave NE, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/315044570/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>Casual BitPlebs meetup at Manuel's Tavern. Main topic: Monitoring the Situation - Red Team edition. Devs embroiled in a struggle to stay ahead of the AI and preserve freedom tech. Includes introduction, community announcements, an astrology update on AI exploits, and a beer social.</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>The event is hosted by ATL BitLab (a Georgia organization) in Atlanta and explicitly mentions AI as a main topic ('Red Team edition' focused on 'staying ahead of the AI'), but it's primarily a casual social meetup with beer rather than an educational or technical AI discussion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>https://ai.georgia.gov/events</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" s="3" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>failed: Failed to scrape page with Firecrawl: Rate Limit Exceeded: Failed to scrape. Rate limit exceeded. Consumed (req/min): 12, Remaining (req/min): 0. Upgrade your plan at https://firecrawl.dev/pricing for increased rate limits or please retry after 1s, resets at Mon Aug 24 2026 14:34:04 GMT+0000 (Coordinated Universal Time) - No additional error details provided.</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8235,7 +8811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K243"/>
+  <dimension ref="A1:K247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -18822,7 +19398,6 @@
           <t>6:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/qWFX016fkCQCe</t>
@@ -18871,7 +19446,6 @@
           <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/07FO6JwhxCwCR</t>
@@ -18920,7 +19494,6 @@
           <t>6:00 PM EDT</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr">
         <is>
           <t>https://www.meetup.com/projects-for-developers-cs-majors-and-ux-designers/events/314898432/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -19546,7 +20119,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
           <t>Fremont, CA</t>
@@ -19589,7 +20161,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
           <t>Frisco, TX</t>
@@ -19632,7 +20203,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
           <t>Katy, TX</t>
@@ -19675,7 +20245,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr">
         <is>
           <t>Mountain View, CA</t>
@@ -19718,7 +20287,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
           <t>Menlo Park, CA</t>
@@ -19761,7 +20329,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
           <t>Norwalk, CT</t>
@@ -19804,7 +20371,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr">
         <is>
           <t>Clearwater, FL</t>
@@ -19847,7 +20413,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
           <t>El Segundo, CA</t>
@@ -19890,7 +20455,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
           <t>McKinney, TX</t>
@@ -19933,7 +20497,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
           <t>Newark, NJ</t>
@@ -20100,6 +20663,198 @@
       <c r="K243" s="2" t="inlineStr">
         <is>
           <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location or in-person status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Fiber Manufacturer Webinar presented by TAG Infrastructure Society</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>1</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>12:00 PM - 1:00 PM</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/4lFO3BwURCMCx</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr"/>
+      <c r="K244" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule; despite being hosted by TAG (a Georgia organization), the event is about fiber manufacturing with no stated AI component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>TAG-Ed Pathways to Leadership Virtual Open House</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>1</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>6:00 PM - 7:00 PM</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar/Details/tag-ed-pathways-to-leadership-virtual-open-house-1848623?sourceTypeId=Website</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>Join us for an inside look at the Pathways to Leadership program, a year-long leadership experience designed for emerging and mid-level professionals. Learn about the program's structure and benefits and hear from graduates.</t>
+        </is>
+      </c>
+      <c r="K245" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, and despite being hosted by TAG (a Georgia organization), the automatic-1 rule applies because there is no genuine AI-focused component stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>TAG-Ed IBM SkillsBuild Orientation x Tech Women Foundation</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>1</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>6:00 PM - 8:00 PM</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/aZFEJ70HvCqCZ</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr">
+        <is>
+          <t>Join us for a mandatory virtual orientation to kick off the upcoming cohort. During this session, participants will receive an overview of the program structure, expectations, key dates, and demo on how to access the learning platform.</t>
+        </is>
+      </c>
+      <c r="K246" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation—it is purely an orientation for program access and logistics, triggering the automatic-1 rule despite TAG's Georgia tie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Optimized Locking in SQL Server 2025: Internals, Contention, and Concurrency</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>1</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/dba-fundamentals-group/events/312863781/?recId=09697859-f96d-4fab-a35e-1add97ec4ec7&amp;recSource=ml-popular-events-nearby-online&amp;searchId=cbfb4fa0-571c-4ddf-bff3-26a32f00c328&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr"/>
+      <c r="K247" s="2" t="inlineStr">
+        <is>
+          <t>The event contains zero mention of AI, machine learning, or automation in its title or description—it is exclusively about SQL Server locking internals, making it an automatic 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>

--- a/events_master.xlsx
+++ b/events_master.xlsx
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K180" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K166" headerRowCount="1">
   <autoFilter ref="A1:K53"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K247" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K243" headerRowCount="1">
   <autoFilter ref="A1:K132"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K180"/>
+  <dimension ref="A1:K166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -473,7 +473,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
@@ -7068,6 +7068,7 @@
           <t>8:30 AM - 2:00 PM</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/qWFJmQmFkCQCe</t>
@@ -7107,6 +7108,8 @@
           <t>August 17, 2026</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
           <t>https://www.georgiamanufacturingalliance.com/events/aimst---ai-conference---gma-special-exhibitor-and-moderator</t>
@@ -7151,6 +7154,7 @@
           <t>4:20 PM EDT</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
           <t>https://www.meetup.com/refactr-tech/events/315951068/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7195,6 +7199,7 @@
           <t>5:00 PM EDT</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
           <t>https://www.meetup.com/georgia-ai-alliance-meetup-group/events/316063226/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7239,6 +7244,7 @@
           <t>7:30 PM EDT</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
           <t>https://www.meetup.com/freeside-atlanta/events/315371013/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7283,6 +7289,7 @@
           <t>11:45 AM EDT</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
           <t>https://www.meetup.com/georgia-ai-alliance-meetup-group/events/315873146/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7376,6 +7383,7 @@
           <t>6:30 PM EDT</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>https://www.meetup.com/blackhack-society-atlanta/events/315951497/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7420,6 +7428,7 @@
           <t>6:30 PM EDT</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
           <t>https://www.meetup.com/ladies-that-ux-atl/events/314440739/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7464,6 +7473,7 @@
           <t>1:30 PM EDT</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>https://www.meetup.com/aittg-atlanta/events/316088846/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7606,6 +7616,7 @@
           <t>10:00 AM</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>https://luma.com/aic-st-8-20</t>
@@ -7650,6 +7661,7 @@
           <t>8:00 AM</t>
         </is>
       </c>
+      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
           <t>https://luma.com/aic-kul-AIS-20260822</t>
@@ -7694,6 +7706,7 @@
           <t>9:00 AM EDT</t>
         </is>
       </c>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>https://www.eventbrite.co.uk/e/build-a-second-brain-for-your-ai-coding-agents-registration-1997854208719?aff=ebdssbdestsearch</t>
@@ -7738,6 +7751,7 @@
           <t>6:30 PM EDT</t>
         </is>
       </c>
+      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/ai-tool-intensive-tickets-1997208673907?aff=ebdssbdestsearch</t>
@@ -7782,6 +7796,7 @@
           <t>10:30 AM EDT</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/free-ai-data-engineering-bootcamp-usa-only-join-whatsapp-group-tickets-1992777462033?aff=ebdssbdestsearch</t>
@@ -7819,6 +7834,7 @@
           <t>August 17, 2026</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
           <t>Marietta, GA</t>
@@ -7868,6 +7884,7 @@
           <t>7:00 PM EDT</t>
         </is>
       </c>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/design-it-release-it-free-live-app-building-challenge-registration-1997505995203?aff=ebdssbdestsearch</t>
@@ -8185,12 +8202,17 @@
           <t>https://atlanta.aitinkerers.org/</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
       <c r="D166" s="3" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>August 17, 2026</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>no_events</t>
@@ -8198,604 +8220,6 @@
       </c>
       <c r="J166" s="2" t="inlineStr"/>
       <c r="K166" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Meet the Data and AI Mentor presented by TAG Data Science &amp; AI Society</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>4</v>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>5:30 PM - 7:30 PM</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>https://members.tagonline.org/ap/Events/Register/WqFXB5btaCJCE</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J167" s="2" t="inlineStr">
-        <is>
-          <t>An immersive, speed-dating style mentorship event where junior professionals connect with senior leaders in technology, data, and AI. Mentees will gain career insights, practical tips, and strategies for long-term success while building meaningful mentor-oriented relationships.</t>
-        </is>
-      </c>
-      <c r="K167" s="2" t="inlineStr">
-        <is>
-          <t>Hosted by TAG Data Science &amp; AI Society (a Georgia organization per the criteria), features AI as a core theme with senior leaders in AI/data mentoring junior professionals, and while marked virtual, the Georgia host elevates it to 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>AI in Action: Real-World Projects Transforming Fintech presented by TAG Fintech Society</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>4</v>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>11:30 AM - 1:30 PM</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>https://members.tagonline.org/ap/Events/Register/AnFJEbAfVCdCN</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>This Lunch &amp; Learn session will feature discussions with a series of tech and financial services leaders who have gone beyond brainstorming about how AI will impact their businesses.</t>
-        </is>
-      </c>
-      <c r="K168" s="2" t="inlineStr">
-        <is>
-          <t>TAG Fintech Society is a Georgia-based organization (TAG chapter), the event has clear AI content focused on real-world AI projects in fintech, and while the location field is blank (treated as in-person default), the virtual designation is explicit in the JSON, making this a Georgia-hosted virtual educational event on AI that scores well under the criteria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>https://www.aimanufacturingconference.com/</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr"/>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" s="3" t="inlineStr"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>no_events</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr"/>
-      <c r="K169" s="2" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Agentic AI Meetup - August</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>4</v>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>5:30 PM EDT</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/aittg-atlanta/events/315755582/?recId=09697859-f96d-4fab-a35e-1add97ec4ec7&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cbfb4fa0-571c-4ddf-bff3-26a32f00c328&amp;eventOrigin=find_page%24all</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>Join us for deep dive tech talks on AI, GenAI, LLMs and Agents, hands-on experiences on code labs, workshops, and networking with speakers and fellow developers.</t>
-        </is>
-      </c>
-      <c r="K170" s="2" t="inlineStr">
-        <is>
-          <t>Strong AI content (agentic AI, GenAI, LLMs, agents with tech talks and hands-on labs) hosted by Atlanta AI Tinkerers (a Georgia-based organization), in-person format, though location venue details are missing from this listing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Cybersecurity n' Chill Networking Monthly Meetup by BlackHack Society</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>4</v>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>6:30 PM EDT</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/blackhack-society-atlanta/events/313204276/?recId=09697859-f96d-4fab-a35e-1add97ec4ec7&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cbfb4fa0-571c-4ddf-bff3-26a32f00c328&amp;eventOrigin=find_page%24all</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>Join BlackHack Society of Atlanta where young professionals and industry experts discuss the latest trends in Cybersecurity, Ethical Hacking, AI, and Offensive Security. This casual meet-and-greet over food, drinks and video games is designed for technology entrepreneurs, ethical hackers, and anyone interested in cybersecurity to connect with the local community.</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>In-person Atlanta event hosted by BlackHack Society with explicit mention of AI as one of several discussion topics alongside cybersecurity and ethical hacking, making it an educational networking event with genuine AI content.</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>FREE REMOTE | LADIES IN AI + AI GROWTH CIRCLE (AN OPEN AI FORUM FOR ALL)</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>2</v>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D172" s="3" t="n">
-        <v>46275</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>7:00 PM EDT</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/ai-growth-circle/events/315505979/?recId=09697859-f96d-4fab-a35e-1add97ec4ec7&amp;recSource=ml-popular-events-nearby-online&amp;searchId=cbfb4fa0-571c-4ddf-bff3-26a32f00c328&amp;eventOrigin=find_page%24all</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>A collaborative community where members share real experiences and help each other grow in AI. Explore topics from basic AI concepts to advanced tools, automation, prompting, business applications, and emerging technologies. Open discussion, live demos, and networking for all experience levels.</t>
-        </is>
-      </c>
-      <c r="K172" s="2" t="inlineStr">
-        <is>
-          <t>Event is virtual-only with clear AI content (AI concepts, tools, automation, prompting), but lacks Georgia-specific hosting or organizational ties, making it a national virtual event that scores below the threshold for out-of-state virtual events.</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Ethical Hacker Tactics, CTF &amp; Tech Talks Monthly by BlackHack Society</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>3</v>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="n">
-        <v>46268</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>6:30 PM EDT</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/blackhack-society-atlanta/events/313204253/?recId=09697859-f96d-4fab-a35e-1add97ec4ec7&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cbfb4fa0-571c-4ddf-bff3-26a32f00c328&amp;eventOrigin=find_page%24all</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>Monthly offensive security hacking practice session featuring guided practice on penetration testing techniques. Topics include Vulnhub, Google Dorking, Capture the Flag Events, Net King of the Hill, FlipperZero, Wifi Pineapple, and Locksport. Bring your laptop and Kali Linux. Guest speakers announced as scheduled.</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>This is an in-person security-focused event hosted by BlackHack Society in Atlanta with legitimate educational content on penetration testing and hacking techniques (which involve automation and technical security tools), but lacks explicit AI/ML mentions and is primarily about offensive security rather than AI specifically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Save millions on inference by building a model router</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>3</v>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>6:00 PM EDT</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/ai-ship-and-social/events/316198820/?recId=09697859-f96d-4fab-a35e-1add97ec4ec7&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cbfb4fa0-571c-4ddf-bff3-26a32f00c328&amp;eventOrigin=find_page%24all</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>Learn how to route AI requests to the right models instead of sending them all to the most expensive ones. Speaker Aria will teach you why using the best model costs ~7x more than necessary, the four ways to build a router, and how to catch bad answers before users see them. You'll write your own routing rule and walk away with a working router you can read end to end in one sitting.</t>
-        </is>
-      </c>
-      <c r="K174" s="2" t="inlineStr">
-        <is>
-          <t>The event has strong AI content (model routing, inference optimization) and appears to be in-person, but the missing location prevents confirmation it's in Georgia, and the Meetup group name suggests it may be national rather than Georgia-based, though the educational technical nature of the talk is a positive factor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Agentic AI Meetup (August)</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>4</v>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>5:30 PM EDT</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/atlantaai/events/315755600/?recId=09697859-f96d-4fab-a35e-1add97ec4ec7&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cbfb4fa0-571c-4ddf-bff3-26a32f00c328&amp;eventOrigin=find_page%24all</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>Join us for deep dive tech talks on AI, GenAI, LLMs and Agents, hands-on experiences on code labs, workshops, and networking with speakers and fellow developers. In collaboration with Google.</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>Strong AI content (Agentic AI, GenAI, LLMs, Agents with hands-on labs) hosted by Atlanta AI Tinkerers (a recognized Georgia organization per criteria), in-person format, educational focus with industry collaboration (Google), though the blank location field and August 2026 date prevent a perfect score.</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>https://luma.com/genai-collective</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr"/>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" s="3" t="inlineStr"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>no_events</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="inlineStr"/>
-      <c r="K176" s="2" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>https://www.eventbrite.com/d/united-states--georgia/science-and-tech--events--this-month/?page=1</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr"/>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" s="3" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>failed: Failed to scrape page with Firecrawl: Rate Limit Exceeded: Failed to scrape. Rate limit exceeded. Consumed (req/min): 11, Remaining (req/min): 0. Upgrade your plan at https://firecrawl.dev/pricing for increased rate limits or please retry after 1s, resets at Mon Aug 24 2026 14:34:04 GMT+0000 (Coordinated Universal Time) - No additional error details provided.</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="inlineStr"/>
-      <c r="K177" s="2" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Agents, Everywhere: Beyond The Chatbot — Global Hackathon</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>5</v>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D178" s="3" t="n">
-        <v>46277</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>10:00 AM</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>https://atlanta.aitinkerers.org/p/agents-everywhere-beyond-the-chatbot-global-hackathon</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="inlineStr">
-        <is>
-          <t>AI Tinkerers will host a hackathon for builders to develop working agents. Sponsors OpenAI, CopilotKit, and OpenRouter will provide support.</t>
-        </is>
-      </c>
-      <c r="K178" s="2" t="inlineStr">
-        <is>
-          <t>This is a Georgia-hosted (Atlanta AI Tinkerers) in-person hackathon with explicit AI content (AI agents development), prominent AI sponsor support, and strong educational/developmental value for builders.</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>BitPlebs: Bitcoin Pub Night @ Manuel's Tavern - August</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>3</v>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="D179" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>6:00 PM EDT</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Manuels Tavern, 602 North Highland Ave NE, Atlanta, GA, US</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/atlbitlab/events/315044570/?eventOrigin=group_events_list</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="inlineStr">
-        <is>
-          <t>Casual BitPlebs meetup at Manuel's Tavern. Main topic: Monitoring the Situation - Red Team edition. Devs embroiled in a struggle to stay ahead of the AI and preserve freedom tech. Includes introduction, community announcements, an astrology update on AI exploits, and a beer social.</t>
-        </is>
-      </c>
-      <c r="K179" s="2" t="inlineStr">
-        <is>
-          <t>The event is hosted by ATL BitLab (a Georgia organization) in Atlanta and explicitly mentions AI as a main topic ('Red Team edition' focused on 'staying ahead of the AI'), but it's primarily a casual social meetup with beer rather than an educational or technical AI discussion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>https://ai.georgia.gov/events</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr"/>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" s="3" t="inlineStr"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>failed: Failed to scrape page with Firecrawl: Rate Limit Exceeded: Failed to scrape. Rate limit exceeded. Consumed (req/min): 12, Remaining (req/min): 0. Upgrade your plan at https://firecrawl.dev/pricing for increased rate limits or please retry after 1s, resets at Mon Aug 24 2026 14:34:04 GMT+0000 (Coordinated Universal Time) - No additional error details provided.</t>
-        </is>
-      </c>
-      <c r="J180" s="2" t="inlineStr"/>
-      <c r="K180" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8811,7 +8235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K247"/>
+  <dimension ref="A1:K243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -19398,6 +18822,7 @@
           <t>6:00 PM - 7:00 PM</t>
         </is>
       </c>
+      <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/qWFX016fkCQCe</t>
@@ -19446,6 +18871,7 @@
           <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
+      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/07FO6JwhxCwCR</t>
@@ -19494,6 +18920,7 @@
           <t>6:00 PM EDT</t>
         </is>
       </c>
+      <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr">
         <is>
           <t>https://www.meetup.com/projects-for-developers-cs-majors-and-ux-designers/events/314898432/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -20119,6 +19546,7 @@
           <t>August 17, 2026</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
           <t>Fremont, CA</t>
@@ -20161,6 +19589,7 @@
           <t>August 17, 2026</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
           <t>Frisco, TX</t>
@@ -20203,6 +19632,7 @@
           <t>August 17, 2026</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
           <t>Katy, TX</t>
@@ -20245,6 +19675,7 @@
           <t>August 17, 2026</t>
         </is>
       </c>
+      <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr">
         <is>
           <t>Mountain View, CA</t>
@@ -20287,6 +19718,7 @@
           <t>August 17, 2026</t>
         </is>
       </c>
+      <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
           <t>Menlo Park, CA</t>
@@ -20329,6 +19761,7 @@
           <t>August 17, 2026</t>
         </is>
       </c>
+      <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
           <t>Norwalk, CT</t>
@@ -20371,6 +19804,7 @@
           <t>August 17, 2026</t>
         </is>
       </c>
+      <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr">
         <is>
           <t>Clearwater, FL</t>
@@ -20413,6 +19847,7 @@
           <t>August 17, 2026</t>
         </is>
       </c>
+      <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
           <t>El Segundo, CA</t>
@@ -20455,6 +19890,7 @@
           <t>August 17, 2026</t>
         </is>
       </c>
+      <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
           <t>McKinney, TX</t>
@@ -20497,6 +19933,7 @@
           <t>August 17, 2026</t>
         </is>
       </c>
+      <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
           <t>Newark, NJ</t>
@@ -20663,198 +20100,6 @@
       <c r="K243" s="2" t="inlineStr">
         <is>
           <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location or in-person status.</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>Fiber Manufacturer Webinar presented by TAG Infrastructure Society</t>
-        </is>
-      </c>
-      <c r="B244" t="n">
-        <v>1</v>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D244" s="3" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>12:00 PM - 1:00 PM</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>https://members.tagonline.org/ap/Events/Register/4lFO3BwURCMCx</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J244" s="2" t="inlineStr"/>
-      <c r="K244" s="2" t="inlineStr">
-        <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule; despite being hosted by TAG (a Georgia organization), the event is about fiber manufacturing with no stated AI component.</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>TAG-Ed Pathways to Leadership Virtual Open House</t>
-        </is>
-      </c>
-      <c r="B245" t="n">
-        <v>1</v>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D245" s="3" t="n">
-        <v>46268</v>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>6:00 PM - 7:00 PM</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr"/>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>https://members.tagonline.org/calendar/Details/tag-ed-pathways-to-leadership-virtual-open-house-1848623?sourceTypeId=Website</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J245" s="2" t="inlineStr">
-        <is>
-          <t>Join us for an inside look at the Pathways to Leadership program, a year-long leadership experience designed for emerging and mid-level professionals. Learn about the program's structure and benefits and hear from graduates.</t>
-        </is>
-      </c>
-      <c r="K245" s="2" t="inlineStr">
-        <is>
-          <t>The event has zero mention of AI, machine learning, or automation in its title or description, and despite being hosted by TAG (a Georgia organization), the automatic-1 rule applies because there is no genuine AI-focused component stated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>TAG-Ed IBM SkillsBuild Orientation x Tech Women Foundation</t>
-        </is>
-      </c>
-      <c r="B246" t="n">
-        <v>1</v>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D246" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>6:00 PM - 8:00 PM</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>https://members.tagonline.org/ap/Events/Register/aZFEJ70HvCqCZ</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J246" s="2" t="inlineStr">
-        <is>
-          <t>Join us for a mandatory virtual orientation to kick off the upcoming cohort. During this session, participants will receive an overview of the program structure, expectations, key dates, and demo on how to access the learning platform.</t>
-        </is>
-      </c>
-      <c r="K246" s="2" t="inlineStr">
-        <is>
-          <t>The event description contains zero mention of AI, machine learning, or automation—it is purely an orientation for program access and logistics, triggering the automatic-1 rule despite TAG's Georgia tie.</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>Optimized Locking in SQL Server 2025: Internals, Contention, and Concurrency</t>
-        </is>
-      </c>
-      <c r="B247" t="n">
-        <v>1</v>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D247" s="3" t="n">
-        <v>46273</v>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>August 24, 2026</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>12:00 PM EDT</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>https://www.meetup.com/dba-fundamentals-group/events/312863781/?recId=09697859-f96d-4fab-a35e-1add97ec4ec7&amp;recSource=ml-popular-events-nearby-online&amp;searchId=cbfb4fa0-571c-4ddf-bff3-26a32f00c328&amp;eventOrigin=find_page%24all</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="J247" s="2" t="inlineStr"/>
-      <c r="K247" s="2" t="inlineStr">
-        <is>
-          <t>The event contains zero mention of AI, machine learning, or automation in its title or description—it is exclusively about SQL Server locking internals, making it an automatic 1 regardless of other criteria.</t>
         </is>
       </c>
     </row>

--- a/events_master.xlsx
+++ b/events_master.xlsx
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K166" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K180" headerRowCount="1">
   <autoFilter ref="A1:K53"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K243" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K258" headerRowCount="1">
   <autoFilter ref="A1:K132"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K166"/>
+  <dimension ref="A1:K180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -7068,7 +7068,6 @@
           <t>8:30 AM - 2:00 PM</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/qWFJmQmFkCQCe</t>
@@ -7108,8 +7107,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
           <t>https://www.georgiamanufacturingalliance.com/events/aimst---ai-conference---gma-special-exhibitor-and-moderator</t>
@@ -7154,7 +7151,6 @@
           <t>4:20 PM EDT</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
           <t>https://www.meetup.com/refactr-tech/events/315951068/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7199,7 +7195,6 @@
           <t>5:00 PM EDT</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
           <t>https://www.meetup.com/georgia-ai-alliance-meetup-group/events/316063226/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7244,7 +7239,6 @@
           <t>7:30 PM EDT</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
           <t>https://www.meetup.com/freeside-atlanta/events/315371013/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7289,7 +7283,6 @@
           <t>11:45 AM EDT</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
           <t>https://www.meetup.com/georgia-ai-alliance-meetup-group/events/315873146/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7383,7 +7376,6 @@
           <t>6:30 PM EDT</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>https://www.meetup.com/blackhack-society-atlanta/events/315951497/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7428,7 +7420,6 @@
           <t>6:30 PM EDT</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
           <t>https://www.meetup.com/ladies-that-ux-atl/events/314440739/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7473,7 +7464,6 @@
           <t>1:30 PM EDT</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>https://www.meetup.com/aittg-atlanta/events/316088846/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -7616,7 +7606,6 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>https://luma.com/aic-st-8-20</t>
@@ -7661,7 +7650,6 @@
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
           <t>https://luma.com/aic-kul-AIS-20260822</t>
@@ -7706,7 +7694,6 @@
           <t>9:00 AM EDT</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>https://www.eventbrite.co.uk/e/build-a-second-brain-for-your-ai-coding-agents-registration-1997854208719?aff=ebdssbdestsearch</t>
@@ -7751,7 +7738,6 @@
           <t>6:30 PM EDT</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/ai-tool-intensive-tickets-1997208673907?aff=ebdssbdestsearch</t>
@@ -7796,7 +7782,6 @@
           <t>10:30 AM EDT</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/free-ai-data-engineering-bootcamp-usa-only-join-whatsapp-group-tickets-1992777462033?aff=ebdssbdestsearch</t>
@@ -7834,7 +7819,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
           <t>Marietta, GA</t>
@@ -7884,7 +7868,6 @@
           <t>7:00 PM EDT</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/design-it-release-it-free-live-app-building-challenge-registration-1997505995203?aff=ebdssbdestsearch</t>
@@ -8202,17 +8185,12 @@
           <t>https://atlanta.aitinkerers.org/</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
-      <c r="C166" t="inlineStr"/>
       <c r="D166" s="3" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>no_events</t>
@@ -8220,6 +8198,628 @@
       </c>
       <c r="J166" s="2" t="inlineStr"/>
       <c r="K166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Meet the Data and AI Mentor presented by TAG Data Science &amp; AI Society</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>4</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>5:30 PM</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/WqFXB5btaCJCE</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>An immersive, speed-dating style mentorship event where junior professionals connect with senior leaders in technology, data, and AI. Mentees will gain career insights, practical tips, and strategies for long-term success while building meaningful mentor-oriented relationships.</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>TAG Data Science &amp; AI Society is a Georgia organization with a genuine AI-focused mentorship component, and while the event is virtual-only (per the 'is_in_person: false' flag), Georgia-hosted virtual events by established local orgs score 3-4, elevated here due to the educational value of the AI-specific mentorship format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>AI in Action: Real-World Projects Transforming Fintech presented by TAG Fintech Society</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>4</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>11:30 AM</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/AnFJEbAfVCdCN</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>This Lunch &amp; Learn session will feature discussions with a series of tech and financial services leaders who have gone beyond brainstorming about how AI will impact their businesses.</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>Strong AI content (real-world AI projects in fintech) hosted by TAG Fintech Society (Georgia organization), though virtual-only format and missing explicit Georgia focus in event description prevent a perfect score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>https://www.aimanufacturingconference.com/</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" s="3" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>no_events</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Cybersecurity n' Chill Networking Monthly Meetup by BlackHack Society</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>4</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>6:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/blackhack-society-atlanta/events/313204276/?recId=87223c12-7c50-4a2a-b9d4-cb14dd08262e&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=77bf5e21-1b7b-4bbf-b4a1-a60c6109ecc9&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>A casual networking meetup for young professionals and industry experts to discuss the latest trends in Cybersecurity, Ethical Hacking, AI, and Offensive Security over food, drinks and video games. Open to technology startup entrepreneurs, ethical hackers, and those exploring cybersecurity.</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>The event explicitly mentions AI as a discussion topic alongside cybersecurity and ethical hacking, is hosted by BlackHack Society (an Atlanta-based organization based on the Meetup URL), and is confirmed as in-person with a clear educational/networking focus rather than a sales pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Ethical Hacker Tactics, CTF &amp; Tech Talks Monthly by BlackHack Society</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>2</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>6:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/blackhack-society-atlanta/events/313204253/?recId=87223c12-7c50-4a2a-b9d4-cb14dd08262e&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=77bf5e21-1b7b-4bbf-b4a1-a60c6109ecc9&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>Monthly offensive security hacking practice session featuring guided practice on penetration testing techniques. Topics include Vulnhub, Google Dorking, Capture the Flag Events, Net King of the Hill, FlipperZero, Wifi Pineapple, and lockpicking. Covers beginner to advanced techniques with bonus guest speakers.</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>The event is security-focused rather than AI/ML/automation-focused, lacks any mention of AI content in its title or description, and while it appears to be in-person and hosted by an Atlanta-area group (BlackHack Society Atlanta), it does not meet the AI content threshold required for a higher score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Save millions on inference by building a model router</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>2</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ai-ship-and-social/events/316198820/?recId=87223c12-7c50-4a2a-b9d4-cb14dd08262e&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=77bf5e21-1b7b-4bbf-b4a1-a60c6109ecc9&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>Learn how to build a model router to send AI requests to the right models instead of the most expensive ones. Speaker Aria will cover why routing saves ~7x costs, four ways to build a router, and how to catch bad answers. You'll write your own routing rule and walk away with a working router. No engineering background needed.</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>The event has clear AI content (model routing for cost optimization) and appears to be educational rather than a sales pitch, but it is hosted by an Atlanta Meetup group with no identifiable Georgia organizational tie and lacks a stated location, making it difficult to confirm local relevance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Monthly Meetup + Demo Night: August 2026</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>5</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>7:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atl-ai/events/314482312/?recId=87223c12-7c50-4a2a-b9d4-cb14dd08262e&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=77bf5e21-1b7b-4bbf-b4a1-a60c6109ecc9&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>Come see demos, learn about new tools, and more from the hackers pushing the possibilities of AI in Atlanta. The evening includes doors open with food and drinks, welcome from organizers, demos from presenters, and networking with board games.</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta AI Tinkerers is a Georgia-based AI organization, the event has explicit AI content (demos, tools, hackers pushing AI possibilities), it's in-person in Atlanta, and the description demonstrates genuine educational/community focus rather than sales pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" s="3" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>no_events</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Data Science with Phython Certification Training in Columbus, GA</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>4</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Rose Hill Heights · Veterans Parkway</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/data-science-with-phython-certification-training-in-columbus-ga-tickets-1984660920238?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>A 4-day instructor-led bootcamp teaching Python, data analysis, visualization, and machine learning basics. Learn practical data science workflows with hands-on labs using real datasets, including a capstone project and career guidance to become job-ready in data science.</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>In-person 4-day bootcamp in Columbus, GA (outside metro Atlanta) with clear AI/ML content (machine learning basics, data science workflows) hosted at a specific venue, though it reads as paid training which slightly limits the score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Wednesd.AI</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>4</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>8:30 AM</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>North Buckhead · Atlanta Tech Village - Buckhead</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/wednesdai-tickets-1990814107587?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>Free weekly Wednesday morning show-and-tell where builders demonstrate how they use AI in their work. Featured speakers share tools, workflows, and lessons learned, followed by open co-working time. For founders, operators, and builders in the tech community.</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>In-person Atlanta event with strong AI focus (show-and-tell format featuring AI tools and workflows), free admission, educational value for tech builders, and clear recurring structure, though Atlanta location prevents highest score per geographic diversity guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>AI Studio Builder Lab — Build Your First AI-Powered Website</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>2</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>6:00 PM CDT</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-studio-builder-lab-build-your-first-ai-powered-website-tickets-1998389681332?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>A live, interactive lab to turn your business idea into a clear, build-ready AI-powered website plan.</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>Event has clear AI content (AI-powered website building) but is virtual-only with no Georgia host indicated, making it ineligible for higher scores per the virtual-only rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>AI Training for Business Owners: Get Out of the Day-to-Day (Free, Live)</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>2</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/ai-training-for-business-owners-get-out-of-the-day-to-day-free-live-tickets-1997983763220?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>Learn how to step out of the day-to-day of your business using AI. Discover what to systemize, delegate, and automate to reclaim your time. This live workshop shows business owners the exact moves to stop doing the work and start leading, with real tools, examples, and results.</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>Event is virtual-only with genuine AI content (automation and delegation strategies), but lacks Georgia organizational ties and reads as a general sales-oriented workshop rather than educational content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Agents, Everywhere: Beyond The Chatbot — Global Hackathon</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>5</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>46277</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://atlanta.aitinkerers.org/p/agents-everywhere-beyond-the-chatbot-global-hackathon</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>AI Tinkerers will host a hackathon for builders to develop working agents. Sponsors OpenAI, CopilotKit, and OpenRouter will provide support.</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>Hackathon hosted by Atlanta AI Tinkerers (Georgia organization) with explicit AI agent development focus, major AI sponsor support, and in-person event matching all top-tier criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" s="3" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>no_events</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8235,7 +8835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K243"/>
+  <dimension ref="A1:K258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -18822,7 +19422,6 @@
           <t>6:00 PM - 7:00 PM</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/qWFX016fkCQCe</t>
@@ -18871,7 +19470,6 @@
           <t>5:30 PM - 7:30 PM</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/07FO6JwhxCwCR</t>
@@ -18920,7 +19518,6 @@
           <t>6:00 PM EDT</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr">
         <is>
           <t>https://www.meetup.com/projects-for-developers-cs-majors-and-ux-designers/events/314898432/?recId=1b4155d4-5c2a-4e60-a0af-4a1c0ccc4b94&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=cfb680a7-12bd-4219-ac05-bff87c35a5f4&amp;eventOrigin=find_page%24all</t>
@@ -19546,7 +20143,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
           <t>Fremont, CA</t>
@@ -19589,7 +20185,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
           <t>Frisco, TX</t>
@@ -19632,7 +20227,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
           <t>Katy, TX</t>
@@ -19675,7 +20269,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr">
         <is>
           <t>Mountain View, CA</t>
@@ -19718,7 +20311,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
           <t>Menlo Park, CA</t>
@@ -19761,7 +20353,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
           <t>Norwalk, CT</t>
@@ -19804,7 +20395,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr">
         <is>
           <t>Clearwater, FL</t>
@@ -19847,7 +20437,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
           <t>El Segundo, CA</t>
@@ -19890,7 +20479,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
           <t>McKinney, TX</t>
@@ -19933,7 +20521,6 @@
           <t>August 17, 2026</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
           <t>Newark, NJ</t>
@@ -20100,6 +20687,719 @@
       <c r="K243" s="2" t="inlineStr">
         <is>
           <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rating regardless of location or in-person status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Fiber Manufacturer Webinar presented by TAG Infrastructure Society</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>1</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/4lFO3BwURCMCx</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr"/>
+      <c r="K244" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule, and the short description is empty, providing no evidence of AI content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>TAG-Ed Pathways to Leadership Virtual Open House</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>1</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar/Details/tag-ed-pathways-to-leadership-virtual-open-house-1848623?sourceTypeId=Website</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>Join us for an inside look at the Pathways to Leadership program, a year-long leadership experience designed for emerging and mid-level professionals. Learn about the program's structure and benefits, and hear from graduates.</t>
+        </is>
+      </c>
+      <c r="K245" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description—it is a generic leadership development program open house with no AI-focused component stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>TAG-Ed IBM SkillsBuild Orientation x Tech Women Foundation</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>1</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/aZFEJ70HvCqCZ</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr">
+        <is>
+          <t>Join us for a mandatory virtual orientation to kick off the upcoming cohort. During this session, participants will receive an overview of the program structure, expectations, key dates, and demo on how to access the learning platform.</t>
+        </is>
+      </c>
+      <c r="K246" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation—it is purely an orientation/onboarding session for a skills training program with no stated AI content, triggering the automatic-1 rule despite the Georgia-based host (TAG).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Steel Materials Plant Tour - Cartersville - A.M.</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>1</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>9:00 AM - 11:30 AM EDT</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Cartersville</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://www.georgiamanufacturingalliance.com/events/steel-materials-plant-tour--cartersville-2026-am</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr"/>
+      <c r="K247" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Open House!</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>1</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>7:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/freeside-atlanta/events/315518448/?recId=87223c12-7c50-4a2a-b9d4-cb14dd08262e&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=77bf5e21-1b7b-4bbf-b4a1-a60c6109ecc9&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr">
+        <is>
+          <t>A meeting hosted by Freeside Atlanta, a non-profit makerspace for engineers, programmers, inventors, and artists. Includes introductions, project updates, announcements, and occasionally a guest talk, followed by an informal open house where attendees can tour the space and network.</t>
+        </is>
+      </c>
+      <c r="K248" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation, triggering the automatic-1 rule despite being hosted by Atlanta AI Tinkerers' peer organization Freeside Atlanta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Optimized Locking in SQL Server 2025: Internals, Contention, and Concurrency</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>1</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/dba-fundamentals-group/events/312863781/?recId=87223c12-7c50-4a2a-b9d4-cb14dd08262e&amp;recSource=ml-popular-events-nearby-online&amp;searchId=77bf5e21-1b7b-4bbf-b4a1-a60c6109ecc9&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr"/>
+      <c r="K249" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description—it is about SQL Server locking internals, which is a database administration topic unrelated to AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Find a Startup to Help or Join</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>1</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/projects-for-developers-cs-majors-and-ux-designers/events/315518454/?recId=87223c12-7c50-4a2a-b9d4-cb14dd08262e&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=77bf5e21-1b7b-4bbf-b4a1-a60c6109ecc9&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr"/>
+      <c r="K250" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation, triggering the automatic-1 rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Tech and Wealth Workshop</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>1</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>5:00 PM CDT</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.ca/e/tech-and-wealth-workshop-tickets-1998674450083?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="inlineStr"/>
+      <c r="K251" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic-1 rule; additionally, it is virtual-only with no Georgia organizational tie and no AI content to override this classification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Modern Data Architecture 2 Days Training in Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>1</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Downtown · For venue information, Please contact us: info@skelora.com</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/modern-data-architecture-2-days-training-in-atlanta-ga-tickets-1992366361420?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr"/>
+      <c r="K252" s="2" t="inlineStr">
+        <is>
+          <t>The event title and description contain zero mention of AI, machine learning, or automation—only "Modern Data Architecture" training—triggering the automatic 1 score per the first criterion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Business Analyst (CBAP) Classroom Training in Macon, GA</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>1</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Mckibben Lane · 500a Northside Crossing</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/business-analyst-cbap-classroom-training-in-macon-ga-tickets-1971091244974?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr"/>
+      <c r="K253" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description—it is a business analyst certification training course with no AI-focused component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Certified Ethical Hacker – Practical Ethical Hacker in Macon, GA</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>1</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Macon, GA</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/certified-ethical-hacker-practical-ethical-hacker-in-macon-ga-tickets-1986302519305?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr"/>
+      <c r="K254" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description—it is a cybersecurity certification course (CEH) with no stated AI component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>CISSP Certification Training Course in Sandy Springs, GA</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>1</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>9:00 AM</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Oaks at Dunwoody · One Glenlake Pkwy NE</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/cissp-certification-training-course-in-sandy-springs-ga-tickets-1980091513018?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr"/>
+      <c r="K255" s="2" t="inlineStr">
+        <is>
+          <t>Event has zero mention of AI, machine learning, or automation in its title or description - it is a CISSP (cybersecurity certification) training course with no AI-focused component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Dahlonega Science Cafe Presentation</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>1</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Dahlonega · Bourbon Street Grille</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/dahlonega-science-cafe-presentation-tickets-1998496801732?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr">
+        <is>
+          <t>Join us for our monthly Dahlonega Science Cafe, where curious minds gather to explore cool science topics in a relaxed setting. Enjoy dinner, engaging conversation, and a speaker presentation followed by Q&amp;A about fascinating scientific discoveries.</t>
+        </is>
+      </c>
+      <c r="K256" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, automation, or any related technical topics—it is a general science cafe with an unspecified speaker presentation, triggering the automatic-1 rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Tech and Wealth Workshop</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>1</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>3:00 PM CDT</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.ca/e/tech-and-wealth-workshop-tickets-1998759249721?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr"/>
+      <c r="K257" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description, triggering the automatic 1 score regardless of other factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>FREE Cybersecurity Bootcamp | USA Only | Live Online</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>1</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>August 24, 2026</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>8:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>https://www.eventbrite.com/e/free-cybersecurity-bootcamp-usa-only-live-online-tickets-1996169284064?aff=ebdssbdestsearch</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr"/>
+      <c r="K258" s="2" t="inlineStr">
+        <is>
+          <t>Event is virtual-only with no Georgia host tie and no AI/machine learning/automation content in title or description, only cybersecurity bootcamp training.</t>
         </is>
       </c>
     </row>

--- a/events_master.xlsx
+++ b/events_master.xlsx
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K180" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EventsTable" displayName="EventsTable" ref="A1:K189" headerRowCount="1">
   <autoFilter ref="A1:K53"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K258" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RejectedEventsTable" displayName="RejectedEventsTable" ref="A1:K264" headerRowCount="1">
   <autoFilter ref="A1:K132"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Event Title"/>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K180"/>
+  <dimension ref="A1:K189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -8226,7 +8226,6 @@
           <t>5:30 PM</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/WqFXB5btaCJCE</t>
@@ -8275,7 +8274,6 @@
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/AnFJEbAfVCdCN</t>
@@ -8303,17 +8301,12 @@
           <t>https://www.aimanufacturingconference.com/</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr"/>
-      <c r="C169" t="inlineStr"/>
       <c r="D169" s="3" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>August 24, 2026</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>no_events</t>
@@ -8349,7 +8342,6 @@
           <t>6:30 PM EDT</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
           <t>https://www.meetup.com/blackhack-society-atlanta/events/313204276/?recId=87223c12-7c50-4a2a-b9d4-cb14dd08262e&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=77bf5e21-1b7b-4bbf-b4a1-a60c6109ecc9&amp;eventOrigin=find_page%24all</t>
@@ -8398,7 +8390,6 @@
           <t>6:30 PM EDT</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
           <t>https://www.meetup.com/blackhack-society-atlanta/events/313204253/?recId=87223c12-7c50-4a2a-b9d4-cb14dd08262e&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=77bf5e21-1b7b-4bbf-b4a1-a60c6109ecc9&amp;eventOrigin=find_page%24all</t>
@@ -8447,7 +8438,6 @@
           <t>6:00 PM EDT</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
           <t>https://www.meetup.com/ai-ship-and-social/events/316198820/?recId=87223c12-7c50-4a2a-b9d4-cb14dd08262e&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=77bf5e21-1b7b-4bbf-b4a1-a60c6109ecc9&amp;eventOrigin=find_page%24all</t>
@@ -8496,7 +8486,6 @@
           <t>7:00 PM EDT</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
           <t>https://www.meetup.com/atl-ai/events/314482312/?recId=87223c12-7c50-4a2a-b9d4-cb14dd08262e&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=77bf5e21-1b7b-4bbf-b4a1-a60c6109ecc9&amp;eventOrigin=find_page%24all</t>
@@ -8524,17 +8513,12 @@
           <t>https://luma.com/genai-collective</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr"/>
-      <c r="C174" t="inlineStr"/>
       <c r="D174" s="3" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>August 24, 2026</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>no_events</t>
@@ -8676,7 +8660,6 @@
           <t>6:00 PM CDT</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/ai-studio-builder-lab-build-your-first-ai-powered-website-tickets-1998389681332?aff=ebdssbdestsearch</t>
@@ -8725,7 +8708,6 @@
           <t>12:00 PM EDT</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/ai-training-for-business-owners-get-out-of-the-day-to-day-free-live-tickets-1997983763220?aff=ebdssbdestsearch</t>
@@ -8774,7 +8756,6 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
           <t>https://atlanta.aitinkerers.org/p/agents-everywhere-beyond-the-chatbot-global-hackathon</t>
@@ -8802,17 +8783,12 @@
           <t>https://www.meetup.com/atlbitlab/events/</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr"/>
-      <c r="C180" t="inlineStr"/>
       <c r="D180" s="3" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>August 24, 2026</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>no_events</t>
@@ -8820,6 +8796,415 @@
       </c>
       <c r="J180" s="2" t="inlineStr"/>
       <c r="K180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Techlanta 2026</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>4</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>August 31, 2026</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>11:00 AM EDT</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Georgia Tech's Historic Academy of Medicine</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://ai.gatech.edu/event/techlanta-2026</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>Don't miss this opportunity to connect with Atlanta's innovation ecosystem and help shape the future of AI, XR, robotics, advanced manufacturing, and emerging technology adoption.</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>In-person event at Georgia Tech with explicit AI focus as a stated theme alongside other emerging technologies, though the description lacks specific session or speaker details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>TAG Data Science &amp; AI Summit 2026: Building the AI-Powered Enterprise presented by TAG Data Science &amp; AI Society</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>5</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>46343</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>August 31, 2026</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>8:00 AM - 4:30 PM</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/ap/Events/Register/OOFvaqjSaCqCD</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>The TAG Data Science &amp; AI Summit 2026 is a full-day Atlanta experience connecting executive strategy with applied implementation.</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>This is a full-day, in-person AI conference hosted by TAG Data Science &amp; AI Society (a Georgia organization) in Atlanta with clear AI focus on enterprise implementation, meeting all top-tier criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>https://www.aimanufacturingconference.com/</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" s="3" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>August 31, 2026</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>no_events</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Give AI the Repeat Work, Not the Keys: Build an AI Ops Layer Safely</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>2</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>August 31, 2026</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>12:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/ai-for-agencies/events/316271485/?recId=ba055001-537f-408c-aeec-a7416042e864&amp;recSource=ml-popular-events-nearby-online&amp;searchId=2a6a602b-d05d-460f-8066-0a8cd22e8068&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>Learn how to build a secure AI operations layer that connects your tools, workflows, and data through controlled access and human guardrails. Discover how to automate audits, reporting, QA, and repeatable processes while keeping humans in control of what impacts customers and revenue.</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>Event is virtual-only with clear AI content but lacks Georgia organizational affiliation or Georgia-specific focus, making it a national webinar that scores at the virtual-only floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>GA AI Alliance Networking Lunch</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>4</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>46276</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>August 31, 2026</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>11:45 AM EDT</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/georgia-ai-alliance-meetup-group/events/316283308/?recId=ba055001-537f-408c-aeec-a7416042e864&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=2a6a602b-d05d-460f-8066-0a8cd22e8068&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>Informal networking lunch for AI professionals across Georgia. Connect with others in the AI community, share what you're working on, and build relationships. Whether you're building with AI, driving adoption, or staying current with developments, join this open invitation event.</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>Georgia-based AI community event (GA AI Alliance) with clear AI focus, in-person networking format, and statewide Georgia audience, though it's a social networking event rather than educational content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>https://luma.com/genai-collective</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" s="3" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>August 31, 2026</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>no_events</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Agents, Everywhere: Bots, Channels, &amp; More — Global Hackathon</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>5</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>46277</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>August 31, 2026</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://atlanta.aitinkerers.org/p/agents-everywhere-bots-channels-more-global-hackathon</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>AI Tinkerers will host a hackathon challenging builders to integrate agents into various environments. Sponsors like OpenAI will provide resources for this in-person event.</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>Strong AI content (agents, bots, hackathon challenge), hosted by Atlanta AI Tinkerers (Georgia organization), in-person event with clear technical focus and industry backing from OpenAI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Snowday 2026: Accelerating Georgia's Data-Driven Future</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>5</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>August 31, 2026</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>8:30 a.m.</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://ai.georgia.gov/events/2026-10-20/snowday-2026</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>A one-day event bringing together Georgia state and Atlanta city leaders to share best practices in data modernization, analytics, AI and digital service transformation. Features customer stories, panel discussions, live demonstrations in public safety, health services, transportation and higher education, hands-on labs, and networking opportunities.</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>Excellent fit: in-person event in Atlanta with explicit AI content (AI and data modernization as stated themes), hosted by Georgia state government, featuring panels, demonstrations, and labs across multiple sectors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026 Georgia Emerging Technology Summit: Data &amp; AI</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>5</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="n">
+        <v>46338</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>August 31, 2026</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>8:00 a.m.</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://ai.georgia.gov/events/2026-11-12/2026-emerging-tech-summit</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>Multi-day AI/data conference hosted by Georgia's official AI office in Atlanta with clear AI focus in the title, meeting all criteria for excellent fit.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8835,7 +9220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K258"/>
+  <dimension ref="A1:K264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -20717,7 +21102,6 @@
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/4lFO3BwURCMCx</t>
@@ -20762,7 +21146,6 @@
           <t>6:00 PM</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/calendar/Details/tag-ed-pathways-to-leadership-virtual-open-house-1848623?sourceTypeId=Website</t>
@@ -20811,7 +21194,6 @@
           <t>6:00 PM</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr">
         <is>
           <t>https://members.tagonline.org/ap/Events/Register/aZFEJ70HvCqCZ</t>
@@ -20909,7 +21291,6 @@
           <t>7:30 PM EDT</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr">
         <is>
           <t>https://www.meetup.com/freeside-atlanta/events/315518448/?recId=87223c12-7c50-4a2a-b9d4-cb14dd08262e&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=77bf5e21-1b7b-4bbf-b4a1-a60c6109ecc9&amp;eventOrigin=find_page%24all</t>
@@ -21007,7 +21388,6 @@
           <t>6:00 PM EDT</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr">
         <is>
           <t>https://www.meetup.com/projects-for-developers-cs-majors-and-ux-designers/events/315518454/?recId=87223c12-7c50-4a2a-b9d4-cb14dd08262e&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=77bf5e21-1b7b-4bbf-b4a1-a60c6109ecc9&amp;eventOrigin=find_page%24all</t>
@@ -21052,7 +21432,6 @@
           <t>5:00 PM CDT</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr">
         <is>
           <t>https://www.eventbrite.ca/e/tech-and-wealth-workshop-tickets-1998674450083?aff=ebdssbdestsearch</t>
@@ -21188,7 +21567,6 @@
           <t>August 24, 2026</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
           <t>Macon, GA</t>
@@ -21340,7 +21718,6 @@
           <t>3:00 PM CDT</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr">
         <is>
           <t>https://www.eventbrite.ca/e/tech-and-wealth-workshop-tickets-1998759249721?aff=ebdssbdestsearch</t>
@@ -21385,7 +21762,6 @@
           <t>8:00 AM EDT</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr">
         <is>
           <t>https://www.eventbrite.com/e/free-cybersecurity-bootcamp-usa-only-live-online-tickets-1996169284064?aff=ebdssbdestsearch</t>
@@ -21400,6 +21776,308 @@
       <c r="K258" s="2" t="inlineStr">
         <is>
           <t>Event is virtual-only with no Georgia host tie and no AI/machine learning/automation content in title or description, only cybersecurity bootcamp training.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Georgia Rural Health Transformation presented by TAG Digital Health Society</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>1</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>August 31, 2026</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>5:30 PM - 7:30 PM</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>https://members.tagonline.org/calendar/Details/georgia-rural-health-transformation-presented-by-tag-digital-health-society-1910658?sourceTypeId=Website</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr">
+        <is>
+          <t>A discussion exploring the impact of new approaches to workforce development, digital health, care delivery, rural hospital sustainability, maternal health, and community-based partnerships to strengthen Georgia's rural healthcare system amid workforce shortages, limited access to care, and infrastructure gaps.</t>
+        </is>
+      </c>
+      <c r="K259" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation despite being hosted by TAG Digital Health Society, and discusses only rural healthcare policy, workforce development, and care delivery with no stated AI-focused component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Out of Office Hours (Social)</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>1</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>August 31, 2026</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>6:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/refactr-tech/events/315893352/?recId=ba055001-537f-408c-aeec-a7416042e864&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=2a6a602b-d05d-460f-8066-0a8cd22e8068&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>A casual happy hour to connect with others across the Atlanta tech community in a relaxed, social setting. Meet new people, catch up with familiar faces, and expand your network. Food and drinks available for purchase.</t>
+        </is>
+      </c>
+      <c r="K260" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description—it is purely a social happy hour with no AI-focused component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Bytes &amp; Bites @ Krog St Market</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>1</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>August 31, 2026</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>11:45 AM EDT</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Krog St Market</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/refactr-tech/events/315803181/?recId=ba055001-537f-408c-aeec-a7416042e864&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=2a6a602b-d05d-460f-8066-0a8cd22e8068&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr">
+        <is>
+          <t>A casual, community-driven lunch where technologists of all backgrounds come together to connect, swap ideas, and build relationships over good food. Easy, low-pressure networking with no agenda—just lunch and conversation.</t>
+        </is>
+      </c>
+      <c r="K261" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description—it is purely a casual networking lunch with no stated AI-focused component, panel, speaker, or theme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Python Atlanta Meetup (In Person!)</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>1</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>46275</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>August 31, 2026</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>7:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/python-atlanta/events/315306147/?recId=ba055001-537f-408c-aeec-a7416042e864&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=2a6a602b-d05d-460f-8066-0a8cd22e8068&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t>A social gathering for the Atlanta Python Programmers community to discuss topics with formal talks scheduled. The meeting starts at 7:30PM, with optional dinner and socializing from 6:00-7:30PM beforehand.</t>
+        </is>
+      </c>
+      <c r="K262" s="2" t="inlineStr">
+        <is>
+          <t>The event description makes no mention of AI, machine learning, or automation—it is a general Python programming meetup with no stated AI-focused component, triggering the automatic-1 rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Open House!</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>1</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>August 31, 2026</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>7:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/freeside-atlanta/events/316117768/?recId=ba055001-537f-408c-aeec-a7416042e864&amp;recSource=ml-popular-events-nearby-offline&amp;searchId=2a6a602b-d05d-460f-8066-0a8cd22e8068&amp;eventOrigin=find_page%24all</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t>A quick meeting to introduce everyone and update on projects and equipment, followed by an informal open house where people can chat, take a tour, and check out the space. Freeside Atlanta is a 501(c)(3) non-profit for engineers, programmers, inventors, artists, and collaborators.</t>
+        </is>
+      </c>
+      <c r="K263" s="2" t="inlineStr">
+        <is>
+          <t>The event description contains zero mention of AI, machine learning, or automation - it is a general open house for a makerspace with no stated AI-focused component, triggering the automatic-1 rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Nostr Atlanta #17 - Rush Hour Avoidance</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>1</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>August 31, 2026</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>4:30 PM EDT</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>684 John Wesley Dobbs Ave NE suite a1, Atlanta, GA, US</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>https://www.meetup.com/atlbitlab/events/316328827/?eventOrigin=group_events_list</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>Join us for Nostr Atlanta! Trying to avoid the nasty rush hour traffic. Bring your laptop as this session will involve some tool building. Informal round-table discussion of Nostr and adjacent topics from 4:30–6:00 PM.</t>
+        </is>
+      </c>
+      <c r="K264" s="2" t="inlineStr">
+        <is>
+          <t>The event has zero mention of AI, machine learning, or automation in its title or description—it is a Nostr (a decentralized social protocol) meetup with tool building and discussion, which falls outside the AI criteria despite being hosted by ATL BitLab, a Georgia organization.</t>
         </is>
       </c>
     </row>
